--- a/research/traditional_assets/database/data/denmark/denmark_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_business_consumer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cpse_iss" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0276</v>
-      </c>
-      <c r="F2">
-        <v>0.477</v>
+        <v>-0.0153</v>
+      </c>
+      <c r="E2">
+        <v>-0.103</v>
       </c>
       <c r="G2">
-        <v>-0.05965315598857841</v>
+        <v>0.02677711263242674</v>
       </c>
       <c r="H2">
-        <v>-0.05965315598857841</v>
+        <v>0.02669879886624125</v>
       </c>
       <c r="I2">
-        <v>-0.03363529379567037</v>
+        <v>0.02699772706152035</v>
       </c>
       <c r="J2">
-        <v>-0.03363529379567037</v>
+        <v>0.02382955676396207</v>
       </c>
       <c r="K2">
-        <v>-363.2</v>
+        <v>173.73</v>
       </c>
       <c r="L2">
-        <v>-0.03313354680387166</v>
+        <v>0.01681761507961093</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>715.6</v>
+        <v>635.4979999999999</v>
       </c>
       <c r="V2">
-        <v>0.2035267349260523</v>
+        <v>0.1623541969139065</v>
       </c>
       <c r="W2">
-        <v>-0.2593359514459121</v>
+        <v>-0.5735294117647058</v>
       </c>
       <c r="X2">
-        <v>0.08308149273103133</v>
+        <v>0.1258059541751281</v>
       </c>
       <c r="Y2">
-        <v>-0.3424174441769435</v>
+        <v>-0.699335365939834</v>
       </c>
       <c r="Z2">
-        <v>13.86854757085019</v>
+        <v>61.52981118589536</v>
       </c>
       <c r="AA2">
-        <v>-0.466472672064777</v>
+        <v>-0.2958158995815899</v>
       </c>
       <c r="AB2">
-        <v>0.0571197093385717</v>
+        <v>0.09629112764643424</v>
       </c>
       <c r="AC2">
-        <v>-0.5235923814033487</v>
+        <v>-0.3893506644762242</v>
       </c>
       <c r="AD2">
-        <v>2880.3</v>
+        <v>2366.33</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2880.3</v>
+        <v>2366.33</v>
       </c>
       <c r="AG2">
-        <v>2164.7</v>
+        <v>1730.832</v>
       </c>
       <c r="AH2">
-        <v>0.4503072088551194</v>
+        <v>0.37676820316024</v>
       </c>
       <c r="AI2">
-        <v>0.7252788759348324</v>
+        <v>0.6303719661585945</v>
       </c>
       <c r="AJ2">
-        <v>0.3810621930395902</v>
+        <v>0.3066078002855928</v>
       </c>
       <c r="AK2">
-        <v>0.6648954141966398</v>
+        <v>0.5550447109302471</v>
       </c>
       <c r="AL2">
-        <v>75.90000000000001</v>
+        <v>63.029</v>
       </c>
       <c r="AM2">
-        <v>71.28</v>
+        <v>54.58</v>
       </c>
       <c r="AN2">
-        <v>-10.84858757062147</v>
+        <v>6.461939676948074</v>
       </c>
       <c r="AO2">
-        <v>-4.857707509881422</v>
+        <v>4.424836186517317</v>
       </c>
       <c r="AP2">
-        <v>-8.153295668549907</v>
+        <v>4.726530946626797</v>
       </c>
       <c r="AQ2">
-        <v>-5.172558922558922</v>
+        <v>5.10980212532063</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0276</v>
-      </c>
-      <c r="F3">
-        <v>0.477</v>
+        <v>-0.0153</v>
+      </c>
+      <c r="E3">
+        <v>-0.103</v>
       </c>
       <c r="G3">
-        <v>-0.05965315598857841</v>
+        <v>0.02687969014766401</v>
       </c>
       <c r="H3">
-        <v>-0.05965315598857841</v>
+        <v>0.02687969014766401</v>
       </c>
       <c r="I3">
-        <v>-0.03363529379567037</v>
+        <v>0.02722827402565964</v>
       </c>
       <c r="J3">
-        <v>-0.03363529379567037</v>
+        <v>0.01764259940661103</v>
       </c>
       <c r="K3">
-        <v>-363.2</v>
+        <v>176.3</v>
       </c>
       <c r="L3">
-        <v>-0.03313354680387166</v>
+        <v>0.01707092713628661</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +760,9032 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>715.6</v>
+        <v>633.9</v>
       </c>
       <c r="V3">
-        <v>0.2035267349260523</v>
+        <v>0.1621393492940454</v>
       </c>
       <c r="W3">
-        <v>-0.2593359514459121</v>
+        <v>0.1621895124195032</v>
       </c>
       <c r="X3">
-        <v>0.08308149273103133</v>
+        <v>0.1258059541751281</v>
       </c>
       <c r="Y3">
-        <v>-0.3424174441769435</v>
+        <v>0.03638355824437509</v>
       </c>
       <c r="Z3">
-        <v>13.86854757085019</v>
+        <v>62.40181268882158</v>
       </c>
       <c r="AA3">
-        <v>-0.466472672064777</v>
+        <v>1.100930183515256</v>
       </c>
       <c r="AB3">
-        <v>0.0571197093385717</v>
+        <v>0.09629112764643424</v>
       </c>
       <c r="AC3">
-        <v>-0.5235923814033487</v>
+        <v>1.004639055868822</v>
       </c>
       <c r="AD3">
-        <v>2880.3</v>
+        <v>2365.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2880.3</v>
+        <v>2365.1</v>
       </c>
       <c r="AG3">
-        <v>2164.7</v>
+        <v>1731.2</v>
       </c>
       <c r="AH3">
-        <v>0.4503072088551194</v>
+        <v>0.3769263869188965</v>
       </c>
       <c r="AI3">
-        <v>0.7252788759348324</v>
+        <v>0.6307942604149998</v>
       </c>
       <c r="AJ3">
-        <v>0.3810621930395902</v>
+        <v>0.3069068217274146</v>
       </c>
       <c r="AK3">
-        <v>0.6648954141966398</v>
+        <v>0.5556732466698764</v>
       </c>
       <c r="AL3">
-        <v>75.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="AM3">
-        <v>71.28</v>
+        <v>54.46</v>
       </c>
       <c r="AN3">
-        <v>-10.84858757062147</v>
+        <v>6.421667119196307</v>
       </c>
       <c r="AO3">
-        <v>-4.857707509881422</v>
+        <v>4.470588235294118</v>
       </c>
       <c r="AP3">
-        <v>-8.153295668549907</v>
+        <v>4.700515883790388</v>
       </c>
       <c r="AQ3">
-        <v>-5.172558922558922</v>
+        <v>5.163422695556371</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Happy Helper A/S (CPSE:HAPPY)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.04657534246575332</v>
+      </c>
+      <c r="H4">
+        <v>-0.9520547945205479</v>
+      </c>
+      <c r="I4">
+        <v>-0.9684931506849315</v>
+      </c>
+      <c r="J4">
+        <v>-0.9684931506849315</v>
+      </c>
+      <c r="K4">
+        <v>-1.17</v>
+      </c>
+      <c r="L4">
+        <v>-1.602739726027397</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.148</v>
+      </c>
+      <c r="V4">
+        <v>0.337129840546697</v>
+      </c>
+      <c r="W4">
+        <v>-0.5735294117647058</v>
+      </c>
+      <c r="X4">
+        <v>0.227099778152949</v>
+      </c>
+      <c r="Y4">
+        <v>-0.8006291899176549</v>
+      </c>
+      <c r="Z4">
+        <v>0.305439330543933</v>
+      </c>
+      <c r="AA4">
+        <v>-0.2958158995815899</v>
+      </c>
+      <c r="AB4">
+        <v>0.0935347648946343</v>
+      </c>
+      <c r="AC4">
+        <v>-0.3893506644762242</v>
+      </c>
+      <c r="AD4">
+        <v>1.23</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1.23</v>
+      </c>
+      <c r="AG4">
+        <v>1.082</v>
+      </c>
+      <c r="AH4">
+        <v>0.7369682444577591</v>
+      </c>
+      <c r="AI4">
+        <v>0.6821963394342763</v>
+      </c>
+      <c r="AJ4">
+        <v>0.7113740959894805</v>
+      </c>
+      <c r="AK4">
+        <v>0.6537764350453172</v>
+      </c>
+      <c r="AL4">
+        <v>0.074</v>
+      </c>
+      <c r="AM4">
+        <v>0.074</v>
+      </c>
+      <c r="AN4">
+        <v>-1.769784172661871</v>
+      </c>
+      <c r="AO4">
+        <v>-9.554054054054054</v>
+      </c>
+      <c r="AP4">
+        <v>-1.556834532374101</v>
+      </c>
+      <c r="AQ4">
+        <v>-9.554054054054054</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Copyright Agent A/S (CPSE:COPY)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-0.47363184079602</v>
+      </c>
+      <c r="H5">
+        <v>-0.5472636815920399</v>
+      </c>
+      <c r="I5">
+        <v>-0.7960199004975126</v>
+      </c>
+      <c r="J5">
+        <v>-0.7960199004975126</v>
+      </c>
+      <c r="K5">
+        <v>-1.4</v>
+      </c>
+      <c r="L5">
+        <v>-0.6965174129353234</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1.45</v>
+      </c>
+      <c r="V5">
+        <v>0.342789598108747</v>
+      </c>
+      <c r="W5">
+        <v>-5.691056910569105</v>
+      </c>
+      <c r="X5">
+        <v>0.09791298813582996</v>
+      </c>
+      <c r="Y5">
+        <v>-5.788969898704935</v>
+      </c>
+      <c r="AB5">
+        <v>0.09791298813582996</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-1.45</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.5215827338129496</v>
+      </c>
+      <c r="AK5">
+        <v>-1.198347107438016</v>
+      </c>
+      <c r="AL5">
+        <v>0.055</v>
+      </c>
+      <c r="AM5">
+        <v>0.046</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
+      </c>
+      <c r="AO5">
+        <v>-29.09090909090909</v>
+      </c>
+      <c r="AP5">
+        <v>1.028368794326241</v>
+      </c>
+      <c r="AQ5">
+        <v>-34.78260869565218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ISS A/S (CPSE:ISS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CPSE:ISS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.376926386918897</v>
+      </c>
+      <c r="F2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G2">
+        <v>3909.6</v>
+      </c>
+      <c r="H2">
+        <v>5739.17268978229</v>
+      </c>
+      <c r="I2">
+        <v>5640.8</v>
+      </c>
+      <c r="J2">
+        <v>5544.50168978229</v>
+      </c>
+      <c r="K2">
+        <v>2365.1</v>
+      </c>
+      <c r="L2">
+        <v>439.229</v>
+      </c>
+      <c r="M2">
+        <v>0.0962911276464342</v>
+      </c>
+      <c r="N2">
+        <v>0.0972896481185382</v>
+      </c>
+      <c r="O2">
+        <v>0.047502</v>
+      </c>
+      <c r="P2">
+        <v>0.0429</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.125805954175128</v>
+      </c>
+      <c r="T2">
+        <v>0.101383492600579</v>
+      </c>
+      <c r="U2">
+        <v>1.47112646089818</v>
+      </c>
+      <c r="V2">
+        <v>1.05818311922445</v>
+      </c>
+      <c r="W2">
+        <v>4.590688766824679</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>3909.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0609</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>368.3</v>
+      </c>
+      <c r="AH2">
+        <v>257.4</v>
+      </c>
+      <c r="AI2">
+        <v>173.7</v>
+      </c>
+      <c r="AJ2">
+        <v>2365.1</v>
+      </c>
+      <c r="AK2">
+        <v>2365.1</v>
+      </c>
+      <c r="AL2">
+        <v>62.9</v>
+      </c>
+      <c r="AM2">
+        <v>2365.1</v>
+      </c>
+      <c r="AN2">
+        <v>633.9</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09791298813582996</v>
+      </c>
+      <c r="C2">
+        <v>6119.935523747137</v>
+      </c>
+      <c r="D2">
+        <v>5486.035523747138</v>
+      </c>
+      <c r="E2">
+        <v>-2365.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>633.9</v>
+      </c>
+      <c r="H2">
+        <v>3909.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>368.3</v>
+      </c>
+      <c r="K2">
+        <v>257.4</v>
+      </c>
+      <c r="L2">
+        <v>110.9</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>110.9</v>
+      </c>
+      <c r="O2">
+        <v>24.398</v>
+      </c>
+      <c r="P2">
+        <v>86.50200000000004</v>
+      </c>
+      <c r="Q2">
+        <v>343.902</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09791298813582996</v>
+      </c>
+      <c r="T2">
+        <v>0.9995026415587441</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09775139956193113</v>
+      </c>
+      <c r="C3">
+        <v>6072.226006541916</v>
+      </c>
+      <c r="D3">
+        <v>5501.073006541917</v>
+      </c>
+      <c r="E3">
+        <v>-2302.353</v>
+      </c>
+      <c r="F3">
+        <v>62.747</v>
+      </c>
+      <c r="G3">
+        <v>633.9</v>
+      </c>
+      <c r="H3">
+        <v>3909.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>368.3</v>
+      </c>
+      <c r="K3">
+        <v>257.4</v>
+      </c>
+      <c r="L3">
+        <v>110.9</v>
+      </c>
+      <c r="M3">
+        <v>2.8675379</v>
+      </c>
+      <c r="N3">
+        <v>108.0324621</v>
+      </c>
+      <c r="O3">
+        <v>23.767141662</v>
+      </c>
+      <c r="P3">
+        <v>84.26532043800003</v>
+      </c>
+      <c r="Q3">
+        <v>341.665320438</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09837872683023346</v>
+      </c>
+      <c r="T3">
+        <v>1.007377510855874</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.035646</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>38.67429267456239</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09758981098803231</v>
+      </c>
+      <c r="C4">
+        <v>6024.59915282409</v>
+      </c>
+      <c r="D4">
+        <v>5516.19315282409</v>
+      </c>
+      <c r="E4">
+        <v>-2239.606</v>
+      </c>
+      <c r="F4">
+        <v>125.494</v>
+      </c>
+      <c r="G4">
+        <v>633.9</v>
+      </c>
+      <c r="H4">
+        <v>3909.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>368.3</v>
+      </c>
+      <c r="K4">
+        <v>257.4</v>
+      </c>
+      <c r="L4">
+        <v>110.9</v>
+      </c>
+      <c r="M4">
+        <v>5.735075800000001</v>
+      </c>
+      <c r="N4">
+        <v>105.1649242</v>
+      </c>
+      <c r="O4">
+        <v>23.136283324</v>
+      </c>
+      <c r="P4">
+        <v>82.02864087600003</v>
+      </c>
+      <c r="Q4">
+        <v>339.428640876</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09885397039595133</v>
+      </c>
+      <c r="T4">
+        <v>1.015413091771312</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.035646</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>19.33714633728119</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09746566241413347</v>
+      </c>
+      <c r="C5">
+        <v>5973.525548897577</v>
+      </c>
+      <c r="D5">
+        <v>5527.866548897578</v>
+      </c>
+      <c r="E5">
+        <v>-2176.859</v>
+      </c>
+      <c r="F5">
+        <v>188.241</v>
+      </c>
+      <c r="G5">
+        <v>633.9</v>
+      </c>
+      <c r="H5">
+        <v>3909.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>368.3</v>
+      </c>
+      <c r="K5">
+        <v>257.4</v>
+      </c>
+      <c r="L5">
+        <v>110.9</v>
+      </c>
+      <c r="M5">
+        <v>8.903799299999999</v>
+      </c>
+      <c r="N5">
+        <v>101.9962007</v>
+      </c>
+      <c r="O5">
+        <v>22.439164154</v>
+      </c>
+      <c r="P5">
+        <v>79.55703654600003</v>
+      </c>
+      <c r="Q5">
+        <v>336.957036546</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09933901279807575</v>
+      </c>
+      <c r="T5">
+        <v>1.023614354767481</v>
+      </c>
+      <c r="U5">
+        <v>0.0473</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.036894</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>12.45535711929177</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09743511384023464</v>
+      </c>
+      <c r="C6">
+        <v>5913.658537162492</v>
+      </c>
+      <c r="D6">
+        <v>5530.746537162493</v>
+      </c>
+      <c r="E6">
+        <v>-2114.112</v>
+      </c>
+      <c r="F6">
+        <v>250.988</v>
+      </c>
+      <c r="G6">
+        <v>633.9</v>
+      </c>
+      <c r="H6">
+        <v>3909.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>368.3</v>
+      </c>
+      <c r="K6">
+        <v>257.4</v>
+      </c>
+      <c r="L6">
+        <v>110.9</v>
+      </c>
+      <c r="M6">
+        <v>12.8254868</v>
+      </c>
+      <c r="N6">
+        <v>98.07451320000004</v>
+      </c>
+      <c r="O6">
+        <v>21.57639290400001</v>
+      </c>
+      <c r="P6">
+        <v>76.49812029600004</v>
+      </c>
+      <c r="Q6">
+        <v>333.898120296</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09983416025024441</v>
+      </c>
+      <c r="T6">
+        <v>1.031986477409403</v>
+      </c>
+      <c r="U6">
+        <v>0.0511</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.039858</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>8.646845279977992</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09738974526633583</v>
+      </c>
+      <c r="C7">
+        <v>5855.194233423523</v>
+      </c>
+      <c r="D7">
+        <v>5535.029233423523</v>
+      </c>
+      <c r="E7">
+        <v>-2051.365</v>
+      </c>
+      <c r="F7">
+        <v>313.735</v>
+      </c>
+      <c r="G7">
+        <v>633.9</v>
+      </c>
+      <c r="H7">
+        <v>3909.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>368.3</v>
+      </c>
+      <c r="K7">
+        <v>257.4</v>
+      </c>
+      <c r="L7">
+        <v>110.9</v>
+      </c>
+      <c r="M7">
+        <v>16.627955</v>
+      </c>
+      <c r="N7">
+        <v>94.27204500000003</v>
+      </c>
+      <c r="O7">
+        <v>20.73984990000001</v>
+      </c>
+      <c r="P7">
+        <v>73.53219510000002</v>
+      </c>
+      <c r="Q7">
+        <v>330.9321951</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1003397318593009</v>
+      </c>
+      <c r="T7">
+        <v>1.04053485526484</v>
+      </c>
+      <c r="U7">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>6.669491227273589</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09737869669243701</v>
+      </c>
+      <c r="C8">
+        <v>5793.491199625752</v>
+      </c>
+      <c r="D8">
+        <v>5536.073199625753</v>
+      </c>
+      <c r="E8">
+        <v>-1988.618</v>
+      </c>
+      <c r="F8">
+        <v>376.482</v>
+      </c>
+      <c r="G8">
+        <v>633.9</v>
+      </c>
+      <c r="H8">
+        <v>3909.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>368.3</v>
+      </c>
+      <c r="K8">
+        <v>257.4</v>
+      </c>
+      <c r="L8">
+        <v>110.9</v>
+      </c>
+      <c r="M8">
+        <v>20.70651</v>
+      </c>
+      <c r="N8">
+        <v>90.19349000000004</v>
+      </c>
+      <c r="O8">
+        <v>19.8425678</v>
+      </c>
+      <c r="P8">
+        <v>70.35092220000004</v>
+      </c>
+      <c r="Q8">
+        <v>327.7509222</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1008560603111032</v>
+      </c>
+      <c r="T8">
+        <v>1.049265113500179</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.0429</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>5.35580356129546</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09728964811853819</v>
+      </c>
+      <c r="C9">
+        <v>5739.172689782285</v>
+      </c>
+      <c r="D9">
+        <v>5544.501689782286</v>
+      </c>
+      <c r="E9">
+        <v>-1925.871</v>
+      </c>
+      <c r="F9">
+        <v>439.229</v>
+      </c>
+      <c r="G9">
+        <v>633.9</v>
+      </c>
+      <c r="H9">
+        <v>3909.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>368.3</v>
+      </c>
+      <c r="K9">
+        <v>257.4</v>
+      </c>
+      <c r="L9">
+        <v>110.9</v>
+      </c>
+      <c r="M9">
+        <v>24.157595</v>
+      </c>
+      <c r="N9">
+        <v>86.74240500000003</v>
+      </c>
+      <c r="O9">
+        <v>19.0833291</v>
+      </c>
+      <c r="P9">
+        <v>67.65907590000003</v>
+      </c>
+      <c r="Q9">
+        <v>325.0590759</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1013834926005787</v>
+      </c>
+      <c r="T9">
+        <v>1.058183119224451</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.0429</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>4.590688766824679</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09769979954463935</v>
+      </c>
+      <c r="C10">
+        <v>5637.8163007408</v>
+      </c>
+      <c r="D10">
+        <v>5505.8923007408</v>
+      </c>
+      <c r="E10">
+        <v>-1863.124</v>
+      </c>
+      <c r="F10">
+        <v>501.976</v>
+      </c>
+      <c r="G10">
+        <v>633.9</v>
+      </c>
+      <c r="H10">
+        <v>3909.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>368.3</v>
+      </c>
+      <c r="K10">
+        <v>257.4</v>
+      </c>
+      <c r="L10">
+        <v>110.9</v>
+      </c>
+      <c r="M10">
+        <v>31.624488</v>
+      </c>
+      <c r="N10">
+        <v>79.27551200000003</v>
+      </c>
+      <c r="O10">
+        <v>17.44061264</v>
+      </c>
+      <c r="P10">
+        <v>61.83489936000003</v>
+      </c>
+      <c r="Q10">
+        <v>319.23489936</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1019223908093906</v>
+      </c>
+      <c r="T10">
+        <v>1.067294994638381</v>
+      </c>
+      <c r="U10">
+        <v>0.063</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.04914</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>3.506776141324408</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09966683097074053</v>
+      </c>
+      <c r="C11">
+        <v>5397.135555685271</v>
+      </c>
+      <c r="D11">
+        <v>5327.958555685272</v>
+      </c>
+      <c r="E11">
+        <v>-1800.377</v>
+      </c>
+      <c r="F11">
+        <v>564.723</v>
+      </c>
+      <c r="G11">
+        <v>633.9</v>
+      </c>
+      <c r="H11">
+        <v>3909.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>368.3</v>
+      </c>
+      <c r="K11">
+        <v>257.4</v>
+      </c>
+      <c r="L11">
+        <v>110.9</v>
+      </c>
+      <c r="M11">
+        <v>51.6156822</v>
+      </c>
+      <c r="N11">
+        <v>59.28431780000003</v>
+      </c>
+      <c r="O11">
+        <v>13.04254991600001</v>
+      </c>
+      <c r="P11">
+        <v>46.24176788400003</v>
+      </c>
+      <c r="Q11">
+        <v>303.641767884</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1024731329348797</v>
+      </c>
+      <c r="T11">
+        <v>1.076607131050419</v>
+      </c>
+      <c r="U11">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>2.148571815253466</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1015075023968417</v>
+      </c>
+      <c r="C12">
+        <v>5177.995449628554</v>
+      </c>
+      <c r="D12">
+        <v>5171.565449628554</v>
+      </c>
+      <c r="E12">
+        <v>-1737.63</v>
+      </c>
+      <c r="F12">
+        <v>627.47</v>
+      </c>
+      <c r="G12">
+        <v>633.9</v>
+      </c>
+      <c r="H12">
+        <v>3909.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>368.3</v>
+      </c>
+      <c r="K12">
+        <v>257.4</v>
+      </c>
+      <c r="L12">
+        <v>110.9</v>
+      </c>
+      <c r="M12">
+        <v>70.59037500000001</v>
+      </c>
+      <c r="N12">
+        <v>40.30962500000003</v>
+      </c>
+      <c r="O12">
+        <v>8.868117500000004</v>
+      </c>
+      <c r="P12">
+        <v>31.44150750000002</v>
+      </c>
+      <c r="Q12">
+        <v>288.8415075</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1030361137742686</v>
+      </c>
+      <c r="T12">
+        <v>1.086126203827169</v>
+      </c>
+      <c r="U12">
+        <v>0.1125</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>1.571035711313334</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1102135505233433</v>
+      </c>
+      <c r="C13">
+        <v>4484.781299292683</v>
+      </c>
+      <c r="D13">
+        <v>4541.098299292683</v>
+      </c>
+      <c r="E13">
+        <v>-1674.883</v>
+      </c>
+      <c r="F13">
+        <v>690.217</v>
+      </c>
+      <c r="G13">
+        <v>633.9</v>
+      </c>
+      <c r="H13">
+        <v>3909.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>368.3</v>
+      </c>
+      <c r="K13">
+        <v>257.4</v>
+      </c>
+      <c r="L13">
+        <v>110.9</v>
+      </c>
+      <c r="M13">
+        <v>135.6966622</v>
+      </c>
+      <c r="N13">
+        <v>-24.79666219999996</v>
+      </c>
+      <c r="O13">
+        <v>-5.45526568399999</v>
+      </c>
+      <c r="P13">
+        <v>-19.34139651599997</v>
+      </c>
+      <c r="Q13">
+        <v>238.058603484</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1039054650661166</v>
+      </c>
+      <c r="T13">
+        <v>1.100825493104308</v>
+      </c>
+      <c r="U13">
+        <v>0.1966</v>
+      </c>
+      <c r="V13">
+        <v>0.1797980849671924</v>
+      </c>
+      <c r="W13">
+        <v>0.16125169649545</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.8172640225781473</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1139496054190597</v>
+      </c>
+      <c r="C14">
+        <v>4196.27406491228</v>
+      </c>
+      <c r="D14">
+        <v>4315.33806491228</v>
+      </c>
+      <c r="E14">
+        <v>-1612.136</v>
+      </c>
+      <c r="F14">
+        <v>752.9639999999999</v>
+      </c>
+      <c r="G14">
+        <v>633.9</v>
+      </c>
+      <c r="H14">
+        <v>3909.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>368.3</v>
+      </c>
+      <c r="K14">
+        <v>257.4</v>
+      </c>
+      <c r="L14">
+        <v>110.9</v>
+      </c>
+      <c r="M14">
+        <v>160.9837032</v>
+      </c>
+      <c r="N14">
+        <v>-50.08370319999995</v>
+      </c>
+      <c r="O14">
+        <v>-11.01841470399999</v>
+      </c>
+      <c r="P14">
+        <v>-39.06528849599996</v>
+      </c>
+      <c r="Q14">
+        <v>218.334711504</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1047521804597275</v>
+      </c>
+      <c r="T14">
+        <v>1.115142046864335</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0.1515557134978369</v>
+      </c>
+      <c r="W14">
+        <v>0.1813973884541625</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.6888896068083497</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1156996054190597</v>
+      </c>
+      <c r="C15">
+        <v>4035.323159021692</v>
+      </c>
+      <c r="D15">
+        <v>4217.134159021693</v>
+      </c>
+      <c r="E15">
+        <v>-1549.389</v>
+      </c>
+      <c r="F15">
+        <v>815.711</v>
+      </c>
+      <c r="G15">
+        <v>633.9</v>
+      </c>
+      <c r="H15">
+        <v>3909.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>368.3</v>
+      </c>
+      <c r="K15">
+        <v>257.4</v>
+      </c>
+      <c r="L15">
+        <v>110.9</v>
+      </c>
+      <c r="M15">
+        <v>174.3990118</v>
+      </c>
+      <c r="N15">
+        <v>-63.49901179999995</v>
+      </c>
+      <c r="O15">
+        <v>-13.96978259599999</v>
+      </c>
+      <c r="P15">
+        <v>-49.52922920399996</v>
+      </c>
+      <c r="Q15">
+        <v>207.870770796</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1055102514994945</v>
+      </c>
+      <c r="T15">
+        <v>1.127959771540937</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.139897581690311</v>
+      </c>
+      <c r="W15">
+        <v>0.1838898970346115</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.6358980985923226</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1174496054190597</v>
+      </c>
+      <c r="C16">
+        <v>3878.742442514585</v>
+      </c>
+      <c r="D16">
+        <v>4123.300442514585</v>
+      </c>
+      <c r="E16">
+        <v>-1486.642</v>
+      </c>
+      <c r="F16">
+        <v>878.4580000000001</v>
+      </c>
+      <c r="G16">
+        <v>633.9</v>
+      </c>
+      <c r="H16">
+        <v>3909.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>368.3</v>
+      </c>
+      <c r="K16">
+        <v>257.4</v>
+      </c>
+      <c r="L16">
+        <v>110.9</v>
+      </c>
+      <c r="M16">
+        <v>187.8143204</v>
+      </c>
+      <c r="N16">
+        <v>-76.91432039999998</v>
+      </c>
+      <c r="O16">
+        <v>-16.92115048799999</v>
+      </c>
+      <c r="P16">
+        <v>-59.99316991199998</v>
+      </c>
+      <c r="Q16">
+        <v>197.406830088</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1062859520983258</v>
+      </c>
+      <c r="T16">
+        <v>1.141075582837925</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1299048972838602</v>
+      </c>
+      <c r="W16">
+        <v>0.1860263329607107</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.5904768058357281</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1191996054190597</v>
+      </c>
+      <c r="C17">
+        <v>3726.246547146377</v>
+      </c>
+      <c r="D17">
+        <v>4033.551547146376</v>
+      </c>
+      <c r="E17">
+        <v>-1423.895</v>
+      </c>
+      <c r="F17">
+        <v>941.2049999999999</v>
+      </c>
+      <c r="G17">
+        <v>633.9</v>
+      </c>
+      <c r="H17">
+        <v>3909.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>368.3</v>
+      </c>
+      <c r="K17">
+        <v>257.4</v>
+      </c>
+      <c r="L17">
+        <v>110.9</v>
+      </c>
+      <c r="M17">
+        <v>201.229629</v>
+      </c>
+      <c r="N17">
+        <v>-90.32962899999995</v>
+      </c>
+      <c r="O17">
+        <v>-19.87251837999999</v>
+      </c>
+      <c r="P17">
+        <v>-70.45711061999997</v>
+      </c>
+      <c r="Q17">
+        <v>186.94288938</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1070799044759531</v>
+      </c>
+      <c r="T17">
+        <v>1.154500001459547</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1212445707982695</v>
+      </c>
+      <c r="W17">
+        <v>0.18787791076333</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.5511116854466795</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1209496054190596</v>
+      </c>
+      <c r="C18">
+        <v>3577.574421012192</v>
+      </c>
+      <c r="D18">
+        <v>3947.626421012193</v>
+      </c>
+      <c r="E18">
+        <v>-1361.148</v>
+      </c>
+      <c r="F18">
+        <v>1003.952</v>
+      </c>
+      <c r="G18">
+        <v>633.9</v>
+      </c>
+      <c r="H18">
+        <v>3909.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>368.3</v>
+      </c>
+      <c r="K18">
+        <v>257.4</v>
+      </c>
+      <c r="L18">
+        <v>110.9</v>
+      </c>
+      <c r="M18">
+        <v>214.6449376</v>
+      </c>
+      <c r="N18">
+        <v>-103.7449376</v>
+      </c>
+      <c r="O18">
+        <v>-22.82388627199999</v>
+      </c>
+      <c r="P18">
+        <v>-80.92105132799998</v>
+      </c>
+      <c r="Q18">
+        <v>176.478948672</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1078927604816192</v>
+      </c>
+      <c r="T18">
+        <v>1.16824404909597</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1136667851233777</v>
+      </c>
+      <c r="W18">
+        <v>0.1894980413406218</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5166672051062622</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1270621545534054</v>
+      </c>
+      <c r="C19">
+        <v>3241.436627590333</v>
+      </c>
+      <c r="D19">
+        <v>3674.235627590333</v>
+      </c>
+      <c r="E19">
+        <v>-1298.401</v>
+      </c>
+      <c r="F19">
+        <v>1066.699</v>
+      </c>
+      <c r="G19">
+        <v>633.9</v>
+      </c>
+      <c r="H19">
+        <v>3909.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>368.3</v>
+      </c>
+      <c r="K19">
+        <v>257.4</v>
+      </c>
+      <c r="L19">
+        <v>110.9</v>
+      </c>
+      <c r="M19">
+        <v>254.7277212</v>
+      </c>
+      <c r="N19">
+        <v>-143.8277212</v>
+      </c>
+      <c r="O19">
+        <v>-31.64209866399999</v>
+      </c>
+      <c r="P19">
+        <v>-112.185622536</v>
+      </c>
+      <c r="Q19">
+        <v>145.214377464</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1088608047456697</v>
+      </c>
+      <c r="T19">
+        <v>1.184612072936026</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.09578070217510351</v>
+      </c>
+      <c r="W19">
+        <v>0.2159275683205853</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.4353668280686525</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1290621545534053</v>
+      </c>
+      <c r="C20">
+        <v>3097.27708773308</v>
+      </c>
+      <c r="D20">
+        <v>3592.823087733081</v>
+      </c>
+      <c r="E20">
+        <v>-1235.654</v>
+      </c>
+      <c r="F20">
+        <v>1129.446</v>
+      </c>
+      <c r="G20">
+        <v>633.9</v>
+      </c>
+      <c r="H20">
+        <v>3909.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>368.3</v>
+      </c>
+      <c r="K20">
+        <v>257.4</v>
+      </c>
+      <c r="L20">
+        <v>110.9</v>
+      </c>
+      <c r="M20">
+        <v>269.7117048</v>
+      </c>
+      <c r="N20">
+        <v>-158.8117048</v>
+      </c>
+      <c r="O20">
+        <v>-34.93857505599999</v>
+      </c>
+      <c r="P20">
+        <v>-123.873129744</v>
+      </c>
+      <c r="Q20">
+        <v>133.526870256</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1097152048035437</v>
+      </c>
+      <c r="T20">
+        <v>1.199058561630368</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.09045955205426444</v>
+      </c>
+      <c r="W20">
+        <v>0.2171982589694416</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.4111797820648384</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1310621545534054</v>
+      </c>
+      <c r="C21">
+        <v>2956.647165854132</v>
+      </c>
+      <c r="D21">
+        <v>3514.940165854133</v>
+      </c>
+      <c r="E21">
+        <v>-1172.907</v>
+      </c>
+      <c r="F21">
+        <v>1192.193</v>
+      </c>
+      <c r="G21">
+        <v>633.9</v>
+      </c>
+      <c r="H21">
+        <v>3909.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>368.3</v>
+      </c>
+      <c r="K21">
+        <v>257.4</v>
+      </c>
+      <c r="L21">
+        <v>110.9</v>
+      </c>
+      <c r="M21">
+        <v>284.6956884</v>
+      </c>
+      <c r="N21">
+        <v>-173.7956884</v>
+      </c>
+      <c r="O21">
+        <v>-38.23505144799999</v>
+      </c>
+      <c r="P21">
+        <v>-135.560636952</v>
+      </c>
+      <c r="Q21">
+        <v>121.839363048</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.110590701159143</v>
+      </c>
+      <c r="T21">
+        <v>1.213861753749262</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.08569852299877684</v>
+      </c>
+      <c r="W21">
+        <v>0.2183351927078921</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3895387409035311</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1330621545534053</v>
+      </c>
+      <c r="C22">
+        <v>2819.322193761152</v>
+      </c>
+      <c r="D22">
+        <v>3440.362193761152</v>
+      </c>
+      <c r="E22">
+        <v>-1110.16</v>
+      </c>
+      <c r="F22">
+        <v>1254.94</v>
+      </c>
+      <c r="G22">
+        <v>633.9</v>
+      </c>
+      <c r="H22">
+        <v>3909.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>368.3</v>
+      </c>
+      <c r="K22">
+        <v>257.4</v>
+      </c>
+      <c r="L22">
+        <v>110.9</v>
+      </c>
+      <c r="M22">
+        <v>299.679672</v>
+      </c>
+      <c r="N22">
+        <v>-188.779672</v>
+      </c>
+      <c r="O22">
+        <v>-41.53152784</v>
+      </c>
+      <c r="P22">
+        <v>-147.24814416</v>
+      </c>
+      <c r="Q22">
+        <v>110.15185584</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1114880849236323</v>
+      </c>
+      <c r="T22">
+        <v>1.229035025671127</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.08141359684883799</v>
+      </c>
+      <c r="W22">
+        <v>0.2193584330724975</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3700618038583545</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1350621545534053</v>
+      </c>
+      <c r="C23">
+        <v>2685.096174623834</v>
+      </c>
+      <c r="D23">
+        <v>3368.883174623833</v>
+      </c>
+      <c r="E23">
+        <v>-1047.413</v>
+      </c>
+      <c r="F23">
+        <v>1317.687</v>
+      </c>
+      <c r="G23">
+        <v>633.9</v>
+      </c>
+      <c r="H23">
+        <v>3909.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>368.3</v>
+      </c>
+      <c r="K23">
+        <v>257.4</v>
+      </c>
+      <c r="L23">
+        <v>110.9</v>
+      </c>
+      <c r="M23">
+        <v>314.6636556</v>
+      </c>
+      <c r="N23">
+        <v>-203.7636555999999</v>
+      </c>
+      <c r="O23">
+        <v>-44.82800423199998</v>
+      </c>
+      <c r="P23">
+        <v>-158.935651368</v>
+      </c>
+      <c r="Q23">
+        <v>98.46434863200002</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1124081872644378</v>
+      </c>
+      <c r="T23">
+        <v>1.244592431059369</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.07753675890365525</v>
+      </c>
+      <c r="W23">
+        <v>0.2202842219738071</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.352439813198433</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1370621545534053</v>
+      </c>
+      <c r="C24">
+        <v>2553.779882815912</v>
+      </c>
+      <c r="D24">
+        <v>3300.313882815912</v>
+      </c>
+      <c r="E24">
+        <v>-984.6659999999999</v>
+      </c>
+      <c r="F24">
+        <v>1380.434</v>
+      </c>
+      <c r="G24">
+        <v>633.9</v>
+      </c>
+      <c r="H24">
+        <v>3909.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>368.3</v>
+      </c>
+      <c r="K24">
+        <v>257.4</v>
+      </c>
+      <c r="L24">
+        <v>110.9</v>
+      </c>
+      <c r="M24">
+        <v>329.6476392</v>
+      </c>
+      <c r="N24">
+        <v>-218.7476392</v>
+      </c>
+      <c r="O24">
+        <v>-48.12448062399999</v>
+      </c>
+      <c r="P24">
+        <v>-170.623158576</v>
+      </c>
+      <c r="Q24">
+        <v>86.776841424</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1133518819729562</v>
+      </c>
+      <c r="T24">
+        <v>1.260548744278079</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.07401236077167091</v>
+      </c>
+      <c r="W24">
+        <v>0.221125848247725</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3364198216894132</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1390621545534053</v>
+      </c>
+      <c r="C25">
+        <v>2425.199191179891</v>
+      </c>
+      <c r="D25">
+        <v>3234.480191179891</v>
+      </c>
+      <c r="E25">
+        <v>-921.9189999999999</v>
+      </c>
+      <c r="F25">
+        <v>1443.181</v>
+      </c>
+      <c r="G25">
+        <v>633.9</v>
+      </c>
+      <c r="H25">
+        <v>3909.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>368.3</v>
+      </c>
+      <c r="K25">
+        <v>257.4</v>
+      </c>
+      <c r="L25">
+        <v>110.9</v>
+      </c>
+      <c r="M25">
+        <v>344.6316228</v>
+      </c>
+      <c r="N25">
+        <v>-233.7316228</v>
+      </c>
+      <c r="O25">
+        <v>-51.42095701599999</v>
+      </c>
+      <c r="P25">
+        <v>-182.310665784</v>
+      </c>
+      <c r="Q25">
+        <v>75.089334216</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1143200882323452</v>
+      </c>
+      <c r="T25">
+        <v>1.276919507190782</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.07079443204246783</v>
+      </c>
+      <c r="W25">
+        <v>0.2218942896282587</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3217928729203083</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1410621545534053</v>
+      </c>
+      <c r="C26">
+        <v>2299.193594579706</v>
+      </c>
+      <c r="D26">
+        <v>3171.221594579706</v>
+      </c>
+      <c r="E26">
+        <v>-859.172</v>
+      </c>
+      <c r="F26">
+        <v>1505.928</v>
+      </c>
+      <c r="G26">
+        <v>633.9</v>
+      </c>
+      <c r="H26">
+        <v>3909.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>368.3</v>
+      </c>
+      <c r="K26">
+        <v>257.4</v>
+      </c>
+      <c r="L26">
+        <v>110.9</v>
+      </c>
+      <c r="M26">
+        <v>359.6156064</v>
+      </c>
+      <c r="N26">
+        <v>-248.7156064</v>
+      </c>
+      <c r="O26">
+        <v>-54.71743340799998</v>
+      </c>
+      <c r="P26">
+        <v>-193.998172992</v>
+      </c>
+      <c r="Q26">
+        <v>63.401827008</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1153137736038235</v>
+      </c>
+      <c r="T26">
+        <v>1.293721079653818</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.06784466404069833</v>
+      </c>
+      <c r="W26">
+        <v>0.2225986942270813</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3083848365486288</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1430621545534053</v>
+      </c>
+      <c r="C27">
+        <v>2175.614903384309</v>
+      </c>
+      <c r="D27">
+        <v>3110.389903384309</v>
+      </c>
+      <c r="E27">
+        <v>-796.425</v>
+      </c>
+      <c r="F27">
+        <v>1568.675</v>
+      </c>
+      <c r="G27">
+        <v>633.9</v>
+      </c>
+      <c r="H27">
+        <v>3909.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>368.3</v>
+      </c>
+      <c r="K27">
+        <v>257.4</v>
+      </c>
+      <c r="L27">
+        <v>110.9</v>
+      </c>
+      <c r="M27">
+        <v>374.59959</v>
+      </c>
+      <c r="N27">
+        <v>-263.69959</v>
+      </c>
+      <c r="O27">
+        <v>-58.01390979999999</v>
+      </c>
+      <c r="P27">
+        <v>-205.6856802</v>
+      </c>
+      <c r="Q27">
+        <v>51.71431979999997</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1163339572518744</v>
+      </c>
+      <c r="T27">
+        <v>1.310970694049202</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.06513087747907038</v>
+      </c>
+      <c r="W27">
+        <v>0.223246746457998</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2960494430866837</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1450621545534053</v>
+      </c>
+      <c r="C28">
+        <v>2054.326084493915</v>
+      </c>
+      <c r="D28">
+        <v>3051.848084493914</v>
+      </c>
+      <c r="E28">
+        <v>-733.6779999999999</v>
+      </c>
+      <c r="F28">
+        <v>1631.422</v>
+      </c>
+      <c r="G28">
+        <v>633.9</v>
+      </c>
+      <c r="H28">
+        <v>3909.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>368.3</v>
+      </c>
+      <c r="K28">
+        <v>257.4</v>
+      </c>
+      <c r="L28">
+        <v>110.9</v>
+      </c>
+      <c r="M28">
+        <v>389.5835736</v>
+      </c>
+      <c r="N28">
+        <v>-278.6835736</v>
+      </c>
+      <c r="O28">
+        <v>-61.31038619199999</v>
+      </c>
+      <c r="P28">
+        <v>-217.373187408</v>
+      </c>
+      <c r="Q28">
+        <v>40.02681259199997</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1173817134309538</v>
+      </c>
+      <c r="T28">
+        <v>1.328686514239056</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.06262584372987538</v>
+      </c>
+      <c r="W28">
+        <v>0.2238449485173058</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2846629260448881</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1470621545534053</v>
+      </c>
+      <c r="C29">
+        <v>1935.200230829248</v>
+      </c>
+      <c r="D29">
+        <v>2995.469230829248</v>
+      </c>
+      <c r="E29">
+        <v>-670.9309999999998</v>
+      </c>
+      <c r="F29">
+        <v>1694.169</v>
+      </c>
+      <c r="G29">
+        <v>633.9</v>
+      </c>
+      <c r="H29">
+        <v>3909.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>368.3</v>
+      </c>
+      <c r="K29">
+        <v>257.4</v>
+      </c>
+      <c r="L29">
+        <v>110.9</v>
+      </c>
+      <c r="M29">
+        <v>404.5675572000001</v>
+      </c>
+      <c r="N29">
+        <v>-293.6675572</v>
+      </c>
+      <c r="O29">
+        <v>-64.606862584</v>
+      </c>
+      <c r="P29">
+        <v>-229.060694616</v>
+      </c>
+      <c r="Q29">
+        <v>28.33930538399994</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1184581752587751</v>
+      </c>
+      <c r="T29">
+        <v>1.346887699365619</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.06030636803617629</v>
+      </c>
+      <c r="W29">
+        <v>0.2243988393129611</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2741198547098922</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1490621545534054</v>
+      </c>
+      <c r="C30">
+        <v>1818.119642972893</v>
+      </c>
+      <c r="D30">
+        <v>2941.135642972893</v>
+      </c>
+      <c r="E30">
+        <v>-608.1839999999997</v>
+      </c>
+      <c r="F30">
+        <v>1756.916</v>
+      </c>
+      <c r="G30">
+        <v>633.9</v>
+      </c>
+      <c r="H30">
+        <v>3909.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>368.3</v>
+      </c>
+      <c r="K30">
+        <v>257.4</v>
+      </c>
+      <c r="L30">
+        <v>110.9</v>
+      </c>
+      <c r="M30">
+        <v>419.5515408000001</v>
+      </c>
+      <c r="N30">
+        <v>-308.6515408</v>
+      </c>
+      <c r="O30">
+        <v>-67.903338976</v>
+      </c>
+      <c r="P30">
+        <v>-240.748201824</v>
+      </c>
+      <c r="Q30">
+        <v>16.65179817599994</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1195645388040359</v>
+      </c>
+      <c r="T30">
+        <v>1.365594472967919</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.05815256917774142</v>
+      </c>
+      <c r="W30">
+        <v>0.2249131664803554</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2643298598988246</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1510621545534053</v>
+      </c>
+      <c r="C31">
+        <v>1702.975008976412</v>
+      </c>
+      <c r="D31">
+        <v>2888.738008976412</v>
+      </c>
+      <c r="E31">
+        <v>-545.4370000000001</v>
+      </c>
+      <c r="F31">
+        <v>1819.663</v>
+      </c>
+      <c r="G31">
+        <v>633.9</v>
+      </c>
+      <c r="H31">
+        <v>3909.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>368.3</v>
+      </c>
+      <c r="K31">
+        <v>257.4</v>
+      </c>
+      <c r="L31">
+        <v>110.9</v>
+      </c>
+      <c r="M31">
+        <v>434.5355244</v>
+      </c>
+      <c r="N31">
+        <v>-323.6355244</v>
+      </c>
+      <c r="O31">
+        <v>-71.19981536799997</v>
+      </c>
+      <c r="P31">
+        <v>-252.435709032</v>
+      </c>
+      <c r="Q31">
+        <v>4.964290968</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1207020675195857</v>
+      </c>
+      <c r="T31">
+        <v>1.384828197939298</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.05614730817161241</v>
+      </c>
+      <c r="W31">
+        <v>0.225392022808619</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2552150371436929</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1530621545534053</v>
+      </c>
+      <c r="C32">
+        <v>1589.664670305492</v>
+      </c>
+      <c r="D32">
+        <v>2838.174670305491</v>
+      </c>
+      <c r="E32">
+        <v>-482.6900000000001</v>
+      </c>
+      <c r="F32">
+        <v>1882.41</v>
+      </c>
+      <c r="G32">
+        <v>633.9</v>
+      </c>
+      <c r="H32">
+        <v>3909.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>368.3</v>
+      </c>
+      <c r="K32">
+        <v>257.4</v>
+      </c>
+      <c r="L32">
+        <v>110.9</v>
+      </c>
+      <c r="M32">
+        <v>449.519508</v>
+      </c>
+      <c r="N32">
+        <v>-338.6195079999999</v>
+      </c>
+      <c r="O32">
+        <v>-74.49629175999998</v>
+      </c>
+      <c r="P32">
+        <v>-264.12321624</v>
+      </c>
+      <c r="Q32">
+        <v>-6.723216239999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1218720970555798</v>
+      </c>
+      <c r="T32">
+        <v>1.40461145790986</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.05427573123255867</v>
+      </c>
+      <c r="W32">
+        <v>0.225838955381665</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2467078692389031</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1550621545534053</v>
+      </c>
+      <c r="C33">
+        <v>1478.093963550569</v>
+      </c>
+      <c r="D33">
+        <v>2789.350963550569</v>
+      </c>
+      <c r="E33">
+        <v>-419.943</v>
+      </c>
+      <c r="F33">
+        <v>1945.157</v>
+      </c>
+      <c r="G33">
+        <v>633.9</v>
+      </c>
+      <c r="H33">
+        <v>3909.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>368.3</v>
+      </c>
+      <c r="K33">
+        <v>257.4</v>
+      </c>
+      <c r="L33">
+        <v>110.9</v>
+      </c>
+      <c r="M33">
+        <v>464.5034916</v>
+      </c>
+      <c r="N33">
+        <v>-353.6034916</v>
+      </c>
+      <c r="O33">
+        <v>-77.79276815199999</v>
+      </c>
+      <c r="P33">
+        <v>-275.810723448</v>
+      </c>
+      <c r="Q33">
+        <v>-18.410723448</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1230760404911679</v>
+      </c>
+      <c r="T33">
+        <v>1.424968145705655</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.0525249011927987</v>
+      </c>
+      <c r="W33">
+        <v>0.2262570535951597</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2387495508763577</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1570621545534053</v>
+      </c>
+      <c r="C34">
+        <v>1368.174628933733</v>
+      </c>
+      <c r="D34">
+        <v>2742.178628933733</v>
+      </c>
+      <c r="E34">
+        <v>-357.1959999999999</v>
+      </c>
+      <c r="F34">
+        <v>2007.904</v>
+      </c>
+      <c r="G34">
+        <v>633.9</v>
+      </c>
+      <c r="H34">
+        <v>3909.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>368.3</v>
+      </c>
+      <c r="K34">
+        <v>257.4</v>
+      </c>
+      <c r="L34">
+        <v>110.9</v>
+      </c>
+      <c r="M34">
+        <v>479.4874752</v>
+      </c>
+      <c r="N34">
+        <v>-368.5874752</v>
+      </c>
+      <c r="O34">
+        <v>-81.08924454399998</v>
+      </c>
+      <c r="P34">
+        <v>-287.498230656</v>
+      </c>
+      <c r="Q34">
+        <v>-30.098230656</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1243153940278027</v>
+      </c>
+      <c r="T34">
+        <v>1.445923559613091</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05088349803052375</v>
+      </c>
+      <c r="W34">
+        <v>0.226649020670311</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2312886274114716</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1590621545534054</v>
+      </c>
+      <c r="C35">
+        <v>1259.82427783601</v>
+      </c>
+      <c r="D35">
+        <v>2696.57527783601</v>
+      </c>
+      <c r="E35">
+        <v>-294.4490000000001</v>
+      </c>
+      <c r="F35">
+        <v>2070.651</v>
+      </c>
+      <c r="G35">
+        <v>633.9</v>
+      </c>
+      <c r="H35">
+        <v>3909.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>368.3</v>
+      </c>
+      <c r="K35">
+        <v>257.4</v>
+      </c>
+      <c r="L35">
+        <v>110.9</v>
+      </c>
+      <c r="M35">
+        <v>494.4714588</v>
+      </c>
+      <c r="N35">
+        <v>-383.5714588</v>
+      </c>
+      <c r="O35">
+        <v>-84.38572093599998</v>
+      </c>
+      <c r="P35">
+        <v>-299.185737864</v>
+      </c>
+      <c r="Q35">
+        <v>-41.785737864</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1255917431923968</v>
+      </c>
+      <c r="T35">
+        <v>1.467504508264033</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.0493415738477806</v>
+      </c>
+      <c r="W35">
+        <v>0.22701723216515</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2242798811262755</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1610621545534053</v>
+      </c>
+      <c r="C36">
+        <v>1152.965912586707</v>
+      </c>
+      <c r="D36">
+        <v>2652.463912586707</v>
+      </c>
+      <c r="E36">
+        <v>-231.7019999999998</v>
+      </c>
+      <c r="F36">
+        <v>2133.398</v>
+      </c>
+      <c r="G36">
+        <v>633.9</v>
+      </c>
+      <c r="H36">
+        <v>3909.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>368.3</v>
+      </c>
+      <c r="K36">
+        <v>257.4</v>
+      </c>
+      <c r="L36">
+        <v>110.9</v>
+      </c>
+      <c r="M36">
+        <v>509.4554424</v>
+      </c>
+      <c r="N36">
+        <v>-398.5554424</v>
+      </c>
+      <c r="O36">
+        <v>-87.68219732799999</v>
+      </c>
+      <c r="P36">
+        <v>-310.873245072</v>
+      </c>
+      <c r="Q36">
+        <v>-53.47324507200005</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1269067696044028</v>
+      </c>
+      <c r="T36">
+        <v>1.489739425055912</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04789035108755176</v>
+      </c>
+      <c r="W36">
+        <v>0.2273637841602927</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2176834140343262</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1630621545534053</v>
+      </c>
+      <c r="C37">
+        <v>1047.527492626711</v>
+      </c>
+      <c r="D37">
+        <v>2609.772492626711</v>
+      </c>
+      <c r="E37">
+        <v>-168.9549999999999</v>
+      </c>
+      <c r="F37">
+        <v>2196.145</v>
+      </c>
+      <c r="G37">
+        <v>633.9</v>
+      </c>
+      <c r="H37">
+        <v>3909.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>368.3</v>
+      </c>
+      <c r="K37">
+        <v>257.4</v>
+      </c>
+      <c r="L37">
+        <v>110.9</v>
+      </c>
+      <c r="M37">
+        <v>524.439426</v>
+      </c>
+      <c r="N37">
+        <v>-413.539426</v>
+      </c>
+      <c r="O37">
+        <v>-90.97867371999999</v>
+      </c>
+      <c r="P37">
+        <v>-322.56075228</v>
+      </c>
+      <c r="Q37">
+        <v>-65.16075228</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1282622583675475</v>
+      </c>
+      <c r="T37">
+        <v>1.512658493133695</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.04652205534219313</v>
+      </c>
+      <c r="W37">
+        <v>0.2276905331842843</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2114638879190598</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1650621545534053</v>
+      </c>
+      <c r="C38">
+        <v>943.4415419037878</v>
+      </c>
+      <c r="D38">
+        <v>2568.433541903787</v>
+      </c>
+      <c r="E38">
+        <v>-106.2080000000001</v>
+      </c>
+      <c r="F38">
+        <v>2258.892</v>
+      </c>
+      <c r="G38">
+        <v>633.9</v>
+      </c>
+      <c r="H38">
+        <v>3909.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>368.3</v>
+      </c>
+      <c r="K38">
+        <v>257.4</v>
+      </c>
+      <c r="L38">
+        <v>110.9</v>
+      </c>
+      <c r="M38">
+        <v>539.4234096</v>
+      </c>
+      <c r="N38">
+        <v>-428.5234096</v>
+      </c>
+      <c r="O38">
+        <v>-94.27515011199998</v>
+      </c>
+      <c r="P38">
+        <v>-334.248259488</v>
+      </c>
+      <c r="Q38">
+        <v>-76.84825948800005</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1296601061545404</v>
+      </c>
+      <c r="T38">
+        <v>1.536293782088909</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04522977602713222</v>
+      </c>
+      <c r="W38">
+        <v>0.2279991294847208</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2055898910324192</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1670621545534053</v>
+      </c>
+      <c r="C39">
+        <v>840.6447929993378</v>
+      </c>
+      <c r="D39">
+        <v>2528.383792999338</v>
+      </c>
+      <c r="E39">
+        <v>-43.46099999999979</v>
+      </c>
+      <c r="F39">
+        <v>2321.639</v>
+      </c>
+      <c r="G39">
+        <v>633.9</v>
+      </c>
+      <c r="H39">
+        <v>3909.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>368.3</v>
+      </c>
+      <c r="K39">
+        <v>257.4</v>
+      </c>
+      <c r="L39">
+        <v>110.9</v>
+      </c>
+      <c r="M39">
+        <v>554.4073932</v>
+      </c>
+      <c r="N39">
+        <v>-443.5073932</v>
+      </c>
+      <c r="O39">
+        <v>-97.57162650399998</v>
+      </c>
+      <c r="P39">
+        <v>-345.935766696</v>
+      </c>
+      <c r="Q39">
+        <v>-88.535766696</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1311023300617553</v>
+      </c>
+      <c r="T39">
+        <v>1.560679397677622</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.04400734964802054</v>
+      </c>
+      <c r="W39">
+        <v>0.2282910449040527</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2000334074910025</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1690621545534053</v>
+      </c>
+      <c r="C40">
+        <v>739.0778640388853</v>
+      </c>
+      <c r="D40">
+        <v>2489.563864038885</v>
+      </c>
+      <c r="E40">
+        <v>19.28600000000006</v>
+      </c>
+      <c r="F40">
+        <v>2384.386</v>
+      </c>
+      <c r="G40">
+        <v>633.9</v>
+      </c>
+      <c r="H40">
+        <v>3909.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>368.3</v>
+      </c>
+      <c r="K40">
+        <v>257.4</v>
+      </c>
+      <c r="L40">
+        <v>110.9</v>
+      </c>
+      <c r="M40">
+        <v>569.3913768</v>
+      </c>
+      <c r="N40">
+        <v>-458.4913768</v>
+      </c>
+      <c r="O40">
+        <v>-100.868102896</v>
+      </c>
+      <c r="P40">
+        <v>-357.623273904</v>
+      </c>
+      <c r="Q40">
+        <v>-100.223273904</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1325910773208159</v>
+      </c>
+      <c r="T40">
+        <v>1.585851646027261</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.04284926149938842</v>
+      </c>
+      <c r="W40">
+        <v>0.2285675963539461</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1947693704517656</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1710621545534053</v>
+      </c>
+      <c r="C41">
+        <v>638.6849649161154</v>
+      </c>
+      <c r="D41">
+        <v>2451.917964916115</v>
+      </c>
+      <c r="E41">
+        <v>82.0329999999999</v>
+      </c>
+      <c r="F41">
+        <v>2447.133</v>
+      </c>
+      <c r="G41">
+        <v>633.9</v>
+      </c>
+      <c r="H41">
+        <v>3909.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>368.3</v>
+      </c>
+      <c r="K41">
+        <v>257.4</v>
+      </c>
+      <c r="L41">
+        <v>110.9</v>
+      </c>
+      <c r="M41">
+        <v>584.3753604</v>
+      </c>
+      <c r="N41">
+        <v>-473.4753603999999</v>
+      </c>
+      <c r="O41">
+        <v>-104.164579288</v>
+      </c>
+      <c r="P41">
+        <v>-369.310781112</v>
+      </c>
+      <c r="Q41">
+        <v>-111.910781112</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1341286359654194</v>
+      </c>
+      <c r="T41">
+        <v>1.611849213994921</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04175056248658359</v>
+      </c>
+      <c r="W41">
+        <v>0.2288299656782039</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1897752840299254</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1730621545534053</v>
+      </c>
+      <c r="C42">
+        <v>539.4136297738419</v>
+      </c>
+      <c r="D42">
+        <v>2415.393629773842</v>
+      </c>
+      <c r="E42">
+        <v>144.7800000000002</v>
+      </c>
+      <c r="F42">
+        <v>2509.88</v>
+      </c>
+      <c r="G42">
+        <v>633.9</v>
+      </c>
+      <c r="H42">
+        <v>3909.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>368.3</v>
+      </c>
+      <c r="K42">
+        <v>257.4</v>
+      </c>
+      <c r="L42">
+        <v>110.9</v>
+      </c>
+      <c r="M42">
+        <v>599.3593440000001</v>
+      </c>
+      <c r="N42">
+        <v>-488.459344</v>
+      </c>
+      <c r="O42">
+        <v>-107.46105568</v>
+      </c>
+      <c r="P42">
+        <v>-380.99828832</v>
+      </c>
+      <c r="Q42">
+        <v>-123.5982883200001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1357174465648431</v>
+      </c>
+      <c r="T42">
+        <v>1.638713367561503</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.040706798424419</v>
+      </c>
+      <c r="W42">
+        <v>0.2290792165362487</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1850309019291773</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1750621545534053</v>
+      </c>
+      <c r="C43">
+        <v>441.2144730441878</v>
+      </c>
+      <c r="D43">
+        <v>2379.941473044188</v>
+      </c>
+      <c r="E43">
+        <v>207.527</v>
+      </c>
+      <c r="F43">
+        <v>2572.627</v>
+      </c>
+      <c r="G43">
+        <v>633.9</v>
+      </c>
+      <c r="H43">
+        <v>3909.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>368.3</v>
+      </c>
+      <c r="K43">
+        <v>257.4</v>
+      </c>
+      <c r="L43">
+        <v>110.9</v>
+      </c>
+      <c r="M43">
+        <v>614.3433276000001</v>
+      </c>
+      <c r="N43">
+        <v>-503.4433276</v>
+      </c>
+      <c r="O43">
+        <v>-110.757532072</v>
+      </c>
+      <c r="P43">
+        <v>-392.685795528</v>
+      </c>
+      <c r="Q43">
+        <v>-135.2857955280001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1373601151506879</v>
+      </c>
+      <c r="T43">
+        <v>1.666488170401528</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03971394968235999</v>
+      </c>
+      <c r="W43">
+        <v>0.2293163088158524</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1805179531016363</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1770621545534053</v>
+      </c>
+      <c r="C44">
+        <v>344.0409666624305</v>
+      </c>
+      <c r="D44">
+        <v>2345.51496666243</v>
+      </c>
+      <c r="E44">
+        <v>270.2739999999999</v>
+      </c>
+      <c r="F44">
+        <v>2635.374</v>
+      </c>
+      <c r="G44">
+        <v>633.9</v>
+      </c>
+      <c r="H44">
+        <v>3909.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>368.3</v>
+      </c>
+      <c r="K44">
+        <v>257.4</v>
+      </c>
+      <c r="L44">
+        <v>110.9</v>
+      </c>
+      <c r="M44">
+        <v>629.3273111999999</v>
+      </c>
+      <c r="N44">
+        <v>-518.4273111999998</v>
+      </c>
+      <c r="O44">
+        <v>-114.0540084639999</v>
+      </c>
+      <c r="P44">
+        <v>-404.3733027359999</v>
+      </c>
+      <c r="Q44">
+        <v>-146.9733027359999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1390594274808721</v>
+      </c>
+      <c r="T44">
+        <v>1.695220725063624</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.03876837945182762</v>
+      </c>
+      <c r="W44">
+        <v>0.2295421109869036</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1762199065992166</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1790621545534054</v>
+      </c>
+      <c r="C45">
+        <v>247.8492363411178</v>
+      </c>
+      <c r="D45">
+        <v>2312.070236341118</v>
+      </c>
+      <c r="E45">
+        <v>333.0210000000002</v>
+      </c>
+      <c r="F45">
+        <v>2698.121</v>
+      </c>
+      <c r="G45">
+        <v>633.9</v>
+      </c>
+      <c r="H45">
+        <v>3909.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>368.3</v>
+      </c>
+      <c r="K45">
+        <v>257.4</v>
+      </c>
+      <c r="L45">
+        <v>110.9</v>
+      </c>
+      <c r="M45">
+        <v>644.3112948</v>
+      </c>
+      <c r="N45">
+        <v>-533.4112948</v>
+      </c>
+      <c r="O45">
+        <v>-117.350484856</v>
+      </c>
+      <c r="P45">
+        <v>-416.060809944</v>
+      </c>
+      <c r="Q45">
+        <v>-158.660809944</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.140818364805098</v>
+      </c>
+      <c r="T45">
+        <v>1.724961439538424</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03786678923201767</v>
+      </c>
+      <c r="W45">
+        <v>0.2297574107313942</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1721217692364441</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1810621545534054</v>
+      </c>
+      <c r="C46">
+        <v>152.5978750287327</v>
+      </c>
+      <c r="D46">
+        <v>2279.565875028733</v>
+      </c>
+      <c r="E46">
+        <v>395.768</v>
+      </c>
+      <c r="F46">
+        <v>2760.868</v>
+      </c>
+      <c r="G46">
+        <v>633.9</v>
+      </c>
+      <c r="H46">
+        <v>3909.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>368.3</v>
+      </c>
+      <c r="K46">
+        <v>257.4</v>
+      </c>
+      <c r="L46">
+        <v>110.9</v>
+      </c>
+      <c r="M46">
+        <v>659.2952784</v>
+      </c>
+      <c r="N46">
+        <v>-548.3952784000001</v>
+      </c>
+      <c r="O46">
+        <v>-120.646961248</v>
+      </c>
+      <c r="P46">
+        <v>-427.748317152</v>
+      </c>
+      <c r="Q46">
+        <v>-170.348317152</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1426401213194747</v>
+      </c>
+      <c r="T46">
+        <v>1.755764322387324</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03700618038583545</v>
+      </c>
+      <c r="W46">
+        <v>0.2299629241238625</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1682099108447065</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1830621545534054</v>
+      </c>
+      <c r="C47">
+        <v>58.24777188521466</v>
+      </c>
+      <c r="D47">
+        <v>2247.962771885214</v>
+      </c>
+      <c r="E47">
+        <v>458.5149999999999</v>
+      </c>
+      <c r="F47">
+        <v>2823.615</v>
+      </c>
+      <c r="G47">
+        <v>633.9</v>
+      </c>
+      <c r="H47">
+        <v>3909.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>368.3</v>
+      </c>
+      <c r="K47">
+        <v>257.4</v>
+      </c>
+      <c r="L47">
+        <v>110.9</v>
+      </c>
+      <c r="M47">
+        <v>674.279262</v>
+      </c>
+      <c r="N47">
+        <v>-563.3792619999999</v>
+      </c>
+      <c r="O47">
+        <v>-123.94343764</v>
+      </c>
+      <c r="P47">
+        <v>-439.43582436</v>
+      </c>
+      <c r="Q47">
+        <v>-182.03582436</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1445281235252833</v>
+      </c>
+      <c r="T47">
+        <v>1.787687310067094</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03618382082170578</v>
+      </c>
+      <c r="W47">
+        <v>0.2301593035877767</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1644719128259354</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1850621545534054</v>
+      </c>
+      <c r="C48">
+        <v>-35.23804471090534</v>
+      </c>
+      <c r="D48">
+        <v>2217.223955289095</v>
+      </c>
+      <c r="E48">
+        <v>521.2620000000002</v>
+      </c>
+      <c r="F48">
+        <v>2886.362</v>
+      </c>
+      <c r="G48">
+        <v>633.9</v>
+      </c>
+      <c r="H48">
+        <v>3909.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>368.3</v>
+      </c>
+      <c r="K48">
+        <v>257.4</v>
+      </c>
+      <c r="L48">
+        <v>110.9</v>
+      </c>
+      <c r="M48">
+        <v>689.2632456</v>
+      </c>
+      <c r="N48">
+        <v>-578.3632456</v>
+      </c>
+      <c r="O48">
+        <v>-127.239914032</v>
+      </c>
+      <c r="P48">
+        <v>-451.123331568</v>
+      </c>
+      <c r="Q48">
+        <v>-193.723331568</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1464860517387145</v>
+      </c>
+      <c r="T48">
+        <v>1.820792630623892</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03539721602123391</v>
+      </c>
+      <c r="W48">
+        <v>0.2303471448141294</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1608964364601541</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1870621545534053</v>
+      </c>
+      <c r="C49">
+        <v>-127.8945514487204</v>
+      </c>
+      <c r="D49">
+        <v>2187.314448551279</v>
+      </c>
+      <c r="E49">
+        <v>584.009</v>
+      </c>
+      <c r="F49">
+        <v>2949.109</v>
+      </c>
+      <c r="G49">
+        <v>633.9</v>
+      </c>
+      <c r="H49">
+        <v>3909.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>368.3</v>
+      </c>
+      <c r="K49">
+        <v>257.4</v>
+      </c>
+      <c r="L49">
+        <v>110.9</v>
+      </c>
+      <c r="M49">
+        <v>704.2472292</v>
+      </c>
+      <c r="N49">
+        <v>-593.3472291999999</v>
+      </c>
+      <c r="O49">
+        <v>-130.536390424</v>
+      </c>
+      <c r="P49">
+        <v>-462.810838776</v>
+      </c>
+      <c r="Q49">
+        <v>-205.410838776</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1485178640356714</v>
+      </c>
+      <c r="T49">
+        <v>1.855147208560192</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03464408376546298</v>
+      </c>
+      <c r="W49">
+        <v>0.2305269927968074</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1574731080248318</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1890621545534053</v>
+      </c>
+      <c r="C50">
+        <v>-219.7548628484165</v>
+      </c>
+      <c r="D50">
+        <v>2158.201137151583</v>
+      </c>
+      <c r="E50">
+        <v>646.7559999999999</v>
+      </c>
+      <c r="F50">
+        <v>3011.856</v>
+      </c>
+      <c r="G50">
+        <v>633.9</v>
+      </c>
+      <c r="H50">
+        <v>3909.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>368.3</v>
+      </c>
+      <c r="K50">
+        <v>257.4</v>
+      </c>
+      <c r="L50">
+        <v>110.9</v>
+      </c>
+      <c r="M50">
+        <v>719.2312128</v>
+      </c>
+      <c r="N50">
+        <v>-608.3312128</v>
+      </c>
+      <c r="O50">
+        <v>-133.832866816</v>
+      </c>
+      <c r="P50">
+        <v>-474.498345984</v>
+      </c>
+      <c r="Q50">
+        <v>-217.098345984</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1506278229594343</v>
+      </c>
+      <c r="T50">
+        <v>1.890823116417119</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03392233202034917</v>
+      </c>
+      <c r="W50">
+        <v>0.2306993471135406</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1541924182743143</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1910621545534053</v>
+      </c>
+      <c r="C51">
+        <v>-310.8503535614473</v>
+      </c>
+      <c r="D51">
+        <v>2129.852646438553</v>
+      </c>
+      <c r="E51">
+        <v>709.5030000000002</v>
+      </c>
+      <c r="F51">
+        <v>3074.603</v>
+      </c>
+      <c r="G51">
+        <v>633.9</v>
+      </c>
+      <c r="H51">
+        <v>3909.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>368.3</v>
+      </c>
+      <c r="K51">
+        <v>257.4</v>
+      </c>
+      <c r="L51">
+        <v>110.9</v>
+      </c>
+      <c r="M51">
+        <v>734.2151964000001</v>
+      </c>
+      <c r="N51">
+        <v>-623.3151964000001</v>
+      </c>
+      <c r="O51">
+        <v>-137.129343208</v>
+      </c>
+      <c r="P51">
+        <v>-486.1858531920001</v>
+      </c>
+      <c r="Q51">
+        <v>-228.7858531920001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1528205253704036</v>
+      </c>
+      <c r="T51">
+        <v>1.927898079484121</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03323003953013796</v>
+      </c>
+      <c r="W51">
+        <v>0.2308646665602031</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1510456342278997</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1930621545534053</v>
+      </c>
+      <c r="C52">
+        <v>-401.210771157027</v>
+      </c>
+      <c r="D52">
+        <v>2102.239228842973</v>
+      </c>
+      <c r="E52">
+        <v>772.25</v>
+      </c>
+      <c r="F52">
+        <v>3137.35</v>
+      </c>
+      <c r="G52">
+        <v>633.9</v>
+      </c>
+      <c r="H52">
+        <v>3909.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>368.3</v>
+      </c>
+      <c r="K52">
+        <v>257.4</v>
+      </c>
+      <c r="L52">
+        <v>110.9</v>
+      </c>
+      <c r="M52">
+        <v>749.1991800000001</v>
+      </c>
+      <c r="N52">
+        <v>-638.29918</v>
+      </c>
+      <c r="O52">
+        <v>-140.4258196</v>
+      </c>
+      <c r="P52">
+        <v>-497.8733604</v>
+      </c>
+      <c r="Q52">
+        <v>-240.4733604</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1551009358778117</v>
+      </c>
+      <c r="T52">
+        <v>1.966456041073803</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03256543873953519</v>
+      </c>
+      <c r="W52">
+        <v>0.231023373228999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1480247215433419</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1950621545534053</v>
+      </c>
+      <c r="C53">
+        <v>-490.864340247299</v>
+      </c>
+      <c r="D53">
+        <v>2075.332659752701</v>
+      </c>
+      <c r="E53">
+        <v>834.9969999999998</v>
+      </c>
+      <c r="F53">
+        <v>3200.097</v>
+      </c>
+      <c r="G53">
+        <v>633.9</v>
+      </c>
+      <c r="H53">
+        <v>3909.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>368.3</v>
+      </c>
+      <c r="K53">
+        <v>257.4</v>
+      </c>
+      <c r="L53">
+        <v>110.9</v>
+      </c>
+      <c r="M53">
+        <v>764.1831635999999</v>
+      </c>
+      <c r="N53">
+        <v>-653.2831635999999</v>
+      </c>
+      <c r="O53">
+        <v>-143.7222959919999</v>
+      </c>
+      <c r="P53">
+        <v>-509.5608676079999</v>
+      </c>
+      <c r="Q53">
+        <v>-252.1608676079999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1574744243651139</v>
+      </c>
+      <c r="T53">
+        <v>2.006587797014085</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03192690072503451</v>
+      </c>
+      <c r="W53">
+        <v>0.2311758561068618</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1451222760228842</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1970621545534053</v>
+      </c>
+      <c r="C54">
+        <v>-579.8378587173534</v>
+      </c>
+      <c r="D54">
+        <v>2049.106141282647</v>
+      </c>
+      <c r="E54">
+        <v>897.7440000000001</v>
+      </c>
+      <c r="F54">
+        <v>3262.844</v>
+      </c>
+      <c r="G54">
+        <v>633.9</v>
+      </c>
+      <c r="H54">
+        <v>3909.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>368.3</v>
+      </c>
+      <c r="K54">
+        <v>257.4</v>
+      </c>
+      <c r="L54">
+        <v>110.9</v>
+      </c>
+      <c r="M54">
+        <v>779.1671472</v>
+      </c>
+      <c r="N54">
+        <v>-668.2671472</v>
+      </c>
+      <c r="O54">
+        <v>-147.018772384</v>
+      </c>
+      <c r="P54">
+        <v>-521.248374816</v>
+      </c>
+      <c r="Q54">
+        <v>-263.848374816</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1599468082060538</v>
+      </c>
+      <c r="T54">
+        <v>2.048391709451879</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03131292186493769</v>
+      </c>
+      <c r="W54">
+        <v>0.2313224742586529</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1423314630224441</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1990621545534054</v>
+      </c>
+      <c r="C55">
+        <v>-668.1567867498052</v>
+      </c>
+      <c r="D55">
+        <v>2023.534213250195</v>
+      </c>
+      <c r="E55">
+        <v>960.491</v>
+      </c>
+      <c r="F55">
+        <v>3325.591</v>
+      </c>
+      <c r="G55">
+        <v>633.9</v>
+      </c>
+      <c r="H55">
+        <v>3909.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>368.3</v>
+      </c>
+      <c r="K55">
+        <v>257.4</v>
+      </c>
+      <c r="L55">
+        <v>110.9</v>
+      </c>
+      <c r="M55">
+        <v>794.1511308</v>
+      </c>
+      <c r="N55">
+        <v>-683.2511308000001</v>
+      </c>
+      <c r="O55">
+        <v>-150.315248776</v>
+      </c>
+      <c r="P55">
+        <v>-532.9358820240001</v>
+      </c>
+      <c r="Q55">
+        <v>-275.5358820240001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1625243998700124</v>
+      </c>
+      <c r="T55">
+        <v>2.091974511780642</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03072211201842943</v>
+      </c>
+      <c r="W55">
+        <v>0.2314635596499991</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1396459637201337</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2010621545534053</v>
+      </c>
+      <c r="C56">
+        <v>-755.8453292656127</v>
+      </c>
+      <c r="D56">
+        <v>1998.592670734387</v>
+      </c>
+      <c r="E56">
+        <v>1023.238</v>
+      </c>
+      <c r="F56">
+        <v>3388.338</v>
+      </c>
+      <c r="G56">
+        <v>633.9</v>
+      </c>
+      <c r="H56">
+        <v>3909.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>368.3</v>
+      </c>
+      <c r="K56">
+        <v>257.4</v>
+      </c>
+      <c r="L56">
+        <v>110.9</v>
+      </c>
+      <c r="M56">
+        <v>809.1351144000001</v>
+      </c>
+      <c r="N56">
+        <v>-698.2351144000002</v>
+      </c>
+      <c r="O56">
+        <v>-153.611725168</v>
+      </c>
+      <c r="P56">
+        <v>-544.6233892320001</v>
+      </c>
+      <c r="Q56">
+        <v>-287.2233892320002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1652140607367518</v>
+      </c>
+      <c r="T56">
+        <v>2.137452218558482</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03015318401808815</v>
+      </c>
+      <c r="W56">
+        <v>0.2315994196564805</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1370599273549461</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2030621545534054</v>
+      </c>
+      <c r="C57">
+        <v>-842.9265123422706</v>
+      </c>
+      <c r="D57">
+        <v>1974.258487657729</v>
+      </c>
+      <c r="E57">
+        <v>1085.985</v>
+      </c>
+      <c r="F57">
+        <v>3451.085</v>
+      </c>
+      <c r="G57">
+        <v>633.9</v>
+      </c>
+      <c r="H57">
+        <v>3909.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>368.3</v>
+      </c>
+      <c r="K57">
+        <v>257.4</v>
+      </c>
+      <c r="L57">
+        <v>110.9</v>
+      </c>
+      <c r="M57">
+        <v>824.119098</v>
+      </c>
+      <c r="N57">
+        <v>-713.219098</v>
+      </c>
+      <c r="O57">
+        <v>-156.90820156</v>
+      </c>
+      <c r="P57">
+        <v>-556.3108964400001</v>
+      </c>
+      <c r="Q57">
+        <v>-298.9108964400001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1680232620864574</v>
+      </c>
+      <c r="T57">
+        <v>2.184951156748671</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.02960494430866836</v>
+      </c>
+      <c r="W57">
+        <v>0.23173033929909</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1345679286757653</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2050621545534053</v>
+      </c>
+      <c r="C58">
+        <v>-929.4222541164977</v>
+      </c>
+      <c r="D58">
+        <v>1950.509745883503</v>
+      </c>
+      <c r="E58">
+        <v>1148.732</v>
+      </c>
+      <c r="F58">
+        <v>3513.832</v>
+      </c>
+      <c r="G58">
+        <v>633.9</v>
+      </c>
+      <c r="H58">
+        <v>3909.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>368.3</v>
+      </c>
+      <c r="K58">
+        <v>257.4</v>
+      </c>
+      <c r="L58">
+        <v>110.9</v>
+      </c>
+      <c r="M58">
+        <v>839.1030816000001</v>
+      </c>
+      <c r="N58">
+        <v>-728.2030816000001</v>
+      </c>
+      <c r="O58">
+        <v>-160.204677952</v>
+      </c>
+      <c r="P58">
+        <v>-567.9984036480001</v>
+      </c>
+      <c r="Q58">
+        <v>-310.5984036480002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1709601544066042</v>
+      </c>
+      <c r="T58">
+        <v>2.234609137583868</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02907628458887071</v>
+      </c>
+      <c r="W58">
+        <v>0.2318565832401777</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1321649299494123</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2070621545534054</v>
+      </c>
+      <c r="C59">
+        <v>-1015.353430630349</v>
+      </c>
+      <c r="D59">
+        <v>1927.325569369651</v>
+      </c>
+      <c r="E59">
+        <v>1211.479</v>
+      </c>
+      <c r="F59">
+        <v>3576.579</v>
+      </c>
+      <c r="G59">
+        <v>633.9</v>
+      </c>
+      <c r="H59">
+        <v>3909.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>368.3</v>
+      </c>
+      <c r="K59">
+        <v>257.4</v>
+      </c>
+      <c r="L59">
+        <v>110.9</v>
+      </c>
+      <c r="M59">
+        <v>854.0870652000001</v>
+      </c>
+      <c r="N59">
+        <v>-743.1870652</v>
+      </c>
+      <c r="O59">
+        <v>-163.501154344</v>
+      </c>
+      <c r="P59">
+        <v>-579.685910856</v>
+      </c>
+      <c r="Q59">
+        <v>-322.285910856</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1740336463695485</v>
+      </c>
+      <c r="T59">
+        <v>2.286576791946283</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02856617433292561</v>
+      </c>
+      <c r="W59">
+        <v>0.2319783975692974</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1298462469678437</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2090621545534053</v>
+      </c>
+      <c r="C60">
+        <v>-1100.739937036513</v>
+      </c>
+      <c r="D60">
+        <v>1904.686062963487</v>
+      </c>
+      <c r="E60">
+        <v>1274.226</v>
+      </c>
+      <c r="F60">
+        <v>3639.326</v>
+      </c>
+      <c r="G60">
+        <v>633.9</v>
+      </c>
+      <c r="H60">
+        <v>3909.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>368.3</v>
+      </c>
+      <c r="K60">
+        <v>257.4</v>
+      </c>
+      <c r="L60">
+        <v>110.9</v>
+      </c>
+      <c r="M60">
+        <v>869.0710488</v>
+      </c>
+      <c r="N60">
+        <v>-758.1710487999999</v>
+      </c>
+      <c r="O60">
+        <v>-166.7976307359999</v>
+      </c>
+      <c r="P60">
+        <v>-591.3734180639999</v>
+      </c>
+      <c r="Q60">
+        <v>-333.9734180639999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1772534950926329</v>
+      </c>
+      <c r="T60">
+        <v>2.341019096516432</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02807365408580621</v>
+      </c>
+      <c r="W60">
+        <v>0.2320960114043095</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1276075185718465</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2110621545534053</v>
+      </c>
+      <c r="C61">
+        <v>-1185.600744539983</v>
+      </c>
+      <c r="D61">
+        <v>1882.572255460017</v>
+      </c>
+      <c r="E61">
+        <v>1336.973</v>
+      </c>
+      <c r="F61">
+        <v>3702.073</v>
+      </c>
+      <c r="G61">
+        <v>633.9</v>
+      </c>
+      <c r="H61">
+        <v>3909.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>368.3</v>
+      </c>
+      <c r="K61">
+        <v>257.4</v>
+      </c>
+      <c r="L61">
+        <v>110.9</v>
+      </c>
+      <c r="M61">
+        <v>884.0550324</v>
+      </c>
+      <c r="N61">
+        <v>-773.1550324</v>
+      </c>
+      <c r="O61">
+        <v>-170.094107128</v>
+      </c>
+      <c r="P61">
+        <v>-603.0609252720001</v>
+      </c>
+      <c r="Q61">
+        <v>-345.6609252720001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1806304096070874</v>
+      </c>
+      <c r="T61">
+        <v>2.398117123260735</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02759782944028407</v>
+      </c>
+      <c r="W61">
+        <v>0.2322096383296602</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1254446792740185</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2130621545534054</v>
+      </c>
+      <c r="C62">
+        <v>-1269.953953418608</v>
+      </c>
+      <c r="D62">
+        <v>1860.966046581392</v>
+      </c>
+      <c r="E62">
+        <v>1399.72</v>
+      </c>
+      <c r="F62">
+        <v>3764.82</v>
+      </c>
+      <c r="G62">
+        <v>633.9</v>
+      </c>
+      <c r="H62">
+        <v>3909.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>368.3</v>
+      </c>
+      <c r="K62">
+        <v>257.4</v>
+      </c>
+      <c r="L62">
+        <v>110.9</v>
+      </c>
+      <c r="M62">
+        <v>899.0390159999999</v>
+      </c>
+      <c r="N62">
+        <v>-788.1390159999999</v>
+      </c>
+      <c r="O62">
+        <v>-173.39058352</v>
+      </c>
+      <c r="P62">
+        <v>-614.7484324799999</v>
+      </c>
+      <c r="Q62">
+        <v>-357.3484324799999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1841761698472646</v>
+      </c>
+      <c r="T62">
+        <v>2.458070051342254</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02713786561627933</v>
+      </c>
+      <c r="W62">
+        <v>0.2323194776908325</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1233539346194515</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2150621545534054</v>
+      </c>
+      <c r="C63">
+        <v>-1353.816842433996</v>
+      </c>
+      <c r="D63">
+        <v>1839.850157566004</v>
+      </c>
+      <c r="E63">
+        <v>1462.467</v>
+      </c>
+      <c r="F63">
+        <v>3827.567</v>
+      </c>
+      <c r="G63">
+        <v>633.9</v>
+      </c>
+      <c r="H63">
+        <v>3909.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>368.3</v>
+      </c>
+      <c r="K63">
+        <v>257.4</v>
+      </c>
+      <c r="L63">
+        <v>110.9</v>
+      </c>
+      <c r="M63">
+        <v>914.0229996</v>
+      </c>
+      <c r="N63">
+        <v>-803.1229996</v>
+      </c>
+      <c r="O63">
+        <v>-176.687059912</v>
+      </c>
+      <c r="P63">
+        <v>-626.435939688</v>
+      </c>
+      <c r="Q63">
+        <v>-369.035939688</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1879037639459124</v>
+      </c>
+      <c r="T63">
+        <v>2.521097488556158</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.0266929825733895</v>
+      </c>
+      <c r="W63">
+        <v>0.2324257157614746</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1213317389699524</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2170621545534053</v>
+      </c>
+      <c r="C64">
+        <v>-1437.205914916237</v>
+      </c>
+      <c r="D64">
+        <v>1819.208085083763</v>
+      </c>
+      <c r="E64">
+        <v>1525.214</v>
+      </c>
+      <c r="F64">
+        <v>3890.314</v>
+      </c>
+      <c r="G64">
+        <v>633.9</v>
+      </c>
+      <c r="H64">
+        <v>3909.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>368.3</v>
+      </c>
+      <c r="K64">
+        <v>257.4</v>
+      </c>
+      <c r="L64">
+        <v>110.9</v>
+      </c>
+      <c r="M64">
+        <v>929.0069832</v>
+      </c>
+      <c r="N64">
+        <v>-818.1069832000001</v>
+      </c>
+      <c r="O64">
+        <v>-179.983536304</v>
+      </c>
+      <c r="P64">
+        <v>-638.1234468960001</v>
+      </c>
+      <c r="Q64">
+        <v>-380.7234468960002</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1918275472076469</v>
+      </c>
+      <c r="T64">
+        <v>2.587442159307636</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02626245059639935</v>
+      </c>
+      <c r="W64">
+        <v>0.2325285267975798</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1193747754381789</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2190621545534053</v>
+      </c>
+      <c r="C65">
+        <v>-1520.136941780786</v>
+      </c>
+      <c r="D65">
+        <v>1799.024058219213</v>
+      </c>
+      <c r="E65">
+        <v>1587.961</v>
+      </c>
+      <c r="F65">
+        <v>3953.061</v>
+      </c>
+      <c r="G65">
+        <v>633.9</v>
+      </c>
+      <c r="H65">
+        <v>3909.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>368.3</v>
+      </c>
+      <c r="K65">
+        <v>257.4</v>
+      </c>
+      <c r="L65">
+        <v>110.9</v>
+      </c>
+      <c r="M65">
+        <v>943.9909668</v>
+      </c>
+      <c r="N65">
+        <v>-833.0909667999999</v>
+      </c>
+      <c r="O65">
+        <v>-183.280012696</v>
+      </c>
+      <c r="P65">
+        <v>-649.810954104</v>
+      </c>
+      <c r="Q65">
+        <v>-392.410954104</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1959634268619077</v>
+      </c>
+      <c r="T65">
+        <v>2.657373028478113</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02584558630121841</v>
+      </c>
+      <c r="W65">
+        <v>0.2326280739912691</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1174799377328111</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2210621545534053</v>
+      </c>
+      <c r="C66">
+        <v>-1602.625001713139</v>
+      </c>
+      <c r="D66">
+        <v>1779.282998286861</v>
+      </c>
+      <c r="E66">
+        <v>1650.708</v>
+      </c>
+      <c r="F66">
+        <v>4015.808</v>
+      </c>
+      <c r="G66">
+        <v>633.9</v>
+      </c>
+      <c r="H66">
+        <v>3909.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>368.3</v>
+      </c>
+      <c r="K66">
+        <v>257.4</v>
+      </c>
+      <c r="L66">
+        <v>110.9</v>
+      </c>
+      <c r="M66">
+        <v>958.9749504</v>
+      </c>
+      <c r="N66">
+        <v>-848.0749504</v>
+      </c>
+      <c r="O66">
+        <v>-186.576489088</v>
+      </c>
+      <c r="P66">
+        <v>-661.498461312</v>
+      </c>
+      <c r="Q66">
+        <v>-404.098461312</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2003290776080718</v>
+      </c>
+      <c r="T66">
+        <v>2.731188945935838</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02544174901526187</v>
+      </c>
+      <c r="W66">
+        <v>0.2327245103351555</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1156443137057357</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2230621545534053</v>
+      </c>
+      <c r="C67">
+        <v>-1684.684518736499</v>
+      </c>
+      <c r="D67">
+        <v>1759.970481263501</v>
+      </c>
+      <c r="E67">
+        <v>1713.455</v>
+      </c>
+      <c r="F67">
+        <v>4078.555</v>
+      </c>
+      <c r="G67">
+        <v>633.9</v>
+      </c>
+      <c r="H67">
+        <v>3909.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>368.3</v>
+      </c>
+      <c r="K67">
+        <v>257.4</v>
+      </c>
+      <c r="L67">
+        <v>110.9</v>
+      </c>
+      <c r="M67">
+        <v>973.958934</v>
+      </c>
+      <c r="N67">
+        <v>-863.0589339999999</v>
+      </c>
+      <c r="O67">
+        <v>-189.8729654799999</v>
+      </c>
+      <c r="P67">
+        <v>-673.18596852</v>
+      </c>
+      <c r="Q67">
+        <v>-415.78596852</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2049441941111595</v>
+      </c>
+      <c r="T67">
+        <v>2.809222915819719</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02505033749195015</v>
+      </c>
+      <c r="W67">
+        <v>0.2328179794069223</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1138651704179553</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2250621545534053</v>
+      </c>
+      <c r="C68">
+        <v>-1766.329297359143</v>
+      </c>
+      <c r="D68">
+        <v>1741.072702640856</v>
+      </c>
+      <c r="E68">
+        <v>1776.202</v>
+      </c>
+      <c r="F68">
+        <v>4141.302</v>
+      </c>
+      <c r="G68">
+        <v>633.9</v>
+      </c>
+      <c r="H68">
+        <v>3909.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>368.3</v>
+      </c>
+      <c r="K68">
+        <v>257.4</v>
+      </c>
+      <c r="L68">
+        <v>110.9</v>
+      </c>
+      <c r="M68">
+        <v>988.9429176</v>
+      </c>
+      <c r="N68">
+        <v>-878.0429176</v>
+      </c>
+      <c r="O68">
+        <v>-193.169441872</v>
+      </c>
+      <c r="P68">
+        <v>-684.873475728</v>
+      </c>
+      <c r="Q68">
+        <v>-427.473475728</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2098307880556054</v>
+      </c>
+      <c r="T68">
+        <v>2.891847119226182</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0246707869238903</v>
+      </c>
+      <c r="W68">
+        <v>0.232908616082575</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1121399405631377</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2270621545534053</v>
+      </c>
+      <c r="C69">
+        <v>-1847.572555481452</v>
+      </c>
+      <c r="D69">
+        <v>1722.576444518548</v>
+      </c>
+      <c r="E69">
+        <v>1838.949</v>
+      </c>
+      <c r="F69">
+        <v>4204.049</v>
+      </c>
+      <c r="G69">
+        <v>633.9</v>
+      </c>
+      <c r="H69">
+        <v>3909.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>368.3</v>
+      </c>
+      <c r="K69">
+        <v>257.4</v>
+      </c>
+      <c r="L69">
+        <v>110.9</v>
+      </c>
+      <c r="M69">
+        <v>1003.9269012</v>
+      </c>
+      <c r="N69">
+        <v>-893.0269012000001</v>
+      </c>
+      <c r="O69">
+        <v>-196.465918264</v>
+      </c>
+      <c r="P69">
+        <v>-696.5609829360001</v>
+      </c>
+      <c r="Q69">
+        <v>-439.1609829360001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2150135392088056</v>
+      </c>
+      <c r="T69">
+        <v>2.979478850111824</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02430256622353373</v>
+      </c>
+      <c r="W69">
+        <v>0.2329965471858201</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1104662101069714</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2290621545534054</v>
+      </c>
+      <c r="C70">
+        <v>-1928.426955227471</v>
+      </c>
+      <c r="D70">
+        <v>1704.46904477253</v>
+      </c>
+      <c r="E70">
+        <v>1901.696</v>
+      </c>
+      <c r="F70">
+        <v>4266.796</v>
+      </c>
+      <c r="G70">
+        <v>633.9</v>
+      </c>
+      <c r="H70">
+        <v>3909.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>368.3</v>
+      </c>
+      <c r="K70">
+        <v>257.4</v>
+      </c>
+      <c r="L70">
+        <v>110.9</v>
+      </c>
+      <c r="M70">
+        <v>1018.9108848</v>
+      </c>
+      <c r="N70">
+        <v>-908.0108848</v>
+      </c>
+      <c r="O70">
+        <v>-199.762394656</v>
+      </c>
+      <c r="P70">
+        <v>-708.248490144</v>
+      </c>
+      <c r="Q70">
+        <v>-450.848490144</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2205202123090808</v>
+      </c>
+      <c r="T70">
+        <v>3.072587564177818</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02394517554377588</v>
+      </c>
+      <c r="W70">
+        <v>0.2330818920801463</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1088417070171631</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2310621545534053</v>
+      </c>
+      <c r="C71">
+        <v>-2008.904631852121</v>
+      </c>
+      <c r="D71">
+        <v>1686.738368147879</v>
+      </c>
+      <c r="E71">
+        <v>1964.443000000001</v>
+      </c>
+      <c r="F71">
+        <v>4329.543000000001</v>
+      </c>
+      <c r="G71">
+        <v>633.9</v>
+      </c>
+      <c r="H71">
+        <v>3909.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>368.3</v>
+      </c>
+      <c r="K71">
+        <v>257.4</v>
+      </c>
+      <c r="L71">
+        <v>110.9</v>
+      </c>
+      <c r="M71">
+        <v>1033.8948684</v>
+      </c>
+      <c r="N71">
+        <v>-922.9948684000001</v>
+      </c>
+      <c r="O71">
+        <v>-203.058871048</v>
+      </c>
+      <c r="P71">
+        <v>-719.9359973520001</v>
+      </c>
+      <c r="Q71">
+        <v>-462.5359973520001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2263821546416318</v>
+      </c>
+      <c r="T71">
+        <v>3.171703292054522</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02359814401415594</v>
+      </c>
+      <c r="W71">
+        <v>0.2331647632094196</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1072642909734361</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2330621545534053</v>
+      </c>
+      <c r="C72">
+        <v>-2089.01722086276</v>
+      </c>
+      <c r="D72">
+        <v>1669.37277913724</v>
+      </c>
+      <c r="E72">
+        <v>2027.19</v>
+      </c>
+      <c r="F72">
+        <v>4392.29</v>
+      </c>
+      <c r="G72">
+        <v>633.9</v>
+      </c>
+      <c r="H72">
+        <v>3909.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>368.3</v>
+      </c>
+      <c r="K72">
+        <v>257.4</v>
+      </c>
+      <c r="L72">
+        <v>110.9</v>
+      </c>
+      <c r="M72">
+        <v>1048.878852</v>
+      </c>
+      <c r="N72">
+        <v>-937.978852</v>
+      </c>
+      <c r="O72">
+        <v>-206.35534744</v>
+      </c>
+      <c r="P72">
+        <v>-731.62350456</v>
+      </c>
+      <c r="Q72">
+        <v>-474.22350456</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2326348931296862</v>
+      </c>
+      <c r="T72">
+        <v>3.277426735123006</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02326102767109657</v>
+      </c>
+      <c r="W72">
+        <v>0.2332452665921421</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1057319439595299</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2350621545534053</v>
+      </c>
+      <c r="C73">
+        <v>-2168.775883482442</v>
+      </c>
+      <c r="D73">
+        <v>1652.361116517558</v>
+      </c>
+      <c r="E73">
+        <v>2089.936999999999</v>
+      </c>
+      <c r="F73">
+        <v>4455.036999999999</v>
+      </c>
+      <c r="G73">
+        <v>633.9</v>
+      </c>
+      <c r="H73">
+        <v>3909.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>368.3</v>
+      </c>
+      <c r="K73">
+        <v>257.4</v>
+      </c>
+      <c r="L73">
+        <v>110.9</v>
+      </c>
+      <c r="M73">
+        <v>1063.8628356</v>
+      </c>
+      <c r="N73">
+        <v>-952.9628355999998</v>
+      </c>
+      <c r="O73">
+        <v>-209.6518238319999</v>
+      </c>
+      <c r="P73">
+        <v>-743.3110117679998</v>
+      </c>
+      <c r="Q73">
+        <v>-485.9110117679999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2393188549617442</v>
+      </c>
+      <c r="T73">
+        <v>3.390441450127247</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02293340756305296</v>
+      </c>
+      <c r="W73">
+        <v>0.233323502273943</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1042427616502408</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2370621545534053</v>
+      </c>
+      <c r="C74">
+        <v>-2248.191330572</v>
+      </c>
+      <c r="D74">
+        <v>1635.692669428</v>
+      </c>
+      <c r="E74">
+        <v>2152.684</v>
+      </c>
+      <c r="F74">
+        <v>4517.784</v>
+      </c>
+      <c r="G74">
+        <v>633.9</v>
+      </c>
+      <c r="H74">
+        <v>3909.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>368.3</v>
+      </c>
+      <c r="K74">
+        <v>257.4</v>
+      </c>
+      <c r="L74">
+        <v>110.9</v>
+      </c>
+      <c r="M74">
+        <v>1078.8468192</v>
+      </c>
+      <c r="N74">
+        <v>-967.9468191999999</v>
+      </c>
+      <c r="O74">
+        <v>-212.948300224</v>
+      </c>
+      <c r="P74">
+        <v>-754.998518976</v>
+      </c>
+      <c r="Q74">
+        <v>-497.598518976</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2464802426389494</v>
+      </c>
+      <c r="T74">
+        <v>3.511528644774649</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02261488801356611</v>
+      </c>
+      <c r="W74">
+        <v>0.2333995647423604</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1027949455162096</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2390621545534053</v>
+      </c>
+      <c r="C75">
+        <v>-2327.273845118677</v>
+      </c>
+      <c r="D75">
+        <v>1619.357154881323</v>
+      </c>
+      <c r="E75">
+        <v>2215.431</v>
+      </c>
+      <c r="F75">
+        <v>4580.531</v>
+      </c>
+      <c r="G75">
+        <v>633.9</v>
+      </c>
+      <c r="H75">
+        <v>3909.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>368.3</v>
+      </c>
+      <c r="K75">
+        <v>257.4</v>
+      </c>
+      <c r="L75">
+        <v>110.9</v>
+      </c>
+      <c r="M75">
+        <v>1093.8308028</v>
+      </c>
+      <c r="N75">
+        <v>-982.9308028</v>
+      </c>
+      <c r="O75">
+        <v>-216.244776616</v>
+      </c>
+      <c r="P75">
+        <v>-766.6860261840001</v>
+      </c>
+      <c r="Q75">
+        <v>-509.2860261840001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.254172103477429</v>
+      </c>
+      <c r="T75">
+        <v>3.641585261247783</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0223050950270789</v>
+      </c>
+      <c r="W75">
+        <v>0.2334735433075336</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1013867955776314</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2410621545534054</v>
+      </c>
+      <c r="C76">
+        <v>-2406.033303390536</v>
+      </c>
+      <c r="D76">
+        <v>1603.344696609464</v>
+      </c>
+      <c r="E76">
+        <v>2278.178</v>
+      </c>
+      <c r="F76">
+        <v>4643.278</v>
+      </c>
+      <c r="G76">
+        <v>633.9</v>
+      </c>
+      <c r="H76">
+        <v>3909.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>368.3</v>
+      </c>
+      <c r="K76">
+        <v>257.4</v>
+      </c>
+      <c r="L76">
+        <v>110.9</v>
+      </c>
+      <c r="M76">
+        <v>1108.8147864</v>
+      </c>
+      <c r="N76">
+        <v>-997.9147863999999</v>
+      </c>
+      <c r="O76">
+        <v>-219.541253008</v>
+      </c>
+      <c r="P76">
+        <v>-778.3735333919999</v>
+      </c>
+      <c r="Q76">
+        <v>-520.9735333919999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2624556459188686</v>
+      </c>
+      <c r="T76">
+        <v>3.781646232834237</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02200367482401027</v>
+      </c>
+      <c r="W76">
+        <v>0.2335455224520264</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1000167037455013</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2430621545534054</v>
+      </c>
+      <c r="C77">
+        <v>-2484.479194848084</v>
+      </c>
+      <c r="D77">
+        <v>1587.645805151916</v>
+      </c>
+      <c r="E77">
+        <v>2340.925</v>
+      </c>
+      <c r="F77">
+        <v>4706.025</v>
+      </c>
+      <c r="G77">
+        <v>633.9</v>
+      </c>
+      <c r="H77">
+        <v>3909.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>368.3</v>
+      </c>
+      <c r="K77">
+        <v>257.4</v>
+      </c>
+      <c r="L77">
+        <v>110.9</v>
+      </c>
+      <c r="M77">
+        <v>1123.79877</v>
+      </c>
+      <c r="N77">
+        <v>-1012.89877</v>
+      </c>
+      <c r="O77">
+        <v>-222.8377293999999</v>
+      </c>
+      <c r="P77">
+        <v>-790.0610405999998</v>
+      </c>
+      <c r="Q77">
+        <v>-532.6610405999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2714018717556234</v>
+      </c>
+      <c r="T77">
+        <v>3.932912082147606</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02171029249302347</v>
+      </c>
+      <c r="W77">
+        <v>0.233615582152666</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.0986831476955613</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2450621545534053</v>
+      </c>
+      <c r="C78">
+        <v>-2562.620640897477</v>
+      </c>
+      <c r="D78">
+        <v>1572.251359102523</v>
+      </c>
+      <c r="E78">
+        <v>2403.672</v>
+      </c>
+      <c r="F78">
+        <v>4768.772</v>
+      </c>
+      <c r="G78">
+        <v>633.9</v>
+      </c>
+      <c r="H78">
+        <v>3909.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>368.3</v>
+      </c>
+      <c r="K78">
+        <v>257.4</v>
+      </c>
+      <c r="L78">
+        <v>110.9</v>
+      </c>
+      <c r="M78">
+        <v>1138.7827536</v>
+      </c>
+      <c r="N78">
+        <v>-1027.8827536</v>
+      </c>
+      <c r="O78">
+        <v>-226.134205792</v>
+      </c>
+      <c r="P78">
+        <v>-801.7485478079999</v>
+      </c>
+      <c r="Q78">
+        <v>-544.3485478079999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2810936164121077</v>
+      </c>
+      <c r="T78">
+        <v>4.096783418903757</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02142463074969421</v>
+      </c>
+      <c r="W78">
+        <v>0.233683798176973</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.09738468522588284</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2470621545534054</v>
+      </c>
+      <c r="C79">
+        <v>-2640.46641256316</v>
+      </c>
+      <c r="D79">
+        <v>1557.152587436841</v>
+      </c>
+      <c r="E79">
+        <v>2466.419</v>
+      </c>
+      <c r="F79">
+        <v>4831.519</v>
+      </c>
+      <c r="G79">
+        <v>633.9</v>
+      </c>
+      <c r="H79">
+        <v>3909.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>368.3</v>
+      </c>
+      <c r="K79">
+        <v>257.4</v>
+      </c>
+      <c r="L79">
+        <v>110.9</v>
+      </c>
+      <c r="M79">
+        <v>1153.7667372</v>
+      </c>
+      <c r="N79">
+        <v>-1042.8667372</v>
+      </c>
+      <c r="O79">
+        <v>-229.430682184</v>
+      </c>
+      <c r="P79">
+        <v>-813.436055016</v>
+      </c>
+      <c r="Q79">
+        <v>-556.036055016</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2916281214735036</v>
+      </c>
+      <c r="T79">
+        <v>4.274904437116964</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02114638879190597</v>
+      </c>
+      <c r="W79">
+        <v>0.2337502423564929</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.09611994905411814</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2490621545534054</v>
+      </c>
+      <c r="C80">
+        <v>-2718.024947151913</v>
+      </c>
+      <c r="D80">
+        <v>1542.341052848087</v>
+      </c>
+      <c r="E80">
+        <v>2529.166</v>
+      </c>
+      <c r="F80">
+        <v>4894.266</v>
+      </c>
+      <c r="G80">
+        <v>633.9</v>
+      </c>
+      <c r="H80">
+        <v>3909.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>368.3</v>
+      </c>
+      <c r="K80">
+        <v>257.4</v>
+      </c>
+      <c r="L80">
+        <v>110.9</v>
+      </c>
+      <c r="M80">
+        <v>1168.7507208</v>
+      </c>
+      <c r="N80">
+        <v>-1057.8507208</v>
+      </c>
+      <c r="O80">
+        <v>-232.7271585759999</v>
+      </c>
+      <c r="P80">
+        <v>-825.1235622239999</v>
+      </c>
+      <c r="Q80">
+        <v>-567.7235622239999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3031203088132083</v>
+      </c>
+      <c r="T80">
+        <v>4.469218275167735</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0208752812432918</v>
+      </c>
+      <c r="W80">
+        <v>0.2338149828391019</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.0948876420149628</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2510621545534054</v>
+      </c>
+      <c r="C81">
+        <v>-2795.30436397481</v>
+      </c>
+      <c r="D81">
+        <v>1527.80863602519</v>
+      </c>
+      <c r="E81">
+        <v>2591.913</v>
+      </c>
+      <c r="F81">
+        <v>4957.013</v>
+      </c>
+      <c r="G81">
+        <v>633.9</v>
+      </c>
+      <c r="H81">
+        <v>3909.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>368.3</v>
+      </c>
+      <c r="K81">
+        <v>257.4</v>
+      </c>
+      <c r="L81">
+        <v>110.9</v>
+      </c>
+      <c r="M81">
+        <v>1183.7347044</v>
+      </c>
+      <c r="N81">
+        <v>-1072.8347044</v>
+      </c>
+      <c r="O81">
+        <v>-236.023634968</v>
+      </c>
+      <c r="P81">
+        <v>-836.8110694320001</v>
+      </c>
+      <c r="Q81">
+        <v>-579.4110694320001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3157069901852659</v>
+      </c>
+      <c r="T81">
+        <v>4.682038193032867</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02061103717692101</v>
+      </c>
+      <c r="W81">
+        <v>0.2338780843221513</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.09368653262236826</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2530621545534054</v>
+      </c>
+      <c r="C82">
+        <v>-2872.312479188644</v>
+      </c>
+      <c r="D82">
+        <v>1513.547520811356</v>
+      </c>
+      <c r="E82">
+        <v>2654.66</v>
+      </c>
+      <c r="F82">
+        <v>5019.76</v>
+      </c>
+      <c r="G82">
+        <v>633.9</v>
+      </c>
+      <c r="H82">
+        <v>3909.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>368.3</v>
+      </c>
+      <c r="K82">
+        <v>257.4</v>
+      </c>
+      <c r="L82">
+        <v>110.9</v>
+      </c>
+      <c r="M82">
+        <v>1198.718688</v>
+      </c>
+      <c r="N82">
+        <v>-1087.818688</v>
+      </c>
+      <c r="O82">
+        <v>-239.32011136</v>
+      </c>
+      <c r="P82">
+        <v>-848.49857664</v>
+      </c>
+      <c r="Q82">
+        <v>-591.09857664</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3295523396945293</v>
+      </c>
+      <c r="T82">
+        <v>4.91614010268451</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0203533992122095</v>
+      </c>
+      <c r="W82">
+        <v>0.2339396082681244</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.09251545096458869</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2550621545534053</v>
+      </c>
+      <c r="C83">
+        <v>-2949.05681981384</v>
+      </c>
+      <c r="D83">
+        <v>1499.550180186161</v>
+      </c>
+      <c r="E83">
+        <v>2717.407000000001</v>
+      </c>
+      <c r="F83">
+        <v>5082.507000000001</v>
+      </c>
+      <c r="G83">
+        <v>633.9</v>
+      </c>
+      <c r="H83">
+        <v>3909.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>368.3</v>
+      </c>
+      <c r="K83">
+        <v>257.4</v>
+      </c>
+      <c r="L83">
+        <v>110.9</v>
+      </c>
+      <c r="M83">
+        <v>1213.7026716</v>
+      </c>
+      <c r="N83">
+        <v>-1102.8026716</v>
+      </c>
+      <c r="O83">
+        <v>-242.616587752</v>
+      </c>
+      <c r="P83">
+        <v>-860.1860838480002</v>
+      </c>
+      <c r="Q83">
+        <v>-602.7860838480002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3448550944152939</v>
+      </c>
+      <c r="T83">
+        <v>5.174884318615272</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02010212267872543</v>
+      </c>
+      <c r="W83">
+        <v>0.2339996131043204</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.09137328490329744</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2570621545534054</v>
+      </c>
+      <c r="C84">
+        <v>-3025.544636981657</v>
+      </c>
+      <c r="D84">
+        <v>1485.809363018343</v>
+      </c>
+      <c r="E84">
+        <v>2780.154</v>
+      </c>
+      <c r="F84">
+        <v>5145.254</v>
+      </c>
+      <c r="G84">
+        <v>633.9</v>
+      </c>
+      <c r="H84">
+        <v>3909.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>368.3</v>
+      </c>
+      <c r="K84">
+        <v>257.4</v>
+      </c>
+      <c r="L84">
+        <v>110.9</v>
+      </c>
+      <c r="M84">
+        <v>1228.6866552</v>
+      </c>
+      <c r="N84">
+        <v>-1117.7866552</v>
+      </c>
+      <c r="O84">
+        <v>-245.913064144</v>
+      </c>
+      <c r="P84">
+        <v>-871.8735910560001</v>
+      </c>
+      <c r="Q84">
+        <v>-614.4735910560001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3618581552161436</v>
+      </c>
+      <c r="T84">
+        <v>5.462377891871678</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01985697484118</v>
+      </c>
+      <c r="W84">
+        <v>0.2340581544079262</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.09025897655081827</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2590621545534054</v>
+      </c>
+      <c r="C85">
+        <v>-3101.782918459684</v>
+      </c>
+      <c r="D85">
+        <v>1472.318081540316</v>
+      </c>
+      <c r="E85">
+        <v>2842.901</v>
+      </c>
+      <c r="F85">
+        <v>5208.001</v>
+      </c>
+      <c r="G85">
+        <v>633.9</v>
+      </c>
+      <c r="H85">
+        <v>3909.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>368.3</v>
+      </c>
+      <c r="K85">
+        <v>257.4</v>
+      </c>
+      <c r="L85">
+        <v>110.9</v>
+      </c>
+      <c r="M85">
+        <v>1243.6706388</v>
+      </c>
+      <c r="N85">
+        <v>-1132.7706388</v>
+      </c>
+      <c r="O85">
+        <v>-249.209540536</v>
+      </c>
+      <c r="P85">
+        <v>-883.561098264</v>
+      </c>
+      <c r="Q85">
+        <v>-626.161098264</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3808615761112109</v>
+      </c>
+      <c r="T85">
+        <v>5.783694238452365</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01961773418044289</v>
+      </c>
+      <c r="W85">
+        <v>0.2341152850777103</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.08917151900201314</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2610621545534053</v>
+      </c>
+      <c r="C86">
+        <v>-3177.77840050107</v>
+      </c>
+      <c r="D86">
+        <v>1459.06959949893</v>
+      </c>
+      <c r="E86">
+        <v>2905.648</v>
+      </c>
+      <c r="F86">
+        <v>5270.748</v>
+      </c>
+      <c r="G86">
+        <v>633.9</v>
+      </c>
+      <c r="H86">
+        <v>3909.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>368.3</v>
+      </c>
+      <c r="K86">
+        <v>257.4</v>
+      </c>
+      <c r="L86">
+        <v>110.9</v>
+      </c>
+      <c r="M86">
+        <v>1258.6546224</v>
+      </c>
+      <c r="N86">
+        <v>-1147.7546224</v>
+      </c>
+      <c r="O86">
+        <v>-252.5060169279999</v>
+      </c>
+      <c r="P86">
+        <v>-895.2486054719999</v>
+      </c>
+      <c r="Q86">
+        <v>-637.8486054719999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4022404246181614</v>
+      </c>
+      <c r="T86">
+        <v>6.145175128355635</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01938418972591381</v>
+      </c>
+      <c r="W86">
+        <v>0.2341710554934518</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.08810995329960825</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2630621545534053</v>
+      </c>
+      <c r="C87">
+        <v>-3253.537579059727</v>
+      </c>
+      <c r="D87">
+        <v>1446.057420940273</v>
+      </c>
+      <c r="E87">
+        <v>2968.395</v>
+      </c>
+      <c r="F87">
+        <v>5333.495</v>
+      </c>
+      <c r="G87">
+        <v>633.9</v>
+      </c>
+      <c r="H87">
+        <v>3909.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>368.3</v>
+      </c>
+      <c r="K87">
+        <v>257.4</v>
+      </c>
+      <c r="L87">
+        <v>110.9</v>
+      </c>
+      <c r="M87">
+        <v>1273.638606</v>
+      </c>
+      <c r="N87">
+        <v>-1162.738606</v>
+      </c>
+      <c r="O87">
+        <v>-255.8024933199999</v>
+      </c>
+      <c r="P87">
+        <v>-906.93611268</v>
+      </c>
+      <c r="Q87">
+        <v>-649.53611268</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4264697862593722</v>
+      </c>
+      <c r="T87">
+        <v>6.554853470246011</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01915614043502071</v>
+      </c>
+      <c r="W87">
+        <v>0.2342255136641171</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.08707336561373058</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2650621545534053</v>
+      </c>
+      <c r="C88">
+        <v>-3329.066720410714</v>
+      </c>
+      <c r="D88">
+        <v>1433.275279589286</v>
+      </c>
+      <c r="E88">
+        <v>3031.142</v>
+      </c>
+      <c r="F88">
+        <v>5396.242</v>
+      </c>
+      <c r="G88">
+        <v>633.9</v>
+      </c>
+      <c r="H88">
+        <v>3909.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>368.3</v>
+      </c>
+      <c r="K88">
+        <v>257.4</v>
+      </c>
+      <c r="L88">
+        <v>110.9</v>
+      </c>
+      <c r="M88">
+        <v>1288.6225896</v>
+      </c>
+      <c r="N88">
+        <v>-1177.7225896</v>
+      </c>
+      <c r="O88">
+        <v>-259.098969712</v>
+      </c>
+      <c r="P88">
+        <v>-918.623619888</v>
+      </c>
+      <c r="Q88">
+        <v>-661.223619888</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4541604852778988</v>
+      </c>
+      <c r="T88">
+        <v>7.023057289549297</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01893339461600884</v>
+      </c>
+      <c r="W88">
+        <v>0.2342787053656971</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.08606088461822203</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2670621545534054</v>
+      </c>
+      <c r="C89">
+        <v>-3404.371871212309</v>
+      </c>
+      <c r="D89">
+        <v>1420.717128787691</v>
+      </c>
+      <c r="E89">
+        <v>3093.889</v>
+      </c>
+      <c r="F89">
+        <v>5458.989</v>
+      </c>
+      <c r="G89">
+        <v>633.9</v>
+      </c>
+      <c r="H89">
+        <v>3909.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>368.3</v>
+      </c>
+      <c r="K89">
+        <v>257.4</v>
+      </c>
+      <c r="L89">
+        <v>110.9</v>
+      </c>
+      <c r="M89">
+        <v>1303.6065732</v>
+      </c>
+      <c r="N89">
+        <v>-1192.7065732</v>
+      </c>
+      <c r="O89">
+        <v>-262.3954461039999</v>
+      </c>
+      <c r="P89">
+        <v>-930.311127096</v>
+      </c>
+      <c r="Q89">
+        <v>-672.911127096</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4861112918377372</v>
+      </c>
+      <c r="T89">
+        <v>7.563292465668474</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01871576939053747</v>
+      </c>
+      <c r="W89">
+        <v>0.2343306742695397</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.0850716790478977</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2690621545534053</v>
+      </c>
+      <c r="C90">
+        <v>-3479.458868043687</v>
+      </c>
+      <c r="D90">
+        <v>1408.377131956313</v>
+      </c>
+      <c r="E90">
+        <v>3156.636</v>
+      </c>
+      <c r="F90">
+        <v>5521.736</v>
+      </c>
+      <c r="G90">
+        <v>633.9</v>
+      </c>
+      <c r="H90">
+        <v>3909.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>368.3</v>
+      </c>
+      <c r="K90">
+        <v>257.4</v>
+      </c>
+      <c r="L90">
+        <v>110.9</v>
+      </c>
+      <c r="M90">
+        <v>1318.5905568</v>
+      </c>
+      <c r="N90">
+        <v>-1207.6905568</v>
+      </c>
+      <c r="O90">
+        <v>-265.691922496</v>
+      </c>
+      <c r="P90">
+        <v>-941.998634304</v>
+      </c>
+      <c r="Q90">
+        <v>-684.598634304</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5233872328242153</v>
+      </c>
+      <c r="T90">
+        <v>8.193566837807515</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01850309019291773</v>
+      </c>
+      <c r="W90">
+        <v>0.2343814620619313</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.0841049554223533</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2710621545534053</v>
+      </c>
+      <c r="C91">
+        <v>-3554.333346449839</v>
+      </c>
+      <c r="D91">
+        <v>1396.249653550161</v>
+      </c>
+      <c r="E91">
+        <v>3219.383</v>
+      </c>
+      <c r="F91">
+        <v>5584.483</v>
+      </c>
+      <c r="G91">
+        <v>633.9</v>
+      </c>
+      <c r="H91">
+        <v>3909.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>368.3</v>
+      </c>
+      <c r="K91">
+        <v>257.4</v>
+      </c>
+      <c r="L91">
+        <v>110.9</v>
+      </c>
+      <c r="M91">
+        <v>1333.5745404</v>
+      </c>
+      <c r="N91">
+        <v>-1222.6745404</v>
+      </c>
+      <c r="O91">
+        <v>-268.988398888</v>
+      </c>
+      <c r="P91">
+        <v>-953.6861415120001</v>
+      </c>
+      <c r="Q91">
+        <v>-696.2861415120001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5674406176264166</v>
+      </c>
+      <c r="T91">
+        <v>8.938436550335471</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01829519030310966</v>
+      </c>
+      <c r="W91">
+        <v>0.2344311085556174</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.08315995592322578</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2730621545534053</v>
+      </c>
+      <c r="C92">
+        <v>-3629.000749523155</v>
+      </c>
+      <c r="D92">
+        <v>1384.329250476844</v>
+      </c>
+      <c r="E92">
+        <v>3282.13</v>
+      </c>
+      <c r="F92">
+        <v>5647.23</v>
+      </c>
+      <c r="G92">
+        <v>633.9</v>
+      </c>
+      <c r="H92">
+        <v>3909.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>368.3</v>
+      </c>
+      <c r="K92">
+        <v>257.4</v>
+      </c>
+      <c r="L92">
+        <v>110.9</v>
+      </c>
+      <c r="M92">
+        <v>1348.558524</v>
+      </c>
+      <c r="N92">
+        <v>-1237.658524</v>
+      </c>
+      <c r="O92">
+        <v>-272.2848752799999</v>
+      </c>
+      <c r="P92">
+        <v>-965.37364872</v>
+      </c>
+      <c r="Q92">
+        <v>-707.97364872</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6203046793890585</v>
+      </c>
+      <c r="T92">
+        <v>9.832280205369019</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01809191041085289</v>
+      </c>
+      <c r="W92">
+        <v>0.2344796517938883</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.08223595641296777</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2750621545534054</v>
+      </c>
+      <c r="C93">
+        <v>-3703.466336049157</v>
+      </c>
+      <c r="D93">
+        <v>1372.610663950843</v>
+      </c>
+      <c r="E93">
+        <v>3344.877</v>
+      </c>
+      <c r="F93">
+        <v>5709.977</v>
+      </c>
+      <c r="G93">
+        <v>633.9</v>
+      </c>
+      <c r="H93">
+        <v>3909.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>368.3</v>
+      </c>
+      <c r="K93">
+        <v>257.4</v>
+      </c>
+      <c r="L93">
+        <v>110.9</v>
+      </c>
+      <c r="M93">
+        <v>1363.5425076</v>
+      </c>
+      <c r="N93">
+        <v>-1252.6425076</v>
+      </c>
+      <c r="O93">
+        <v>-275.581351672</v>
+      </c>
+      <c r="P93">
+        <v>-977.0611559280001</v>
+      </c>
+      <c r="Q93">
+        <v>-719.6611559280001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6849163104322873</v>
+      </c>
+      <c r="T93">
+        <v>10.92475578374336</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01789309820853582</v>
+      </c>
+      <c r="W93">
+        <v>0.2345271281478017</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.0813322645842538</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2770621545534054</v>
+      </c>
+      <c r="C94">
+        <v>-3777.735188241955</v>
+      </c>
+      <c r="D94">
+        <v>1361.088811758045</v>
+      </c>
+      <c r="E94">
+        <v>3407.624</v>
+      </c>
+      <c r="F94">
+        <v>5772.724</v>
+      </c>
+      <c r="G94">
+        <v>633.9</v>
+      </c>
+      <c r="H94">
+        <v>3909.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>368.3</v>
+      </c>
+      <c r="K94">
+        <v>257.4</v>
+      </c>
+      <c r="L94">
+        <v>110.9</v>
+      </c>
+      <c r="M94">
+        <v>1378.5264912</v>
+      </c>
+      <c r="N94">
+        <v>-1267.6264912</v>
+      </c>
+      <c r="O94">
+        <v>-278.877828064</v>
+      </c>
+      <c r="P94">
+        <v>-988.748663136</v>
+      </c>
+      <c r="Q94">
+        <v>-731.348663136</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7656808492363234</v>
+      </c>
+      <c r="T94">
+        <v>12.29035025671128</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01769860801061696</v>
+      </c>
+      <c r="W94">
+        <v>0.2345735724070647</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.08044821823007708</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2790621545534054</v>
+      </c>
+      <c r="C95">
+        <v>-3851.812219093364</v>
+      </c>
+      <c r="D95">
+        <v>1349.758780906636</v>
+      </c>
+      <c r="E95">
+        <v>3470.371000000001</v>
+      </c>
+      <c r="F95">
+        <v>5835.471</v>
+      </c>
+      <c r="G95">
+        <v>633.9</v>
+      </c>
+      <c r="H95">
+        <v>3909.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>368.3</v>
+      </c>
+      <c r="K95">
+        <v>257.4</v>
+      </c>
+      <c r="L95">
+        <v>110.9</v>
+      </c>
+      <c r="M95">
+        <v>1393.5104748</v>
+      </c>
+      <c r="N95">
+        <v>-1282.6104748</v>
+      </c>
+      <c r="O95">
+        <v>-282.174304456</v>
+      </c>
+      <c r="P95">
+        <v>-1000.436170344</v>
+      </c>
+      <c r="Q95">
+        <v>-743.0361703440001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8695209705557982</v>
+      </c>
+      <c r="T95">
+        <v>14.0461145790986</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01750830039759957</v>
+      </c>
+      <c r="W95">
+        <v>0.2346190178650532</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.07958318362545258</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2810621545534054</v>
+      </c>
+      <c r="C96">
+        <v>-3925.702179357998</v>
+      </c>
+      <c r="D96">
+        <v>1338.615820642002</v>
+      </c>
+      <c r="E96">
+        <v>3533.118</v>
+      </c>
+      <c r="F96">
+        <v>5898.218</v>
+      </c>
+      <c r="G96">
+        <v>633.9</v>
+      </c>
+      <c r="H96">
+        <v>3909.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>368.3</v>
+      </c>
+      <c r="K96">
+        <v>257.4</v>
+      </c>
+      <c r="L96">
+        <v>110.9</v>
+      </c>
+      <c r="M96">
+        <v>1408.4944584</v>
+      </c>
+      <c r="N96">
+        <v>-1297.5944584</v>
+      </c>
+      <c r="O96">
+        <v>-285.4707808479999</v>
+      </c>
+      <c r="P96">
+        <v>-1012.123677552</v>
+      </c>
+      <c r="Q96">
+        <v>-754.7236775519999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.007974465648432</v>
+      </c>
+      <c r="T96">
+        <v>16.38713367561504</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01732204188273149</v>
+      </c>
+      <c r="W96">
+        <v>0.2346634963984038</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.07873655401241586</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2830621545534053</v>
+      </c>
+      <c r="C97">
+        <v>-3999.409664195196</v>
+      </c>
+      <c r="D97">
+        <v>1327.655335804804</v>
+      </c>
+      <c r="E97">
+        <v>3595.865</v>
+      </c>
+      <c r="F97">
+        <v>5960.965</v>
+      </c>
+      <c r="G97">
+        <v>633.9</v>
+      </c>
+      <c r="H97">
+        <v>3909.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>368.3</v>
+      </c>
+      <c r="K97">
+        <v>257.4</v>
+      </c>
+      <c r="L97">
+        <v>110.9</v>
+      </c>
+      <c r="M97">
+        <v>1423.478442</v>
+      </c>
+      <c r="N97">
+        <v>-1312.578442</v>
+      </c>
+      <c r="O97">
+        <v>-288.76725724</v>
+      </c>
+      <c r="P97">
+        <v>-1023.81118476</v>
+      </c>
+      <c r="Q97">
+        <v>-766.4111847600001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.201809358778118</v>
+      </c>
+      <c r="T97">
+        <v>19.66456041073806</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01713970459975537</v>
+      </c>
+      <c r="W97">
+        <v>0.2347070385415784</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.07790774818070623</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2850621545534053</v>
+      </c>
+      <c r="C98">
+        <v>-4072.939119487301</v>
+      </c>
+      <c r="D98">
+        <v>1316.872880512698</v>
+      </c>
+      <c r="E98">
+        <v>3658.612</v>
+      </c>
+      <c r="F98">
+        <v>6023.712</v>
+      </c>
+      <c r="G98">
+        <v>633.9</v>
+      </c>
+      <c r="H98">
+        <v>3909.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>368.3</v>
+      </c>
+      <c r="K98">
+        <v>257.4</v>
+      </c>
+      <c r="L98">
+        <v>110.9</v>
+      </c>
+      <c r="M98">
+        <v>1438.4624256</v>
+      </c>
+      <c r="N98">
+        <v>-1327.5624256</v>
+      </c>
+      <c r="O98">
+        <v>-292.0637336319999</v>
+      </c>
+      <c r="P98">
+        <v>-1035.498691968</v>
+      </c>
+      <c r="Q98">
+        <v>-778.098691968</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.492561698472645</v>
+      </c>
+      <c r="T98">
+        <v>24.58070051342252</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01696116601017458</v>
+      </c>
+      <c r="W98">
+        <v>0.2347496735567703</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.0770962091371572</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2870621545534053</v>
+      </c>
+      <c r="C99">
+        <v>-4146.294847852538</v>
+      </c>
+      <c r="D99">
+        <v>1306.264152147462</v>
+      </c>
+      <c r="E99">
+        <v>3721.359</v>
+      </c>
+      <c r="F99">
+        <v>6086.459</v>
+      </c>
+      <c r="G99">
+        <v>633.9</v>
+      </c>
+      <c r="H99">
+        <v>3909.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>368.3</v>
+      </c>
+      <c r="K99">
+        <v>257.4</v>
+      </c>
+      <c r="L99">
+        <v>110.9</v>
+      </c>
+      <c r="M99">
+        <v>1453.4464092</v>
+      </c>
+      <c r="N99">
+        <v>-1342.5464092</v>
+      </c>
+      <c r="O99">
+        <v>-295.360210024</v>
+      </c>
+      <c r="P99">
+        <v>-1047.186199176</v>
+      </c>
+      <c r="Q99">
+        <v>-789.786199176</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.97714893129686</v>
+      </c>
+      <c r="T99">
+        <v>32.77426735123003</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01678630862862639</v>
+      </c>
+      <c r="W99">
+        <v>0.234791429499484</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.07630140285739273</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2890621545534053</v>
+      </c>
+      <c r="C100">
+        <v>-4219.481014369573</v>
+      </c>
+      <c r="D100">
+        <v>1295.824985630427</v>
+      </c>
+      <c r="E100">
+        <v>3784.106</v>
+      </c>
+      <c r="F100">
+        <v>6149.206</v>
+      </c>
+      <c r="G100">
+        <v>633.9</v>
+      </c>
+      <c r="H100">
+        <v>3909.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>368.3</v>
+      </c>
+      <c r="K100">
+        <v>257.4</v>
+      </c>
+      <c r="L100">
+        <v>110.9</v>
+      </c>
+      <c r="M100">
+        <v>1468.4303928</v>
+      </c>
+      <c r="N100">
+        <v>-1357.5303928</v>
+      </c>
+      <c r="O100">
+        <v>-298.656686416</v>
+      </c>
+      <c r="P100">
+        <v>-1058.873706384</v>
+      </c>
+      <c r="Q100">
+        <v>-801.4737063840001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.94632339694529</v>
+      </c>
+      <c r="T100">
+        <v>49.16140102684504</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01661501976506898</v>
+      </c>
+      <c r="W100">
+        <v>0.2348323332801016</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.07552281711394992</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2910621545534053</v>
+      </c>
+      <c r="C101">
+        <v>-4292.501652029763</v>
+      </c>
+      <c r="D101">
+        <v>1285.551347970236</v>
+      </c>
+      <c r="E101">
+        <v>3846.853</v>
+      </c>
+      <c r="F101">
+        <v>6211.953</v>
+      </c>
+      <c r="G101">
+        <v>633.9</v>
+      </c>
+      <c r="H101">
+        <v>3909.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>368.3</v>
+      </c>
+      <c r="K101">
+        <v>257.4</v>
+      </c>
+      <c r="L101">
+        <v>110.9</v>
+      </c>
+      <c r="M101">
+        <v>1483.4143764</v>
+      </c>
+      <c r="N101">
+        <v>-1372.5143764</v>
+      </c>
+      <c r="O101">
+        <v>-301.9531628079999</v>
+      </c>
+      <c r="P101">
+        <v>-1070.561213592</v>
+      </c>
+      <c r="Q101">
+        <v>-813.1612135920001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.853846793890579</v>
+      </c>
+      <c r="T101">
+        <v>98.32280205369008</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01644719128259354</v>
+      </c>
+      <c r="W101">
+        <v>0.2348724107217167</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.07475996037542521</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_business_consumer_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.1892325315005728</v>
       </c>
       <c r="X2">
-        <v>0.1161370833446278</v>
+        <v>0.1160918628537447</v>
       </c>
       <c r="Y2">
-        <v>0.07309544815594493</v>
+        <v>0.07314066864682808</v>
       </c>
       <c r="Z2">
         <v>28.15308343409915</v>
@@ -662,10 +662,10 @@
         <v>0.8971595503831649</v>
       </c>
       <c r="AB2">
-        <v>0.08246741043867031</v>
+        <v>0.08244361842161282</v>
       </c>
       <c r="AC2">
-        <v>0.8146921399444945</v>
+        <v>0.814715931961552</v>
       </c>
       <c r="AD2">
         <v>2901.2</v>
@@ -787,10 +787,10 @@
         <v>0.1892325315005728</v>
       </c>
       <c r="X3">
-        <v>0.1161370833446278</v>
+        <v>0.1160918628537447</v>
       </c>
       <c r="Y3">
-        <v>0.07309544815594493</v>
+        <v>0.07314066864682808</v>
       </c>
       <c r="Z3">
         <v>28.15308343409915</v>
@@ -799,10 +799,10 @@
         <v>0.8971595503831649</v>
       </c>
       <c r="AB3">
-        <v>0.08246741043867031</v>
+        <v>0.08244361842161282</v>
       </c>
       <c r="AC3">
-        <v>0.8146921399444945</v>
+        <v>0.814715931961552</v>
       </c>
       <c r="AD3">
         <v>2901.2</v>
@@ -1139,49 +1139,49 @@
         <v>3.27505112474438</v>
       </c>
       <c r="F2">
-        <v>4.67441851221626</v>
+        <v>4.66113548363595</v>
       </c>
       <c r="G2">
         <v>5.33210806836978</v>
       </c>
       <c r="H2">
-        <v>2.25046866384856</v>
+        <v>2.36299209704098</v>
       </c>
       <c r="I2">
         <v>0.473866457598327</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K2">
         <v>3221.2</v>
       </c>
       <c r="L2">
-        <v>4654.34695974205</v>
+        <v>4638.64973317436</v>
       </c>
       <c r="M2">
         <v>5242.4</v>
       </c>
       <c r="N2">
-        <v>4998.82695974205</v>
+        <v>5044.35373317436</v>
       </c>
       <c r="O2">
         <v>2901.2</v>
       </c>
       <c r="P2">
-        <v>1224.48</v>
+        <v>1285.704</v>
       </c>
       <c r="Q2">
-        <v>0.0824674104386703</v>
+        <v>0.0824436184216128</v>
       </c>
       <c r="R2">
-        <v>0.0851682733888889</v>
+        <v>0.0846197894029381</v>
       </c>
       <c r="S2">
         <v>0.045084</v>
       </c>
       <c r="T2">
-        <v>0.045162</v>
+        <v>0.043134</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.116137083344628</v>
+        <v>0.116091862853745</v>
       </c>
       <c r="X2">
-        <v>0.09516984173611109</v>
+        <v>0.0956476574720735</v>
       </c>
       <c r="Y2">
         <v>1.62336865713036</v>
       </c>
       <c r="Z2">
-        <v>1.13944806737584</v>
+        <v>1.15121610790008</v>
       </c>
       <c r="AA2">
         <v>2901.2</v>
@@ -1236,7 +1236,7 @@
         <v>3221.2</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08711367509298004</v>
+        <v>0.08708711407311603</v>
       </c>
       <c r="C2">
-        <v>5716.952753466476</v>
+        <v>5717.167489285272</v>
       </c>
       <c r="D2">
-        <v>4836.952753466476</v>
+        <v>4837.167489285272</v>
       </c>
       <c r="E2">
         <v>-2901.2</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08711367509298004</v>
+        <v>0.08708711407311603</v>
       </c>
       <c r="T2">
         <v>0.9535130270927493</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08696804500777548</v>
+        <v>0.0869306224221552</v>
       </c>
       <c r="C3">
-        <v>5667.482525380371</v>
+        <v>5668.577586835087</v>
       </c>
       <c r="D3">
-        <v>4848.706525380371</v>
+        <v>4849.801586835088</v>
       </c>
       <c r="E3">
         <v>-2839.976</v>
@@ -1539,37 +1539,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M3">
-        <v>3.165280800000001</v>
+        <v>3.0795672</v>
       </c>
       <c r="N3">
-        <v>328.2388008326531</v>
+        <v>328.3245144326531</v>
       </c>
       <c r="O3">
-        <v>72.21253618318369</v>
+        <v>72.23139317518368</v>
       </c>
       <c r="P3">
-        <v>256.0262646494695</v>
+        <v>256.0931212574694</v>
       </c>
       <c r="Q3">
-        <v>479.8262646494695</v>
+        <v>479.8931212574694</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08743917677553079</v>
+        <v>0.08741240648702545</v>
       </c>
       <c r="T3">
         <v>0.9610255539728739</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>104.6997415308787</v>
+        <v>107.6138496450583</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08682241492257094</v>
+        <v>0.08677413077119434</v>
       </c>
       <c r="C4">
-        <v>5618.069559659913</v>
+        <v>5620.053854689033</v>
       </c>
       <c r="D4">
-        <v>4860.517559659913</v>
+        <v>4862.501854689033</v>
       </c>
       <c r="E4">
         <v>-2778.752</v>
@@ -1621,37 +1621,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M4">
-        <v>6.330561600000001</v>
+        <v>6.1591344</v>
       </c>
       <c r="N4">
-        <v>325.0735200326531</v>
+        <v>325.2449472326531</v>
       </c>
       <c r="O4">
-        <v>71.51617440718368</v>
+        <v>71.55388839118368</v>
       </c>
       <c r="P4">
-        <v>253.5573456254694</v>
+        <v>253.6910588414694</v>
       </c>
       <c r="Q4">
-        <v>477.3573456254694</v>
+        <v>477.4910588414695</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08777132134956217</v>
+        <v>0.08774433752162687</v>
       </c>
       <c r="T4">
         <v>0.9686913977281033</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>52.34987076543936</v>
+        <v>53.80692482252913</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08667678483736635</v>
+        <v>0.08661763912023347</v>
       </c>
       <c r="C5">
-        <v>5568.714275785596</v>
+        <v>5571.596814056315</v>
       </c>
       <c r="D5">
-        <v>4872.386275785596</v>
+        <v>4875.268814056314</v>
       </c>
       <c r="E5">
         <v>-2717.528</v>
@@ -1703,37 +1703,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M5">
-        <v>9.495842400000001</v>
+        <v>9.238701599999999</v>
       </c>
       <c r="N5">
-        <v>321.9082392326531</v>
+        <v>322.1653800326531</v>
       </c>
       <c r="O5">
-        <v>70.81981263118368</v>
+        <v>70.87638360718368</v>
       </c>
       <c r="P5">
-        <v>251.0884266014694</v>
+        <v>251.2889964254694</v>
       </c>
       <c r="Q5">
-        <v>474.8884266014694</v>
+        <v>475.0889964254694</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08811031426532615</v>
+        <v>0.08808311249508606</v>
       </c>
       <c r="T5">
         <v>0.976515300117461</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.89991384362624</v>
+        <v>35.87128321501943</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.0865311547521618</v>
+        <v>0.08646114746927261</v>
       </c>
       <c r="C6">
-        <v>5519.41709734519</v>
+        <v>5523.20699163449</v>
       </c>
       <c r="D6">
-        <v>4884.31309734519</v>
+        <v>4888.10299163449</v>
       </c>
       <c r="E6">
         <v>-2656.304</v>
@@ -1785,37 +1785,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M6">
-        <v>12.6611232</v>
+        <v>12.3182688</v>
       </c>
       <c r="N6">
-        <v>318.7429584326531</v>
+        <v>319.0858128326531</v>
       </c>
       <c r="O6">
-        <v>70.12345085518368</v>
+        <v>70.19887882318369</v>
       </c>
       <c r="P6">
-        <v>248.6195075774694</v>
+        <v>248.8869340094694</v>
       </c>
       <c r="Q6">
-        <v>472.4195075774694</v>
+        <v>472.6869340094694</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08845636953350189</v>
+        <v>0.0884289452804923</v>
       </c>
       <c r="T6">
         <v>0.9845022004732636</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.17493538271968</v>
+        <v>26.90346241126457</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08638552466695726</v>
+        <v>0.08630465581831177</v>
       </c>
       <c r="C7">
-        <v>5470.178452084147</v>
+        <v>5474.884919681891</v>
       </c>
       <c r="D7">
-        <v>4896.298452084147</v>
+        <v>4901.004919681891</v>
       </c>
       <c r="E7">
         <v>-2595.08</v>
@@ -1867,37 +1867,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M7">
-        <v>15.826404</v>
+        <v>15.397836</v>
       </c>
       <c r="N7">
-        <v>315.5776776326531</v>
+        <v>316.0062456326531</v>
       </c>
       <c r="O7">
-        <v>69.42708907918369</v>
+        <v>69.52137403918368</v>
       </c>
       <c r="P7">
-        <v>246.1505885534694</v>
+        <v>246.4848715934694</v>
       </c>
       <c r="Q7">
-        <v>469.9505885534694</v>
+        <v>470.2848715934695</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08880971017574449</v>
+        <v>0.08878205875611767</v>
       </c>
       <c r="T7">
         <v>0.992657246099715</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.93994830617574</v>
+        <v>21.52276992901166</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0862398945817527</v>
+        <v>0.08614816416735091</v>
       </c>
       <c r="C8">
-        <v>5420.998771956737</v>
+        <v>5426.631136091219</v>
       </c>
       <c r="D8">
-        <v>4908.342771956737</v>
+        <v>4913.975136091219</v>
       </c>
       <c r="E8">
         <v>-2533.856</v>
@@ -1949,37 +1949,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M8">
-        <v>18.9916848</v>
+        <v>18.4774032</v>
       </c>
       <c r="N8">
-        <v>312.4123968326531</v>
+        <v>312.9266784326531</v>
       </c>
       <c r="O8">
-        <v>68.7307273031837</v>
+        <v>68.84386925518369</v>
       </c>
       <c r="P8">
-        <v>243.6816695294694</v>
+        <v>244.0828091774695</v>
       </c>
       <c r="Q8">
-        <v>467.4816695294695</v>
+        <v>467.8828091774695</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08917056870399223</v>
+        <v>0.08914268528441587</v>
       </c>
       <c r="T8">
         <v>1.000985803335239</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.44995692181313</v>
+        <v>17.93564160750972</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08609426449654814</v>
+        <v>0.08599167251639006</v>
       </c>
       <c r="C9">
-        <v>5371.878493177933</v>
+        <v>5378.446184464276</v>
       </c>
       <c r="D9">
-        <v>4920.446493177933</v>
+        <v>4927.014184464276</v>
       </c>
       <c r="E9">
         <v>-2472.632</v>
@@ -2031,37 +2031,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M9">
-        <v>22.15696560000001</v>
+        <v>21.5569704</v>
       </c>
       <c r="N9">
-        <v>309.2471160326531</v>
+        <v>309.8471112326531</v>
       </c>
       <c r="O9">
-        <v>68.0343655271837</v>
+        <v>68.16636447118368</v>
       </c>
       <c r="P9">
-        <v>241.2127505054694</v>
+        <v>241.6807467614694</v>
       </c>
       <c r="Q9">
-        <v>465.0127505054695</v>
+        <v>465.4807467614694</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08953918763069693</v>
+        <v>0.0895110672219248</v>
       </c>
       <c r="T9">
         <v>1.009493469328517</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.95710593298268</v>
+        <v>15.37340709215118</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08594863441134359</v>
+        <v>0.08583518086542921</v>
       </c>
       <c r="C10">
-        <v>5322.818056276079</v>
+        <v>5330.330614187928</v>
       </c>
       <c r="D10">
-        <v>4932.610056276079</v>
+        <v>4940.122614187929</v>
       </c>
       <c r="E10">
         <v>-2411.408</v>
@@ -2113,37 +2113,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M10">
-        <v>25.3222464</v>
+        <v>24.6365376</v>
       </c>
       <c r="N10">
-        <v>306.0818352326531</v>
+        <v>306.7675440326531</v>
       </c>
       <c r="O10">
-        <v>67.33800375118369</v>
+        <v>67.48885968718369</v>
       </c>
       <c r="P10">
-        <v>238.7438314814694</v>
+        <v>239.2786843454694</v>
       </c>
       <c r="Q10">
-        <v>462.5438314814695</v>
+        <v>463.0786843454695</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08991582001232998</v>
+        <v>0.08988745746242305</v>
       </c>
       <c r="T10">
         <v>1.018186084582518</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.08746769135984</v>
+        <v>13.45173120563229</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08588022432613904</v>
+        <v>0.08578398921446836</v>
       </c>
       <c r="C11">
-        <v>5267.328703776444</v>
+        <v>5273.409805809099</v>
       </c>
       <c r="D11">
-        <v>4938.344703776444</v>
+        <v>4944.425805809099</v>
       </c>
       <c r="E11">
         <v>-2350.184</v>
@@ -2195,37 +2195,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M11">
-        <v>29.0936448</v>
+        <v>28.5426288</v>
       </c>
       <c r="N11">
-        <v>302.3104368326531</v>
+        <v>302.8614528326531</v>
       </c>
       <c r="O11">
-        <v>66.50829610318368</v>
+        <v>66.62951962318368</v>
       </c>
       <c r="P11">
-        <v>235.8021407294694</v>
+        <v>236.2319332094694</v>
       </c>
       <c r="Q11">
-        <v>459.6021407294695</v>
+        <v>460.0319332094695</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09030073002872421</v>
+        <v>0.09027212001589929</v>
       </c>
       <c r="T11">
         <v>1.027069746325619</v>
       </c>
       <c r="U11">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.39094410173912</v>
+        <v>11.61084649752559</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08574317424093447</v>
+        <v>0.08563919756350749</v>
       </c>
       <c r="C12">
-        <v>5217.633480295575</v>
+        <v>5224.397741845968</v>
       </c>
       <c r="D12">
-        <v>4949.873480295575</v>
+        <v>4956.637741845968</v>
       </c>
       <c r="E12">
         <v>-2288.96</v>
@@ -2277,37 +2277,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M12">
-        <v>32.326272</v>
+        <v>31.714032</v>
       </c>
       <c r="N12">
-        <v>299.0778096326531</v>
+        <v>299.6900496326531</v>
       </c>
       <c r="O12">
-        <v>65.79711811918368</v>
+        <v>65.93181091918368</v>
       </c>
       <c r="P12">
-        <v>233.2806915134694</v>
+        <v>233.7582387134694</v>
       </c>
       <c r="Q12">
-        <v>457.0806915134694</v>
+        <v>457.5582387134694</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09069419360103831</v>
+        <v>0.09066533062611944</v>
       </c>
       <c r="T12">
         <v>1.036150822774121</v>
       </c>
       <c r="U12">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.25184969156521</v>
+        <v>10.44976184777303</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08579488415572993</v>
+        <v>0.08564026591254666</v>
       </c>
       <c r="C13">
-        <v>5152.053277841541</v>
+        <v>5163.08341485038</v>
       </c>
       <c r="D13">
-        <v>4945.517277841541</v>
+        <v>4956.54741485038</v>
       </c>
       <c r="E13">
         <v>-2227.736</v>
@@ -2359,37 +2359,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M13">
-        <v>37.04052</v>
+        <v>36.030324</v>
       </c>
       <c r="N13">
-        <v>294.3635616326531</v>
+        <v>295.3737576326531</v>
       </c>
       <c r="O13">
-        <v>64.75998355918368</v>
+        <v>64.98222667918368</v>
       </c>
       <c r="P13">
-        <v>229.6035780734694</v>
+        <v>230.3915309534694</v>
       </c>
       <c r="Q13">
-        <v>453.4035780734694</v>
+        <v>454.1915309534695</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09109649905138194</v>
+        <v>0.09106737742982769</v>
       </c>
       <c r="T13">
         <v>1.045435968356298</v>
       </c>
       <c r="U13">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.947068821729637</v>
+        <v>9.197921218600563</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08567499407052537</v>
+        <v>0.08550873426158578</v>
       </c>
       <c r="C14">
-        <v>5100.940931441022</v>
+        <v>5113.00498374607</v>
       </c>
       <c r="D14">
-        <v>4955.628931441022</v>
+        <v>4967.69298374607</v>
       </c>
       <c r="E14">
         <v>-2166.512</v>
@@ -2441,37 +2441,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M14">
-        <v>40.40784</v>
+        <v>39.305808</v>
       </c>
       <c r="N14">
-        <v>290.9962416326531</v>
+        <v>292.0982736326531</v>
       </c>
       <c r="O14">
-        <v>64.01917315918368</v>
+        <v>64.26162019918368</v>
       </c>
       <c r="P14">
-        <v>226.9770684734694</v>
+        <v>227.8366534334694</v>
       </c>
       <c r="Q14">
-        <v>450.7770684734694</v>
+        <v>451.6366534334694</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0915079478074152</v>
+        <v>0.09147856166089294</v>
       </c>
       <c r="T14">
         <v>1.054932139974433</v>
       </c>
       <c r="U14">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.201479753252169</v>
+        <v>8.431427783717183</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08570720398532082</v>
+        <v>0.08537720261062492</v>
       </c>
       <c r="C15">
-        <v>5036.996254033003</v>
+        <v>5062.976790705267</v>
       </c>
       <c r="D15">
-        <v>4952.908254033003</v>
+        <v>4978.888790705268</v>
       </c>
       <c r="E15">
         <v>-2105.288</v>
@@ -2523,45 +2523,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M15">
-        <v>44.96902800000001</v>
+        <v>42.581292</v>
       </c>
       <c r="N15">
-        <v>286.4350536326531</v>
+        <v>288.8227896326531</v>
       </c>
       <c r="O15">
-        <v>63.01571179918368</v>
+        <v>63.54101371918368</v>
       </c>
       <c r="P15">
-        <v>223.4193418334694</v>
+        <v>225.2817759134694</v>
       </c>
       <c r="Q15">
-        <v>447.2193418334694</v>
+        <v>449.0817759134694</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09192885515554117</v>
+        <v>0.09189919840301716</v>
       </c>
       <c r="T15">
         <v>1.064646614388387</v>
       </c>
       <c r="U15">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04407000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.36960740251386</v>
+        <v>7.782856415738937</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08559901390011626</v>
+        <v>0.08533303095966409</v>
       </c>
       <c r="C16">
-        <v>4984.922611220373</v>
+        <v>5005.523953355429</v>
       </c>
       <c r="D16">
-        <v>4962.058611220374</v>
+        <v>4982.659953355429</v>
       </c>
       <c r="E16">
         <v>-2044.064</v>
@@ -2605,37 +2605,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M16">
-        <v>48.42818400000001</v>
+        <v>46.54248480000001</v>
       </c>
       <c r="N16">
-        <v>282.9758976326531</v>
+        <v>284.8615968326531</v>
       </c>
       <c r="O16">
-        <v>62.25469747918369</v>
+        <v>62.66955130318368</v>
       </c>
       <c r="P16">
-        <v>220.7212001534695</v>
+        <v>222.1920455294694</v>
       </c>
       <c r="Q16">
-        <v>444.5212001534695</v>
+        <v>445.9920455294695</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09235955104664681</v>
+        <v>0.09232961739495824</v>
       </c>
       <c r="T16">
         <v>1.074587006811968</v>
       </c>
       <c r="U16">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.84320687376287</v>
+        <v>7.120463874173152</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0854908238149117</v>
+        <v>0.08520773930870321</v>
       </c>
       <c r="C17">
-        <v>4932.882841035977</v>
+        <v>4955.027900937132</v>
       </c>
       <c r="D17">
-        <v>4971.242841035977</v>
+        <v>4993.387900937132</v>
       </c>
       <c r="E17">
         <v>-1982.84</v>
@@ -2687,37 +2687,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M17">
-        <v>51.88734</v>
+        <v>49.866948</v>
       </c>
       <c r="N17">
-        <v>279.5167416326531</v>
+        <v>281.5371336326531</v>
       </c>
       <c r="O17">
-        <v>61.49368315918369</v>
+        <v>61.93816939918369</v>
       </c>
       <c r="P17">
-        <v>218.0230584734694</v>
+        <v>219.5989642334694</v>
       </c>
       <c r="Q17">
-        <v>441.8230584734695</v>
+        <v>443.3989642334694</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09280038095871965</v>
+        <v>0.09277016389259202</v>
       </c>
       <c r="T17">
         <v>1.084761290821987</v>
       </c>
       <c r="U17">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.38699308217868</v>
+        <v>6.645766282561611</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08555735372970713</v>
+        <v>0.08508244765774235</v>
       </c>
       <c r="C18">
-        <v>4866.007112258945</v>
+        <v>4904.57814394652</v>
       </c>
       <c r="D18">
-        <v>4965.591112258945</v>
+        <v>5004.16214394652</v>
       </c>
       <c r="E18">
         <v>-1921.616</v>
@@ -2769,45 +2769,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M18">
-        <v>56.7179136</v>
+        <v>53.1914112</v>
       </c>
       <c r="N18">
-        <v>274.6861680326531</v>
+        <v>278.2126704326531</v>
       </c>
       <c r="O18">
-        <v>60.43095696718368</v>
+        <v>61.20678749518368</v>
       </c>
       <c r="P18">
-        <v>214.2552110654694</v>
+        <v>217.0058829374694</v>
       </c>
       <c r="Q18">
-        <v>438.0552110654694</v>
+        <v>440.8058829374694</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09325170682107993</v>
+        <v>0.09322119959255043</v>
       </c>
       <c r="T18">
         <v>1.095177819689386</v>
       </c>
       <c r="U18">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04516200000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>5.843023140270327</v>
+        <v>6.230405889901509</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08546008364450258</v>
+        <v>0.08508975600678151</v>
       </c>
       <c r="C19">
-        <v>4813.050572116863</v>
+        <v>4842.724398078037</v>
       </c>
       <c r="D19">
-        <v>4973.858572116863</v>
+        <v>5003.532398078037</v>
       </c>
       <c r="E19">
         <v>-1860.392</v>
@@ -2851,37 +2851,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M19">
-        <v>60.26278320000001</v>
+        <v>57.55668240000001</v>
       </c>
       <c r="N19">
-        <v>271.1412984326531</v>
+        <v>273.8473992326531</v>
       </c>
       <c r="O19">
-        <v>59.65108565518369</v>
+        <v>60.24642783118369</v>
       </c>
       <c r="P19">
-        <v>211.4902127774694</v>
+        <v>213.6009714014694</v>
       </c>
       <c r="Q19">
-        <v>435.2902127774694</v>
+        <v>437.4009714014694</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09371390800542481</v>
+        <v>0.09368310362262833</v>
       </c>
       <c r="T19">
         <v>1.105845349252386</v>
       </c>
       <c r="U19">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.499315896725014</v>
+        <v>5.75787324449147</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08536281355929803</v>
+        <v>0.08497226435582066</v>
       </c>
       <c r="C20">
-        <v>4760.121607698012</v>
+        <v>4791.643666436574</v>
       </c>
       <c r="D20">
-        <v>4982.153607698012</v>
+        <v>5013.675666436574</v>
       </c>
       <c r="E20">
         <v>-1799.168</v>
@@ -2933,37 +2933,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M20">
-        <v>63.80765280000001</v>
+        <v>60.94236960000001</v>
       </c>
       <c r="N20">
-        <v>267.5964288326531</v>
+        <v>270.4617120326531</v>
       </c>
       <c r="O20">
-        <v>58.87121434318368</v>
+        <v>59.50157664718368</v>
       </c>
       <c r="P20">
-        <v>208.7252144894694</v>
+        <v>210.9601353854694</v>
       </c>
       <c r="Q20">
-        <v>432.5252144894694</v>
+        <v>434.7601353854694</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09418738238938784</v>
+        <v>0.09415627360465934</v>
       </c>
       <c r="T20">
         <v>1.116773062463264</v>
       </c>
       <c r="U20">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.193798346906957</v>
+        <v>5.437991397575277</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08526554347409347</v>
+        <v>0.0848547727048598</v>
       </c>
       <c r="C21">
-        <v>4707.220357199159</v>
+        <v>4740.604143637571</v>
       </c>
       <c r="D21">
-        <v>4990.476357199159</v>
+        <v>5023.860143637571</v>
       </c>
       <c r="E21">
         <v>-1737.944</v>
@@ -3015,37 +3015,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M21">
-        <v>67.3525224</v>
+        <v>64.3280568</v>
       </c>
       <c r="N21">
-        <v>264.0515592326531</v>
+        <v>267.0760248326531</v>
       </c>
       <c r="O21">
-        <v>58.09134303118368</v>
+        <v>58.75672546318368</v>
       </c>
       <c r="P21">
-        <v>205.9602162014694</v>
+        <v>208.3192993694694</v>
       </c>
       <c r="Q21">
-        <v>429.7602162014695</v>
+        <v>432.1192993694694</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09467254749888082</v>
+        <v>0.0946411267961232</v>
       </c>
       <c r="T21">
         <v>1.127970595753423</v>
       </c>
       <c r="U21">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.920440539175013</v>
+        <v>5.151781324018684</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08516827338888892</v>
+        <v>0.08473728105389895</v>
       </c>
       <c r="C22">
-        <v>4654.346959742046</v>
+        <v>4689.606081319635</v>
       </c>
       <c r="D22">
-        <v>4998.826959742047</v>
+        <v>5034.086081319634</v>
       </c>
       <c r="E22">
         <v>-1676.72</v>
@@ -3097,37 +3097,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M22">
-        <v>70.89739200000001</v>
+        <v>67.71374400000001</v>
       </c>
       <c r="N22">
-        <v>260.5066896326531</v>
+        <v>263.6903376326531</v>
       </c>
       <c r="O22">
-        <v>57.31147171918368</v>
+        <v>58.01187427918368</v>
       </c>
       <c r="P22">
-        <v>203.1952179134694</v>
+        <v>205.6784633534694</v>
       </c>
       <c r="Q22">
-        <v>426.9952179134694</v>
+        <v>429.4784633534695</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09516984173611115</v>
+        <v>0.09513810131737369</v>
       </c>
       <c r="T22">
         <v>1.139448067375836</v>
       </c>
       <c r="U22">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.674418512216262</v>
+        <v>4.89419225781775</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08549688330368437</v>
+        <v>0.08461978940293809</v>
       </c>
       <c r="C23">
-        <v>4565.023553859056</v>
+        <v>4638.649733174365</v>
       </c>
       <c r="D23">
-        <v>4970.727553859056</v>
+        <v>5044.353733174365</v>
       </c>
       <c r="E23">
         <v>-1615.496</v>
@@ -3179,45 +3179,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M23">
-        <v>77.78509200000001</v>
+        <v>71.09943120000001</v>
       </c>
       <c r="N23">
-        <v>253.6189896326531</v>
+        <v>260.3046504326531</v>
       </c>
       <c r="O23">
-        <v>55.79617771918368</v>
+        <v>57.26702309518368</v>
       </c>
       <c r="P23">
-        <v>197.8228119134694</v>
+        <v>203.0376273374694</v>
       </c>
       <c r="Q23">
-        <v>421.6228119134694</v>
+        <v>426.8376273374694</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09567972570086627</v>
+        <v>0.09564765747207352</v>
       </c>
       <c r="T23">
         <v>1.151216107900081</v>
       </c>
       <c r="U23">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04719</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.260508962728399</v>
+        <v>4.661135483635951</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0854198932184798</v>
+        <v>0.08493129775197723</v>
       </c>
       <c r="C24">
-        <v>4510.354595743599</v>
+        <v>4550.294064480369</v>
       </c>
       <c r="D24">
-        <v>4977.282595743599</v>
+        <v>5017.222064480369</v>
       </c>
       <c r="E24">
         <v>-1554.272</v>
@@ -3261,37 +3261,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M24">
-        <v>81.489144</v>
+        <v>77.8524384</v>
       </c>
       <c r="N24">
-        <v>249.9149376326531</v>
+        <v>253.5516432326531</v>
       </c>
       <c r="O24">
-        <v>54.98128627918368</v>
+        <v>55.78136151118369</v>
       </c>
       <c r="P24">
-        <v>194.9336513534694</v>
+        <v>197.7702817214694</v>
       </c>
       <c r="Q24">
-        <v>418.7336513534694</v>
+        <v>421.5702817214694</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09620268361343565</v>
+        <v>0.09617027916920157</v>
       </c>
       <c r="T24">
         <v>1.163285893053154</v>
       </c>
       <c r="U24">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.066849464422563</v>
+        <v>4.256823401341956</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08582728313327524</v>
+        <v>0.08483330610101637</v>
       </c>
       <c r="C25">
-        <v>4414.639793090507</v>
+        <v>4497.573395982321</v>
       </c>
       <c r="D25">
-        <v>4942.791793090507</v>
+        <v>5025.725395982321</v>
       </c>
       <c r="E25">
         <v>-1493.048</v>
@@ -3343,45 +3343,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M25">
-        <v>88.99520640000001</v>
+        <v>81.39118560000001</v>
       </c>
       <c r="N25">
-        <v>242.4088752326531</v>
+        <v>250.0128960326531</v>
       </c>
       <c r="O25">
-        <v>53.32995255118368</v>
+        <v>55.00283712718368</v>
       </c>
       <c r="P25">
-        <v>189.0789226814694</v>
+        <v>195.0100589054694</v>
       </c>
       <c r="Q25">
-        <v>412.8789226814694</v>
+        <v>418.8100589054694</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09673922484840941</v>
+        <v>0.09670647545586541</v>
       </c>
       <c r="T25">
         <v>1.175669179119294</v>
       </c>
       <c r="U25">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04929600000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.723841935296113</v>
+        <v>4.071744123022739</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08577135304807069</v>
+        <v>0.08539051445005552</v>
       </c>
       <c r="C26">
-        <v>4358.122659738896</v>
+        <v>4388.377409157563</v>
       </c>
       <c r="D26">
-        <v>4947.498659738896</v>
+        <v>4977.753409157564</v>
       </c>
       <c r="E26">
         <v>-1431.824</v>
@@ -3425,37 +3425,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M26">
-        <v>92.86456319999999</v>
+        <v>90.0727488</v>
       </c>
       <c r="N26">
-        <v>238.5395184326531</v>
+        <v>241.3313328326531</v>
       </c>
       <c r="O26">
-        <v>52.47869405518369</v>
+        <v>53.09289322318369</v>
       </c>
       <c r="P26">
-        <v>186.0608243774694</v>
+        <v>188.2384396094694</v>
       </c>
       <c r="Q26">
-        <v>409.8608243774694</v>
+        <v>412.0384396094694</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09728988558956669</v>
+        <v>0.09725678217112568</v>
       </c>
       <c r="T26">
         <v>1.188378341134542</v>
       </c>
       <c r="U26">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04929600000000001</v>
+        <v>0.04781400000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.568681854658776</v>
+        <v>3.679293527152278</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08663192296286613</v>
+        <v>0.08531982279909467</v>
       </c>
       <c r="C27">
-        <v>4225.454163733948</v>
+        <v>4333.18871220515</v>
       </c>
       <c r="D27">
-        <v>4876.054163733948</v>
+        <v>4983.788712205151</v>
       </c>
       <c r="E27">
         <v>-1370.6</v>
@@ -3507,45 +3507,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M27">
-        <v>103.92774</v>
+        <v>93.82578000000001</v>
       </c>
       <c r="N27">
-        <v>227.4763416326531</v>
+        <v>237.5783016326531</v>
       </c>
       <c r="O27">
-        <v>50.04479515918368</v>
+        <v>52.26722635918368</v>
       </c>
       <c r="P27">
-        <v>177.4315464734694</v>
+        <v>185.3110752734694</v>
       </c>
       <c r="Q27">
-        <v>401.2315464734694</v>
+        <v>409.1110752734695</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09785523061715484</v>
+        <v>0.09782176373212623</v>
       </c>
       <c r="T27">
         <v>1.201426414136864</v>
       </c>
       <c r="U27">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.05296200000000002</v>
+        <v>0.04781400000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.188793306124554</v>
+        <v>3.532121786066186</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08661265287766159</v>
+        <v>0.08581697114813382</v>
       </c>
       <c r="C28">
-        <v>4165.807373809808</v>
+        <v>4229.828472070334</v>
       </c>
       <c r="D28">
-        <v>4877.631373809809</v>
+        <v>4941.652472070335</v>
       </c>
       <c r="E28">
         <v>-1309.376</v>
@@ -3589,37 +3589,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M28">
-        <v>108.0848496</v>
+        <v>102.0359184</v>
       </c>
       <c r="N28">
-        <v>223.3192320326531</v>
+        <v>229.3681632326531</v>
       </c>
       <c r="O28">
-        <v>49.13023104718368</v>
+        <v>50.46099591118368</v>
       </c>
       <c r="P28">
-        <v>174.1890009854694</v>
+        <v>178.9071673214694</v>
       </c>
       <c r="Q28">
-        <v>397.9890009854694</v>
+        <v>402.7071673214695</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09843585524008322</v>
+        <v>0.09840201506504569</v>
       </c>
       <c r="T28">
         <v>1.21482713776087</v>
       </c>
       <c r="U28">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.05296200000000002</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.066147409735148</v>
+        <v>3.247915898923815</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08855196279245703</v>
+        <v>0.08576811949717296</v>
       </c>
       <c r="C29">
-        <v>3950.809898569566</v>
+        <v>4172.713343556555</v>
       </c>
       <c r="D29">
-        <v>4723.857898569566</v>
+        <v>4945.761343556554</v>
       </c>
       <c r="E29">
         <v>-1248.152</v>
@@ -3671,45 +3671,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M29">
-        <v>127.6153056</v>
+        <v>105.9603768</v>
       </c>
       <c r="N29">
-        <v>203.7887760326531</v>
+        <v>225.4437048326531</v>
       </c>
       <c r="O29">
-        <v>44.83353072718369</v>
+        <v>49.59761506318368</v>
       </c>
       <c r="P29">
-        <v>158.9552453054694</v>
+        <v>175.8460897694694</v>
       </c>
       <c r="Q29">
-        <v>382.7552453054694</v>
+        <v>399.6460897694694</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09903238738692743</v>
+        <v>0.09899816369475747</v>
       </c>
       <c r="T29">
         <v>1.228595004497863</v>
       </c>
       <c r="U29">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.06021600000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.596899173453479</v>
+        <v>3.127622717482193</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08860523270725248</v>
+        <v>0.0857192678462121</v>
       </c>
       <c r="C30">
-        <v>3885.498677428513</v>
+        <v>4115.605053595</v>
       </c>
       <c r="D30">
-        <v>4719.770677428512</v>
+        <v>4949.877053595</v>
       </c>
       <c r="E30">
         <v>-1186.928</v>
@@ -3753,45 +3753,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M30">
-        <v>132.3417984</v>
+        <v>109.8848352</v>
       </c>
       <c r="N30">
-        <v>199.0622832326531</v>
+        <v>221.5192464326531</v>
       </c>
       <c r="O30">
-        <v>43.79370231118368</v>
+        <v>48.73423421518368</v>
       </c>
       <c r="P30">
-        <v>155.2685809214694</v>
+        <v>172.7850122174694</v>
       </c>
       <c r="Q30">
-        <v>379.0685809214694</v>
+        <v>396.5850122174695</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09964548987118399</v>
+        <v>0.09961087200862792</v>
       </c>
       <c r="T30">
         <v>1.24274531197755</v>
       </c>
       <c r="U30">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.06021600000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.504152774401569</v>
+        <v>3.015921906143543</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08972164262204792</v>
+        <v>0.08743477619525125</v>
       </c>
       <c r="C31">
-        <v>3740.21469049352</v>
+        <v>3913.837761429974</v>
       </c>
       <c r="D31">
-        <v>4635.71069049352</v>
+        <v>4809.333761429974</v>
       </c>
       <c r="E31">
         <v>-1125.704</v>
@@ -3835,45 +3835,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M31">
-        <v>145.4131224</v>
+        <v>127.6581624</v>
       </c>
       <c r="N31">
-        <v>185.9909592326531</v>
+        <v>203.7459192326531</v>
       </c>
       <c r="O31">
-        <v>40.91801103118369</v>
+        <v>44.82410223118369</v>
       </c>
       <c r="P31">
-        <v>145.0729482014694</v>
+        <v>158.9218170014694</v>
       </c>
       <c r="Q31">
-        <v>368.8729482014695</v>
+        <v>382.7218170014694</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1002758628479548</v>
+        <v>0.1002408397116215</v>
       </c>
       <c r="T31">
         <v>1.257294219667932</v>
       </c>
       <c r="U31">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.06388200000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.279052097657543</v>
+        <v>2.596027354633558</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08981157253684335</v>
+        <v>0.08744676454429037</v>
       </c>
       <c r="C32">
-        <v>3672.349550677749</v>
+        <v>3851.659689744032</v>
       </c>
       <c r="D32">
-        <v>4629.069550677748</v>
+        <v>4808.379689744032</v>
       </c>
       <c r="E32">
         <v>-1064.48</v>
@@ -3917,45 +3917,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M32">
-        <v>150.427368</v>
+        <v>132.060168</v>
       </c>
       <c r="N32">
-        <v>180.9767136326531</v>
+        <v>199.3439136326531</v>
       </c>
       <c r="O32">
-        <v>39.81487699918369</v>
+        <v>43.85566099918368</v>
       </c>
       <c r="P32">
-        <v>141.1618366334694</v>
+        <v>155.4882526334694</v>
       </c>
       <c r="Q32">
-        <v>364.9618366334695</v>
+        <v>379.2882526334694</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1009242464812048</v>
+        <v>0.1008888064918434</v>
       </c>
       <c r="T32">
         <v>1.272258810435183</v>
       </c>
       <c r="U32">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.06388200000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.203083694402292</v>
+        <v>2.509493109479106</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08990150245163879</v>
+        <v>0.08840177289332952</v>
       </c>
       <c r="C33">
-        <v>3604.503411894067</v>
+        <v>3715.630268171059</v>
       </c>
       <c r="D33">
-        <v>4622.447411894067</v>
+        <v>4733.574268171059</v>
       </c>
       <c r="E33">
         <v>-1003.256</v>
@@ -3999,37 +3999,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M33">
-        <v>155.4416136</v>
+        <v>143.8641552</v>
       </c>
       <c r="N33">
-        <v>175.9624680326531</v>
+        <v>187.5399264326531</v>
       </c>
       <c r="O33">
-        <v>38.71174296718368</v>
+        <v>41.25878381518368</v>
       </c>
       <c r="P33">
-        <v>137.2507250654694</v>
+        <v>146.2811426174694</v>
       </c>
       <c r="Q33">
-        <v>361.0507250654695</v>
+        <v>370.0811426174695</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1015914238429548</v>
+        <v>0.1015555549178689</v>
       </c>
       <c r="T33">
         <v>1.287657157456556</v>
       </c>
       <c r="U33">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.06388200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.132016478453831</v>
+        <v>2.303590363923071</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08999143236643424</v>
+        <v>0.08844418124236868</v>
       </c>
       <c r="C34">
-        <v>3536.676192712899</v>
+        <v>3651.138375470006</v>
       </c>
       <c r="D34">
-        <v>4615.844192712899</v>
+        <v>4730.306375470006</v>
       </c>
       <c r="E34">
         <v>-942.0319999999999</v>
@@ -4081,37 +4081,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M34">
-        <v>160.4558592</v>
+        <v>148.5049344</v>
       </c>
       <c r="N34">
-        <v>170.9482224326531</v>
+        <v>182.8991472326531</v>
       </c>
       <c r="O34">
-        <v>37.60860893518369</v>
+        <v>40.23781239118369</v>
       </c>
       <c r="P34">
-        <v>133.3396134974694</v>
+        <v>142.6613348414694</v>
       </c>
       <c r="Q34">
-        <v>357.1396134974694</v>
+        <v>366.4613348414695</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1022782240682857</v>
+        <v>0.1022419135917187</v>
       </c>
       <c r="T34">
         <v>1.303508397037382</v>
       </c>
       <c r="U34">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.06388200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.065390963502149</v>
+        <v>2.231603165050475</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09008136228122968</v>
+        <v>0.08848658959140782</v>
       </c>
       <c r="C35">
-        <v>3468.867812169296</v>
+        <v>3586.650991731822</v>
       </c>
       <c r="D35">
-        <v>4609.259812169296</v>
+        <v>4727.042991731822</v>
       </c>
       <c r="E35">
         <v>-880.8079999999998</v>
@@ -4163,37 +4163,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M35">
-        <v>165.4701048</v>
+        <v>153.1457136</v>
       </c>
       <c r="N35">
-        <v>165.9339768326531</v>
+        <v>178.2583680326531</v>
       </c>
       <c r="O35">
-        <v>36.50547490318369</v>
+        <v>39.21684096718368</v>
       </c>
       <c r="P35">
-        <v>129.4285019294694</v>
+        <v>139.0415270654694</v>
       </c>
       <c r="Q35">
-        <v>353.2285019294694</v>
+        <v>362.8415270654694</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1029855257928801</v>
+        <v>0.1029487605841908</v>
       </c>
       <c r="T35">
         <v>1.319832807948979</v>
       </c>
       <c r="U35">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.06388200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.002803358547538</v>
+        <v>2.163978826715612</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09449405219602512</v>
+        <v>0.08852899794044697</v>
       </c>
       <c r="C36">
-        <v>3106.126180610079</v>
+        <v>3522.168107630893</v>
       </c>
       <c r="D36">
-        <v>4307.742180610079</v>
+        <v>4723.784107630893</v>
       </c>
       <c r="E36">
         <v>-819.5839999999998</v>
@@ -4245,45 +4245,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M36">
-        <v>204.4146912</v>
+        <v>157.7864928</v>
       </c>
       <c r="N36">
-        <v>126.9893904326531</v>
+        <v>173.6175888326531</v>
       </c>
       <c r="O36">
-        <v>27.93766589518368</v>
+        <v>38.19586954318368</v>
       </c>
       <c r="P36">
-        <v>99.05172453746941</v>
+        <v>135.4217192894694</v>
       </c>
       <c r="Q36">
-        <v>322.8517245374694</v>
+        <v>359.2217192894694</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1037142609030684</v>
+        <v>0.1036770271824954</v>
       </c>
       <c r="T36">
         <v>1.336651897979109</v>
       </c>
       <c r="U36">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.07659600000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.621234167109869</v>
+        <v>2.100332390635741</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09471112211082057</v>
+        <v>0.08857140628948611</v>
       </c>
       <c r="C37">
-        <v>3031.084595019502</v>
+        <v>3457.68971386731</v>
       </c>
       <c r="D37">
-        <v>4293.924595019502</v>
+        <v>4720.52971386731</v>
       </c>
       <c r="E37">
         <v>-758.3599999999997</v>
@@ -4327,45 +4327,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M37">
-        <v>210.426888</v>
+        <v>162.427272</v>
       </c>
       <c r="N37">
-        <v>120.9771936326531</v>
+        <v>168.9768096326531</v>
       </c>
       <c r="O37">
-        <v>26.61498259918368</v>
+        <v>37.17489811918368</v>
       </c>
       <c r="P37">
-        <v>94.36221103346939</v>
+        <v>131.8019115134694</v>
       </c>
       <c r="Q37">
-        <v>318.1622110334694</v>
+        <v>355.6019115134694</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1044654186320317</v>
+        <v>0.1044277019838248</v>
       </c>
       <c r="T37">
         <v>1.353988498471704</v>
       </c>
       <c r="U37">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.07659600000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.57491319090673</v>
+        <v>2.040322893760434</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09492819202561602</v>
+        <v>0.09260117463852525</v>
       </c>
       <c r="C38">
-        <v>2956.131369040676</v>
+        <v>3106.424077744265</v>
       </c>
       <c r="D38">
-        <v>4280.195369040676</v>
+        <v>4430.488077744265</v>
       </c>
       <c r="E38">
         <v>-697.136</v>
@@ -4409,37 +4409,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M38">
-        <v>216.4390848</v>
+        <v>198.36576</v>
       </c>
       <c r="N38">
-        <v>114.9649968326531</v>
+        <v>133.0383216326531</v>
       </c>
       <c r="O38">
-        <v>25.29229930318368</v>
+        <v>29.26843075918368</v>
       </c>
       <c r="P38">
-        <v>89.67269752946942</v>
+        <v>103.7698908734694</v>
       </c>
       <c r="Q38">
-        <v>313.4726975294694</v>
+        <v>327.5698908734694</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.105240050040025</v>
+        <v>0.1052018353726957</v>
       </c>
       <c r="T38">
         <v>1.371866867729693</v>
       </c>
       <c r="U38">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.07659600000000001</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.531165602270432</v>
+        <v>1.670671801588405</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1157838776663159</v>
+        <v>0.09275434298756441</v>
       </c>
       <c r="C39">
-        <v>1889.04365262889</v>
+        <v>3034.877288274719</v>
       </c>
       <c r="D39">
-        <v>3274.33165262889</v>
+        <v>4420.165288274719</v>
       </c>
       <c r="E39">
         <v>-635.9119999999998</v>
@@ -4491,45 +4491,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M39">
-        <v>370.6011168000001</v>
+        <v>203.87592</v>
       </c>
       <c r="N39">
-        <v>-39.19703516734694</v>
+        <v>127.5281616326531</v>
       </c>
       <c r="O39">
-        <v>-8.623347736816326</v>
+        <v>28.05619555918368</v>
       </c>
       <c r="P39">
-        <v>-30.57368743053061</v>
+        <v>99.4719660734694</v>
       </c>
       <c r="Q39">
-        <v>193.2263125694694</v>
+        <v>323.2719660734694</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.106603851219108</v>
+        <v>0.1060005444247054</v>
       </c>
       <c r="T39">
-        <v>1.403343181267363</v>
+        <v>1.390312804265714</v>
       </c>
       <c r="U39">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V39">
-        <v>0.1967314577698101</v>
+        <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.1314147335088591</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8942338989536824</v>
+        <v>1.625518509653583</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1169618776663159</v>
+        <v>0.09290751133660355</v>
       </c>
       <c r="C40">
-        <v>1784.926081338871</v>
+        <v>2963.378490032731</v>
       </c>
       <c r="D40">
-        <v>3231.43808133887</v>
+        <v>4409.890490032731</v>
       </c>
       <c r="E40">
         <v>-574.6880000000001</v>
@@ -4573,45 +4573,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M40">
-        <v>380.6173632</v>
+        <v>209.38608</v>
       </c>
       <c r="N40">
-        <v>-49.21328156734688</v>
+        <v>122.0180016326531</v>
       </c>
       <c r="O40">
-        <v>-10.82692194481631</v>
+        <v>26.84396035918369</v>
       </c>
       <c r="P40">
-        <v>-38.38635962253057</v>
+        <v>95.17404127346944</v>
       </c>
       <c r="Q40">
-        <v>185.4136403774694</v>
+        <v>318.9740412734694</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1075845584968355</v>
+        <v>0.1068250182848444</v>
       </c>
       <c r="T40">
-        <v>1.425977748707159</v>
+        <v>1.409353771012573</v>
       </c>
       <c r="U40">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V40">
-        <v>0.1915543141442888</v>
+        <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.1322617142059944</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.8707014279285856</v>
+        <v>1.582741706767962</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1181398776663159</v>
+        <v>0.09306067968564269</v>
       </c>
       <c r="C41">
-        <v>1681.917785623353</v>
+        <v>2891.927349123583</v>
       </c>
       <c r="D41">
-        <v>3189.653785623353</v>
+        <v>4399.663349123583</v>
       </c>
       <c r="E41">
         <v>-513.4639999999999</v>
@@ -4655,45 +4655,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M41">
-        <v>390.6336096000001</v>
+        <v>214.89624</v>
       </c>
       <c r="N41">
-        <v>-59.22952796734694</v>
+        <v>116.5078416326531</v>
       </c>
       <c r="O41">
-        <v>-13.03049615281633</v>
+        <v>25.63172515918368</v>
       </c>
       <c r="P41">
-        <v>-46.19903181453061</v>
+        <v>90.87611647346942</v>
       </c>
       <c r="Q41">
-        <v>177.6009681854694</v>
+        <v>314.6761164734694</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1085974201115378</v>
+        <v>0.1076765240748241</v>
       </c>
       <c r="T41">
-        <v>1.449354433112195</v>
+        <v>1.429019031751134</v>
       </c>
       <c r="U41">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V41">
-        <v>0.186642665063666</v>
+        <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.1330652599955843</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8483757502893911</v>
+        <v>1.542158586081604</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1193178776663159</v>
+        <v>0.09321384803468184</v>
       </c>
       <c r="C42">
-        <v>1579.976284135251</v>
+        <v>2820.523534742778</v>
       </c>
       <c r="D42">
-        <v>3148.936284135251</v>
+        <v>4389.483534742778</v>
       </c>
       <c r="E42">
         <v>-452.2399999999998</v>
@@ -4737,45 +4737,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M42">
-        <v>400.6498560000001</v>
+        <v>220.4064</v>
       </c>
       <c r="N42">
-        <v>-69.24577436734694</v>
+        <v>110.9976816326531</v>
       </c>
       <c r="O42">
-        <v>-15.23407036081633</v>
+        <v>24.41948995918368</v>
       </c>
       <c r="P42">
-        <v>-54.01170400653061</v>
+        <v>86.57819167346942</v>
       </c>
       <c r="Q42">
-        <v>169.7882959934694</v>
+        <v>310.3781916734694</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1096440437800634</v>
+        <v>0.1085564133911364</v>
       </c>
       <c r="T42">
-        <v>1.473510340330731</v>
+        <v>1.449339801180979</v>
       </c>
       <c r="U42">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V42">
-        <v>0.1819765984370744</v>
+        <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.1338286284956947</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8271663565321563</v>
+        <v>1.503604621429564</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1204958776663159</v>
+        <v>0.113239317483897</v>
       </c>
       <c r="C43">
-        <v>1479.061237367105</v>
+        <v>1739.845246610926</v>
       </c>
       <c r="D43">
-        <v>3109.245237367105</v>
+        <v>3370.029246610926</v>
       </c>
       <c r="E43">
         <v>-391.0159999999996</v>
@@ -4819,37 +4819,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M43">
-        <v>410.6661024000001</v>
+        <v>368.4950112000001</v>
       </c>
       <c r="N43">
-        <v>-79.262020767347</v>
+        <v>-37.09092956734696</v>
       </c>
       <c r="O43">
-        <v>-17.43764456881634</v>
+        <v>-8.160004504816332</v>
       </c>
       <c r="P43">
-        <v>-61.82437619853066</v>
+        <v>-28.93092506253063</v>
       </c>
       <c r="Q43">
-        <v>161.9756238014693</v>
+        <v>194.8690749374694</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1107261462170136</v>
+        <v>0.1101014679417273</v>
       </c>
       <c r="T43">
-        <v>1.498485091861761</v>
+        <v>1.485022354312409</v>
       </c>
       <c r="U43">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1775381448166579</v>
+        <v>0.197855861662161</v>
       </c>
       <c r="W43">
-        <v>0.1345547595079948</v>
+        <v>0.1177547595079948</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.806991567348445</v>
+        <v>0.8993448257370955</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1443253030076596</v>
+        <v>0.114249317483897</v>
       </c>
       <c r="C44">
-        <v>786.1283425155157</v>
+        <v>1639.602882944711</v>
       </c>
       <c r="D44">
-        <v>2477.536342515516</v>
+        <v>3331.01088294471</v>
       </c>
       <c r="E44">
         <v>-329.7919999999999</v>
@@ -4901,45 +4901,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M44">
-        <v>554.9098464</v>
+        <v>377.4826944</v>
       </c>
       <c r="N44">
-        <v>-223.5057647673469</v>
+        <v>-46.0786127673469</v>
       </c>
       <c r="O44">
-        <v>-49.17126824881631</v>
+        <v>-10.13729480881632</v>
       </c>
       <c r="P44">
-        <v>-174.3344965185306</v>
+        <v>-35.94131795853058</v>
       </c>
       <c r="Q44">
-        <v>49.46550348146945</v>
+        <v>187.8586820414694</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1130997441541065</v>
+        <v>0.1112101139407226</v>
       </c>
       <c r="T44">
-        <v>1.553267353401186</v>
+        <v>1.510626188007451</v>
       </c>
       <c r="U44">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1313887263529078</v>
+        <v>0.193145007813062</v>
       </c>
       <c r="W44">
-        <v>0.1874463128530425</v>
+        <v>0.1184463128530425</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5972214834223081</v>
+        <v>0.8779318536957362</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1460253030076596</v>
+        <v>0.115259317483897</v>
       </c>
       <c r="C45">
-        <v>689.5072340002475</v>
+        <v>1540.253691141862</v>
       </c>
       <c r="D45">
-        <v>2442.139234000247</v>
+        <v>3292.885691141862</v>
       </c>
       <c r="E45">
         <v>-268.5680000000002</v>
@@ -4983,45 +4983,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M45">
-        <v>568.1219856</v>
+        <v>386.4703776</v>
       </c>
       <c r="N45">
-        <v>-236.7179039673469</v>
+        <v>-55.06629596734689</v>
       </c>
       <c r="O45">
-        <v>-52.07793887281632</v>
+        <v>-12.11458511281632</v>
       </c>
       <c r="P45">
-        <v>-184.6399650945306</v>
+        <v>-42.95171085453057</v>
       </c>
       <c r="Q45">
-        <v>39.16003490546944</v>
+        <v>180.8482891454694</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.114280441419968</v>
+        <v>0.1123576597993318</v>
       </c>
       <c r="T45">
-        <v>1.580517657846821</v>
+        <v>1.537128401832143</v>
       </c>
       <c r="U45">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1283331745772588</v>
+        <v>0.1886532634453164</v>
       </c>
       <c r="W45">
-        <v>0.1881057009262276</v>
+        <v>0.1191057009262276</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5833326117148125</v>
+        <v>0.8575148338423471</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1477253030076596</v>
+        <v>0.116269317483897</v>
       </c>
       <c r="C46">
-        <v>593.8833307955506</v>
+        <v>1441.767349765802</v>
       </c>
       <c r="D46">
-        <v>2407.73933079555</v>
+        <v>3255.623349765801</v>
       </c>
       <c r="E46">
         <v>-207.3440000000001</v>
@@ -5065,45 +5065,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M46">
-        <v>581.3341248</v>
+        <v>395.4580608</v>
       </c>
       <c r="N46">
-        <v>-249.9300431673469</v>
+        <v>-64.05397916734688</v>
       </c>
       <c r="O46">
-        <v>-54.98460949681633</v>
+        <v>-14.09187541681631</v>
       </c>
       <c r="P46">
-        <v>-194.9454336705306</v>
+        <v>-49.96210375053057</v>
       </c>
       <c r="Q46">
-        <v>28.85456632946941</v>
+        <v>173.8378962494695</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1155033064453246</v>
+        <v>0.1135461894386056</v>
       </c>
       <c r="T46">
-        <v>1.608741187451229</v>
+        <v>1.564577123293431</v>
       </c>
       <c r="U46">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1254165115186847</v>
+        <v>0.1843656892761046</v>
       </c>
       <c r="W46">
-        <v>0.1887351168142679</v>
+        <v>0.1197351168142679</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5700750523576577</v>
+        <v>0.8380258603459301</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1494253030076596</v>
+        <v>0.117279317483897</v>
       </c>
       <c r="C47">
-        <v>499.2150784204464</v>
+        <v>1344.114894494064</v>
       </c>
       <c r="D47">
-        <v>2374.295078420446</v>
+        <v>3219.194894494064</v>
       </c>
       <c r="E47">
         <v>-146.1199999999999</v>
@@ -5147,45 +5147,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M47">
-        <v>594.5462640000001</v>
+        <v>404.445744</v>
       </c>
       <c r="N47">
-        <v>-263.1421823673469</v>
+        <v>-73.04166236734693</v>
       </c>
       <c r="O47">
-        <v>-57.89128012081633</v>
+        <v>-16.06916572081633</v>
       </c>
       <c r="P47">
-        <v>-205.2509022465306</v>
+        <v>-56.9724966465306</v>
       </c>
       <c r="Q47">
-        <v>18.5490977534694</v>
+        <v>166.8275033534694</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.116770639289785</v>
+        <v>0.1147779383374893</v>
       </c>
       <c r="T47">
-        <v>1.637991027223069</v>
+        <v>1.593023980080585</v>
       </c>
       <c r="U47">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1226294779293806</v>
+        <v>0.1802686739588578</v>
       </c>
       <c r="W47">
-        <v>0.1893365586628397</v>
+        <v>0.1203365586628397</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.5574067178608209</v>
+        <v>0.8194030634493538</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1511253030076596</v>
+        <v>0.118289317483897</v>
       </c>
       <c r="C48">
-        <v>405.4631995820464</v>
+        <v>1247.268643032033</v>
       </c>
       <c r="D48">
-        <v>2341.767199582046</v>
+        <v>3183.572643032033</v>
       </c>
       <c r="E48">
         <v>-84.89599999999973</v>
@@ -5229,45 +5229,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M48">
-        <v>607.7584032000001</v>
+        <v>413.4334272</v>
       </c>
       <c r="N48">
-        <v>-276.354321567347</v>
+        <v>-82.02934556734692</v>
       </c>
       <c r="O48">
-        <v>-60.79795074481633</v>
+        <v>-18.04645602481632</v>
       </c>
       <c r="P48">
-        <v>-215.5563708225307</v>
+        <v>-63.9828895425306</v>
       </c>
       <c r="Q48">
-        <v>8.243629177469359</v>
+        <v>159.8171104574694</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.118084910387744</v>
+        <v>0.1160553075659613</v>
       </c>
       <c r="T48">
-        <v>1.668324194393867</v>
+        <v>1.622524424156151</v>
       </c>
       <c r="U48">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1199636197135245</v>
+        <v>0.1763497897423609</v>
       </c>
       <c r="W48">
-        <v>0.1899118508658214</v>
+        <v>0.1209118508658214</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5452891805160203</v>
+        <v>0.8015899533743678</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1528253030076596</v>
+        <v>0.1455800116638015</v>
       </c>
       <c r="C49">
-        <v>312.5905402961585</v>
+        <v>453.2642998099022</v>
       </c>
       <c r="D49">
-        <v>2310.118540296158</v>
+        <v>2450.792299809902</v>
       </c>
       <c r="E49">
         <v>-23.67200000000003</v>
@@ -5311,37 +5311,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M49">
-        <v>620.9705424</v>
+        <v>577.8076224</v>
       </c>
       <c r="N49">
-        <v>-289.5664607673469</v>
+        <v>-246.4035407673469</v>
       </c>
       <c r="O49">
-        <v>-63.70462136881631</v>
+        <v>-54.20877896881632</v>
       </c>
       <c r="P49">
-        <v>-225.8618393985306</v>
+        <v>-192.1947617985306</v>
       </c>
       <c r="Q49">
-        <v>-2.061839398530566</v>
+        <v>31.60523820146943</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.119448776621475</v>
+        <v>0.1190803023877805</v>
       </c>
       <c r="T49">
-        <v>1.69980200938243</v>
+        <v>1.692385736438349</v>
       </c>
       <c r="U49">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1174112022728112</v>
+        <v>0.1261819594147045</v>
       </c>
       <c r="W49">
-        <v>0.1904626625495273</v>
+        <v>0.1754626625495274</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5336872830582328</v>
+        <v>0.5735543609759294</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1545253030076596</v>
+        <v>0.1471300116638015</v>
       </c>
       <c r="C50">
-        <v>220.5619283194274</v>
+        <v>360.4144709191428</v>
       </c>
       <c r="D50">
-        <v>2279.313928319427</v>
+        <v>2419.166470919142</v>
       </c>
       <c r="E50">
         <v>37.55199999999968</v>
@@ -5393,37 +5393,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M50">
-        <v>634.1826815999999</v>
+        <v>590.1014015999999</v>
       </c>
       <c r="N50">
-        <v>-302.7785999673468</v>
+        <v>-258.6973199673468</v>
       </c>
       <c r="O50">
-        <v>-66.61129199281629</v>
+        <v>-56.9134103928163</v>
       </c>
       <c r="P50">
-        <v>-236.1673079745305</v>
+        <v>-201.7839095745305</v>
       </c>
       <c r="Q50">
-        <v>-12.36730797453049</v>
+        <v>22.01609042546951</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1208650992488111</v>
+        <v>0.1204895389721609</v>
       </c>
       <c r="T50">
-        <v>1.732490509562862</v>
+        <v>1.72493161598524</v>
       </c>
       <c r="U50">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1149651355587943</v>
+        <v>0.1235531685935648</v>
       </c>
       <c r="W50">
-        <v>0.1909905237464122</v>
+        <v>0.1759905237464122</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5225687979945197</v>
+        <v>0.561605311788931</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1562253030076596</v>
+        <v>0.1486800116638015</v>
       </c>
       <c r="C51">
-        <v>129.3440427589949</v>
+        <v>268.3704636113503</v>
       </c>
       <c r="D51">
-        <v>2249.320042758995</v>
+        <v>2388.34646361135</v>
       </c>
       <c r="E51">
         <v>98.77599999999984</v>
@@ -5475,37 +5475,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M51">
-        <v>647.3948207999999</v>
+        <v>602.3951807999999</v>
       </c>
       <c r="N51">
-        <v>-315.9907391673468</v>
+        <v>-270.9910991673468</v>
       </c>
       <c r="O51">
-        <v>-69.51796261681631</v>
+        <v>-59.6180418168163</v>
       </c>
       <c r="P51">
-        <v>-246.4727765505305</v>
+        <v>-211.3730573505305</v>
       </c>
       <c r="Q51">
-        <v>-22.6727765505305</v>
+        <v>12.42694264946948</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1223369639399642</v>
+        <v>0.1219540397363209</v>
       </c>
       <c r="T51">
-        <v>1.766460911711153</v>
+        <v>1.75875380453397</v>
       </c>
       <c r="U51">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1126189083024924</v>
+        <v>0.1210316753569615</v>
       </c>
       <c r="W51">
-        <v>0.1914968395883221</v>
+        <v>0.1764968395883221</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5119041286476926</v>
+        <v>0.5501439788952793</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1579253030076596</v>
+        <v>0.1502300116638015</v>
       </c>
       <c r="C52">
-        <v>38.9052938434088</v>
+        <v>177.1018669916516</v>
       </c>
       <c r="D52">
-        <v>2220.105293843409</v>
+        <v>2358.301866991651</v>
       </c>
       <c r="E52">
         <v>160</v>
@@ -5557,37 +5557,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M52">
-        <v>660.6069600000001</v>
+        <v>614.68896</v>
       </c>
       <c r="N52">
-        <v>-329.202878367347</v>
+        <v>-283.2848783673468</v>
       </c>
       <c r="O52">
-        <v>-72.42463324081633</v>
+        <v>-62.32267324081631</v>
       </c>
       <c r="P52">
-        <v>-256.7782451265306</v>
+        <v>-220.9622051265305</v>
       </c>
       <c r="Q52">
-        <v>-32.97824512653062</v>
+        <v>2.837794873469477</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1238677032187635</v>
+        <v>0.1234771205310473</v>
       </c>
       <c r="T52">
-        <v>1.801790129945376</v>
+        <v>1.79392888062465</v>
       </c>
       <c r="U52">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1103665301364425</v>
+        <v>0.1186110418498222</v>
       </c>
       <c r="W52">
-        <v>0.1919829027965557</v>
+        <v>0.1769829027965557</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5016660460747387</v>
+        <v>0.5391410993173738</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1752035564840955</v>
+        <v>0.1517800116638015</v>
       </c>
       <c r="C53">
-        <v>-281.2149308592361</v>
+        <v>86.57978138986437</v>
       </c>
       <c r="D53">
-        <v>1961.209069140764</v>
+        <v>2329.003781389864</v>
       </c>
       <c r="E53">
         <v>221.2240000000002</v>
@@ -5639,45 +5639,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M53">
-        <v>767.4918192</v>
+        <v>626.9827392</v>
       </c>
       <c r="N53">
-        <v>-436.0877375673469</v>
+        <v>-295.5786575673469</v>
       </c>
       <c r="O53">
-        <v>-95.93930226481632</v>
+        <v>-65.02730466481631</v>
       </c>
       <c r="P53">
-        <v>-340.1484353025306</v>
+        <v>-230.5513529025305</v>
       </c>
       <c r="Q53">
-        <v>-116.3484353025306</v>
+        <v>-6.751352902530527</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1260287858894238</v>
+        <v>0.1250623678888238</v>
       </c>
       <c r="T53">
-        <v>1.851667573054986</v>
+        <v>1.830539674106786</v>
       </c>
       <c r="U53">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09499631935514406</v>
+        <v>0.1162853351468845</v>
       </c>
       <c r="W53">
-        <v>0.2224499047025056</v>
+        <v>0.1774499047025056</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.4318014516142912</v>
+        <v>0.5285697052131114</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1772035564840955</v>
+        <v>0.1533300116638015</v>
       </c>
       <c r="C54">
-        <v>-368.5595294493978</v>
+        <v>-3.223274360211235</v>
       </c>
       <c r="D54">
-        <v>1935.088470550602</v>
+        <v>2300.424725639789</v>
       </c>
       <c r="E54">
         <v>282.4480000000003</v>
@@ -5721,45 +5721,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M54">
-        <v>782.5406784</v>
+        <v>639.2765184000001</v>
       </c>
       <c r="N54">
-        <v>-451.1365967673469</v>
+        <v>-307.872436767347</v>
       </c>
       <c r="O54">
-        <v>-99.25005128881632</v>
+        <v>-67.73193608881634</v>
       </c>
       <c r="P54">
-        <v>-351.8865454785306</v>
+        <v>-240.1405006785307</v>
       </c>
       <c r="Q54">
-        <v>-128.0865454785306</v>
+        <v>-16.34050067853065</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1277002189287868</v>
+        <v>0.126713667219841</v>
       </c>
       <c r="T54">
-        <v>1.890243980826964</v>
+        <v>1.868675917317344</v>
       </c>
       <c r="U54">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.09316946705985282</v>
+        <v>0.1140490787017521</v>
       </c>
       <c r="W54">
-        <v>0.2228989449966882</v>
+        <v>0.1778989449966882</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.4234975775447856</v>
+        <v>0.5184049031897823</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1792035564840955</v>
+        <v>0.1548800116638015</v>
       </c>
       <c r="C55">
-        <v>-455.2174924181159</v>
+        <v>-92.33344889763111</v>
       </c>
       <c r="D55">
-        <v>1909.654507581884</v>
+        <v>2272.538551102369</v>
       </c>
       <c r="E55">
         <v>343.672</v>
@@ -5803,45 +5803,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M55">
-        <v>797.5895376</v>
+        <v>651.5702976</v>
       </c>
       <c r="N55">
-        <v>-466.1854559673469</v>
+        <v>-320.1662159673469</v>
       </c>
       <c r="O55">
-        <v>-102.5608003128163</v>
+        <v>-70.43656751281631</v>
       </c>
       <c r="P55">
-        <v>-363.6246556545306</v>
+        <v>-249.7296484545306</v>
       </c>
       <c r="Q55">
-        <v>-139.8246556545305</v>
+        <v>-25.92964845453056</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1294427767783355</v>
+        <v>0.1284352346074972</v>
       </c>
       <c r="T55">
-        <v>1.930461937865836</v>
+        <v>1.908434979387926</v>
       </c>
       <c r="U55">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.09141155258702542</v>
+        <v>0.1118972092922851</v>
       </c>
       <c r="W55">
-        <v>0.2233310403741092</v>
+        <v>0.1783310403741092</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.4155070572137519</v>
+        <v>0.5086236786012959</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1812035564840955</v>
+        <v>0.1756934526445722</v>
       </c>
       <c r="C56">
-        <v>-541.2155430479238</v>
+        <v>-471.6898621722935</v>
       </c>
       <c r="D56">
-        <v>1884.880456952076</v>
+        <v>1954.406137827707</v>
       </c>
       <c r="E56">
         <v>404.8960000000002</v>
@@ -5885,37 +5885,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M56">
-        <v>812.6383968</v>
+        <v>779.5774368</v>
       </c>
       <c r="N56">
-        <v>-481.2343151673469</v>
+        <v>-448.1733551673469</v>
       </c>
       <c r="O56">
-        <v>-105.8715493368163</v>
+        <v>-98.59813813681632</v>
       </c>
       <c r="P56">
-        <v>-375.3627658305306</v>
+        <v>-349.5752170305306</v>
       </c>
       <c r="Q56">
-        <v>-151.5627658305306</v>
+        <v>-125.7752170305305</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1312610980126471</v>
+        <v>0.1310217418397704</v>
       </c>
       <c r="T56">
-        <v>1.972428501732485</v>
+        <v>1.968169557500471</v>
       </c>
       <c r="U56">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08971874605763606</v>
+        <v>0.09352361230265879</v>
       </c>
       <c r="W56">
-        <v>0.2237471322190331</v>
+        <v>0.213747132219033</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4078124820801639</v>
+        <v>0.425107328648449</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1832035564840955</v>
+        <v>0.1775934526445722</v>
       </c>
       <c r="C57">
-        <v>-626.5790356507609</v>
+        <v>-557.5746181628988</v>
       </c>
       <c r="D57">
-        <v>1860.740964349239</v>
+        <v>1929.745381837101</v>
       </c>
       <c r="E57">
         <v>466.1200000000003</v>
@@ -5967,37 +5967,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M57">
-        <v>827.687256</v>
+        <v>794.0140560000001</v>
       </c>
       <c r="N57">
-        <v>-496.2831743673469</v>
+        <v>-462.609974367347</v>
       </c>
       <c r="O57">
-        <v>-109.1822983608163</v>
+        <v>-101.7741943608163</v>
       </c>
       <c r="P57">
-        <v>-387.1008760065306</v>
+        <v>-360.8357800065306</v>
       </c>
       <c r="Q57">
-        <v>-163.3008760065306</v>
+        <v>-137.0357800065306</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1331602335240393</v>
+        <v>0.1329155583250986</v>
       </c>
       <c r="T57">
-        <v>2.016260246215429</v>
+        <v>2.011906658778259</v>
       </c>
       <c r="U57">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08808749612931539</v>
+        <v>0.09182318298806499</v>
       </c>
       <c r="W57">
-        <v>0.2241480934514143</v>
+        <v>0.2141480934514143</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4003977096787064</v>
+        <v>0.4173781044912045</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1852035564840955</v>
+        <v>0.1794934526445722</v>
       </c>
       <c r="C58">
-        <v>-711.332042120901</v>
+        <v>-642.8447886759463</v>
       </c>
       <c r="D58">
-        <v>1837.211957879099</v>
+        <v>1905.699211324054</v>
       </c>
       <c r="E58">
         <v>527.3440000000005</v>
@@ -6049,37 +6049,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M58">
-        <v>842.7361152000002</v>
+        <v>808.4506752000001</v>
       </c>
       <c r="N58">
-        <v>-511.3320335673471</v>
+        <v>-477.046593567347</v>
       </c>
       <c r="O58">
-        <v>-112.4930473848164</v>
+        <v>-104.9502505848163</v>
       </c>
       <c r="P58">
-        <v>-398.8389861825307</v>
+        <v>-372.0963429825306</v>
       </c>
       <c r="Q58">
-        <v>-175.0389861825307</v>
+        <v>-148.2963429825306</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1351456933768583</v>
+        <v>0.1348954573779418</v>
       </c>
       <c r="T58">
-        <v>2.062084342720325</v>
+        <v>2.057631810114129</v>
       </c>
       <c r="U58">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08651450512700619</v>
+        <v>0.09018348329184954</v>
       </c>
       <c r="W58">
-        <v>0.2245347346397819</v>
+        <v>0.2145347346397819</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3932477505773008</v>
+        <v>0.4099249240538615</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1872035564840955</v>
+        <v>0.1813934526445722</v>
       </c>
       <c r="C59">
-        <v>-795.4974320031365</v>
+        <v>-727.5230656314166</v>
       </c>
       <c r="D59">
-        <v>1814.270567996864</v>
+        <v>1882.244934368583</v>
       </c>
       <c r="E59">
         <v>588.5680000000002</v>
@@ -6131,37 +6131,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M59">
-        <v>857.7849744000001</v>
+        <v>822.8872944000001</v>
       </c>
       <c r="N59">
-        <v>-526.3808927673469</v>
+        <v>-491.483212767347</v>
       </c>
       <c r="O59">
-        <v>-115.8037964088163</v>
+        <v>-108.1263068088163</v>
       </c>
       <c r="P59">
-        <v>-410.5770963585306</v>
+        <v>-383.3569059585307</v>
       </c>
       <c r="Q59">
-        <v>-186.7770963585306</v>
+        <v>-159.5569059585306</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.137223500199576</v>
+        <v>0.1369674447588242</v>
       </c>
       <c r="T59">
-        <v>2.110039792551031</v>
+        <v>2.105483712674923</v>
       </c>
       <c r="U59">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08499670679144468</v>
+        <v>0.08860131691830832</v>
       </c>
       <c r="W59">
-        <v>0.2249078094706629</v>
+        <v>0.2149078094706629</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3863486672338395</v>
+        <v>0.4027332587195833</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1892035564840955</v>
+        <v>0.1832934526445722</v>
       </c>
       <c r="C60">
-        <v>-879.0969466360407</v>
+        <v>-811.6310374132991</v>
       </c>
       <c r="D60">
-        <v>1791.895053363959</v>
+        <v>1859.360962586701</v>
       </c>
       <c r="E60">
         <v>649.7919999999999</v>
@@ -6213,37 +6213,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M60">
-        <v>872.8338336</v>
+        <v>837.3239136</v>
       </c>
       <c r="N60">
-        <v>-541.4297519673469</v>
+        <v>-505.9198319673469</v>
       </c>
       <c r="O60">
-        <v>-119.1145454328163</v>
+        <v>-111.3023630328163</v>
       </c>
       <c r="P60">
-        <v>-422.3152065345305</v>
+        <v>-394.6174689345306</v>
       </c>
       <c r="Q60">
-        <v>-198.5152065345305</v>
+        <v>-170.8174689345306</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1394002502043278</v>
+        <v>0.1391380982054628</v>
       </c>
       <c r="T60">
-        <v>2.160278835230816</v>
+        <v>2.15561427726242</v>
       </c>
       <c r="U60">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08353124632952322</v>
+        <v>0.08707370800592371</v>
       </c>
       <c r="W60">
-        <v>0.2252680196522032</v>
+        <v>0.2152680196522032</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3796874833160147</v>
+        <v>0.3957895818451077</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1912035564840955</v>
+        <v>0.1851934526445722</v>
       </c>
       <c r="C61">
-        <v>-962.1512678755939</v>
+        <v>-895.1892551467054</v>
       </c>
       <c r="D61">
-        <v>1770.064732124406</v>
+        <v>1837.026744853294</v>
       </c>
       <c r="E61">
         <v>711.0159999999996</v>
@@ -6295,37 +6295,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M61">
-        <v>887.8826928</v>
+        <v>851.7605327999999</v>
       </c>
       <c r="N61">
-        <v>-556.4786111673468</v>
+        <v>-520.3564511673467</v>
       </c>
       <c r="O61">
-        <v>-122.4252944568163</v>
+        <v>-114.4784192568163</v>
       </c>
       <c r="P61">
-        <v>-434.0533167105305</v>
+        <v>-405.8780319105304</v>
       </c>
       <c r="Q61">
-        <v>-210.2533167105305</v>
+        <v>-182.0780319105304</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1416831831361406</v>
+        <v>0.1414146371860838</v>
       </c>
       <c r="T61">
-        <v>2.212968562919372</v>
+        <v>2.20819023524443</v>
       </c>
       <c r="U61">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08211546249342962</v>
+        <v>0.08559788244650128</v>
       </c>
       <c r="W61">
-        <v>0.225616019319115</v>
+        <v>0.215616019319115</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.373252102242862</v>
+        <v>0.3890812838477332</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1932035564840955</v>
+        <v>0.1870934526445722</v>
       </c>
       <c r="C62">
-        <v>-1044.680081855785</v>
+        <v>-978.2172942550292</v>
       </c>
       <c r="D62">
-        <v>1748.759918144215</v>
+        <v>1815.22270574497</v>
       </c>
       <c r="E62">
         <v>772.2399999999998</v>
@@ -6377,37 +6377,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M62">
-        <v>902.931552</v>
+        <v>866.197152</v>
       </c>
       <c r="N62">
-        <v>-571.527470367347</v>
+        <v>-534.7930703673469</v>
       </c>
       <c r="O62">
-        <v>-125.7360434808163</v>
+        <v>-117.6544754808163</v>
       </c>
       <c r="P62">
-        <v>-445.7914268865306</v>
+        <v>-417.1385948865306</v>
       </c>
       <c r="Q62">
-        <v>-221.9914268865306</v>
+        <v>-193.3385948865306</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1440802627145442</v>
+        <v>0.1438050031157359</v>
       </c>
       <c r="T62">
-        <v>2.268292776992357</v>
+        <v>2.263394991125542</v>
       </c>
       <c r="U62">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08074687145187244</v>
+        <v>0.08417125107239291</v>
       </c>
       <c r="W62">
-        <v>0.2259524189971298</v>
+        <v>0.2159524189971298</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3670312338721474</v>
+        <v>0.3825965957836041</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1952035564840955</v>
+        <v>0.1889934526445722</v>
       </c>
       <c r="C63">
-        <v>-1126.702138199375</v>
+        <v>-1060.733811684737</v>
       </c>
       <c r="D63">
-        <v>1727.961861800624</v>
+        <v>1793.930188315263</v>
       </c>
       <c r="E63">
         <v>833.4639999999999</v>
@@ -6459,37 +6459,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M63">
-        <v>917.9804112</v>
+        <v>880.6337712</v>
       </c>
       <c r="N63">
-        <v>-586.5763295673469</v>
+        <v>-549.2296895673469</v>
       </c>
       <c r="O63">
-        <v>-129.0467925048163</v>
+        <v>-120.8305317048163</v>
       </c>
       <c r="P63">
-        <v>-457.5295370625306</v>
+        <v>-428.3991578625306</v>
       </c>
       <c r="Q63">
-        <v>-233.7295370625305</v>
+        <v>-204.5991578625305</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1466002694508145</v>
+        <v>0.1463179519135753</v>
       </c>
       <c r="T63">
-        <v>2.326454130248572</v>
+        <v>2.321430760128761</v>
       </c>
       <c r="U63">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07942315224774339</v>
+        <v>0.08279139449743565</v>
       </c>
       <c r="W63">
-        <v>0.2262777891775047</v>
+        <v>0.2162777891775047</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3610143283988336</v>
+        <v>0.3763245204428892</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1972035564840955</v>
+        <v>0.1908934526445722</v>
       </c>
       <c r="C64">
-        <v>-1208.235305053154</v>
+        <v>-1142.756599149375</v>
       </c>
       <c r="D64">
-        <v>1707.652694946846</v>
+        <v>1773.131400850625</v>
       </c>
       <c r="E64">
         <v>894.6880000000001</v>
@@ -6541,37 +6541,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M64">
-        <v>933.0292704000001</v>
+        <v>895.0703904000001</v>
       </c>
       <c r="N64">
-        <v>-601.625188767347</v>
+        <v>-563.6663087673469</v>
       </c>
       <c r="O64">
-        <v>-132.3575415288163</v>
+        <v>-124.0065879288163</v>
       </c>
       <c r="P64">
-        <v>-469.2676472385307</v>
+        <v>-439.6597208385306</v>
       </c>
       <c r="Q64">
-        <v>-245.4676472385307</v>
+        <v>-215.8597208385306</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1492529081205728</v>
+        <v>0.1489631611744589</v>
       </c>
       <c r="T64">
-        <v>2.387676607360376</v>
+        <v>2.382521043290044</v>
       </c>
       <c r="U64">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07814213366310237</v>
+        <v>0.08145604942489636</v>
       </c>
       <c r="W64">
-        <v>0.2265926635456094</v>
+        <v>0.2165926635456094</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3551915166504652</v>
+        <v>0.3702547701131653</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1992035564840955</v>
+        <v>0.1927934526445722</v>
       </c>
       <c r="C65">
-        <v>-1289.296620287205</v>
+        <v>-1224.302632712166</v>
       </c>
       <c r="D65">
-        <v>1687.815379712794</v>
+        <v>1752.809367287834</v>
       </c>
       <c r="E65">
         <v>955.9119999999998</v>
@@ -6623,37 +6623,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M65">
-        <v>948.0781296</v>
+        <v>909.5070095999999</v>
       </c>
       <c r="N65">
-        <v>-616.674047967347</v>
+        <v>-578.1029279673469</v>
       </c>
       <c r="O65">
-        <v>-135.6682905528163</v>
+        <v>-127.1826441528163</v>
       </c>
       <c r="P65">
-        <v>-481.0057574145306</v>
+        <v>-450.9202838145306</v>
       </c>
       <c r="Q65">
-        <v>-257.2057574145306</v>
+        <v>-227.1202838145306</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1520489326643721</v>
+        <v>0.1517513547197145</v>
       </c>
       <c r="T65">
-        <v>2.452208407559306</v>
+        <v>2.446913503919504</v>
       </c>
       <c r="U65">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07690178233511662</v>
+        <v>0.08016309625942182</v>
       </c>
       <c r="W65">
-        <v>0.2268975419020283</v>
+        <v>0.2168975419020283</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3495535560687119</v>
+        <v>0.3643777102700991</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2012035564840955</v>
+        <v>0.1946934526445722</v>
       </c>
       <c r="C66">
-        <v>-1369.902339166575</v>
+        <v>-1305.388118997617</v>
       </c>
       <c r="D66">
-        <v>1668.433660833425</v>
+        <v>1732.947881002383</v>
       </c>
       <c r="E66">
         <v>1017.136</v>
@@ -6705,37 +6705,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M66">
-        <v>963.1269888</v>
+        <v>923.9436287999999</v>
       </c>
       <c r="N66">
-        <v>-631.7229071673469</v>
+        <v>-592.5395471673469</v>
       </c>
       <c r="O66">
-        <v>-138.9790395768163</v>
+        <v>-130.3587003768163</v>
       </c>
       <c r="P66">
-        <v>-492.7438675905306</v>
+        <v>-462.1808467905306</v>
       </c>
       <c r="Q66">
-        <v>-268.9438675905305</v>
+        <v>-238.3808467905306</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1550002919050491</v>
+        <v>0.1546944479063733</v>
       </c>
       <c r="T66">
-        <v>2.520325307769286</v>
+        <v>2.514883323472824</v>
       </c>
       <c r="U66">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07570019198613041</v>
+        <v>0.07891054788036836</v>
       </c>
       <c r="W66">
-        <v>0.2271928928098092</v>
+        <v>0.2171928928098092</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3440917817551383</v>
+        <v>0.3586843085471288</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2032035564840955</v>
+        <v>0.1965934526445722</v>
       </c>
       <c r="C67">
-        <v>-1450.067978775626</v>
+        <v>-1386.028538296524</v>
       </c>
       <c r="D67">
-        <v>1649.492021224374</v>
+        <v>1713.531461703476</v>
       </c>
       <c r="E67">
         <v>1078.36</v>
@@ -6787,37 +6787,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M67">
-        <v>978.1758480000001</v>
+        <v>938.3802480000001</v>
       </c>
       <c r="N67">
-        <v>-646.771766367347</v>
+        <v>-606.9761663673469</v>
       </c>
       <c r="O67">
-        <v>-142.2897886008163</v>
+        <v>-133.5347566008163</v>
       </c>
       <c r="P67">
-        <v>-504.4819777665307</v>
+        <v>-473.4414097665306</v>
       </c>
       <c r="Q67">
-        <v>-280.6819777665307</v>
+        <v>-249.6414097665306</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1581203002451934</v>
+        <v>0.1578057178465554</v>
       </c>
       <c r="T67">
-        <v>2.59233460227698</v>
+        <v>2.586737132714905</v>
       </c>
       <c r="U67">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07453557364788226</v>
+        <v>0.0776965394514396</v>
       </c>
       <c r="W67">
-        <v>0.2274791559973506</v>
+        <v>0.2174791559973505</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3387980620358284</v>
+        <v>0.3531660884156347</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2052035564840956</v>
+        <v>0.1984934526445722</v>
       </c>
       <c r="C68">
-        <v>-1529.808359450301</v>
+        <v>-1466.23868480532</v>
       </c>
       <c r="D68">
-        <v>1630.975640549699</v>
+        <v>1694.54531519468</v>
       </c>
       <c r="E68">
         <v>1139.584</v>
@@ -6869,37 +6869,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M68">
-        <v>993.2247072000001</v>
+        <v>952.8168672</v>
       </c>
       <c r="N68">
-        <v>-661.820625567347</v>
+        <v>-621.4127855673469</v>
       </c>
       <c r="O68">
-        <v>-145.6005376248163</v>
+        <v>-136.7108128248163</v>
       </c>
       <c r="P68">
-        <v>-516.2200879425307</v>
+        <v>-484.7019727425305</v>
       </c>
       <c r="Q68">
-        <v>-292.4200879425306</v>
+        <v>-260.9019727425305</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.161423838487699</v>
+        <v>0.1611000036655717</v>
       </c>
       <c r="T68">
-        <v>2.668579737638068</v>
+        <v>2.662817636618284</v>
       </c>
       <c r="U68">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07340624677442949</v>
+        <v>0.07651931915672082</v>
       </c>
       <c r="W68">
-        <v>0.2277567445428453</v>
+        <v>0.2177567445428452</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3336647580655887</v>
+        <v>0.3478150870760038</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2072035564840955</v>
+        <v>0.2003934526445722</v>
       </c>
       <c r="C69">
-        <v>-1609.137643450764</v>
+        <v>-1546.032704219597</v>
       </c>
       <c r="D69">
-        <v>1612.870356549236</v>
+        <v>1675.975295780403</v>
       </c>
       <c r="E69">
         <v>1200.808</v>
@@ -6951,37 +6951,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M69">
-        <v>1008.2735664</v>
+        <v>967.2534864</v>
       </c>
       <c r="N69">
-        <v>-676.8694847673469</v>
+        <v>-635.8494047673469</v>
       </c>
       <c r="O69">
-        <v>-148.9112866488163</v>
+        <v>-139.8868690488163</v>
       </c>
       <c r="P69">
-        <v>-527.9581981185306</v>
+        <v>-495.9625357185305</v>
       </c>
       <c r="Q69">
-        <v>-304.1581981185306</v>
+        <v>-272.1625357185305</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1649275911691445</v>
+        <v>0.164593943170589</v>
       </c>
       <c r="T69">
-        <v>2.749445790293767</v>
+        <v>2.743509080152172</v>
       </c>
       <c r="U69">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07231063115093056</v>
+        <v>0.07537723976632202</v>
       </c>
       <c r="W69">
-        <v>0.2280260468631013</v>
+        <v>0.2180260468631013</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3286846870496843</v>
+        <v>0.3426238171196455</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2092035564840956</v>
+        <v>0.2022934526445722</v>
       </c>
       <c r="C70">
-        <v>-1688.069371086518</v>
+        <v>-1625.42412888257</v>
       </c>
       <c r="D70">
-        <v>1595.162628913482</v>
+        <v>1657.80787111743</v>
       </c>
       <c r="E70">
         <v>1262.032</v>
@@ -7033,37 +7033,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M70">
-        <v>1023.3224256</v>
+        <v>981.6901056</v>
       </c>
       <c r="N70">
-        <v>-691.918343967347</v>
+        <v>-650.2860239673469</v>
       </c>
       <c r="O70">
-        <v>-152.2220356728164</v>
+        <v>-143.0629252728163</v>
       </c>
       <c r="P70">
-        <v>-539.6963082945307</v>
+        <v>-507.2230986945306</v>
       </c>
       <c r="Q70">
-        <v>-315.8963082945307</v>
+        <v>-283.4230986945306</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1686503283931802</v>
+        <v>0.1683062538946699</v>
       </c>
       <c r="T70">
-        <v>2.835365971240447</v>
+        <v>2.829243738906927</v>
       </c>
       <c r="U70">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07124723951635804</v>
+        <v>0.07426875094622903</v>
       </c>
       <c r="W70">
-        <v>0.2282874285268792</v>
+        <v>0.2182874285268792</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3238510887107183</v>
+        <v>0.3375852315737684</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2112035564840956</v>
+        <v>0.2041934526445723</v>
       </c>
       <c r="C71">
-        <v>-1766.616494487659</v>
+        <v>-1704.42591067201</v>
       </c>
       <c r="D71">
-        <v>1577.839505512341</v>
+        <v>1640.03008932799</v>
       </c>
       <c r="E71">
         <v>1323.256</v>
@@ -7115,37 +7115,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M71">
-        <v>1038.3712848</v>
+        <v>996.1267248</v>
       </c>
       <c r="N71">
-        <v>-706.967203167347</v>
+        <v>-664.7226431673469</v>
       </c>
       <c r="O71">
-        <v>-155.5327846968163</v>
+        <v>-146.2389814968163</v>
       </c>
       <c r="P71">
-        <v>-551.4344184705307</v>
+        <v>-518.4836616705305</v>
       </c>
       <c r="Q71">
-        <v>-327.6344184705306</v>
+        <v>-294.6836616705305</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1726132422123151</v>
+        <v>0.1722580685364335</v>
       </c>
       <c r="T71">
-        <v>2.926829389667559</v>
+        <v>2.920509665968441</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07021467082771518</v>
+        <v>0.0731923922368634</v>
       </c>
       <c r="W71">
-        <v>0.2285412339105476</v>
+        <v>0.2185412339105476</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3191575946714326</v>
+        <v>0.3326926919857428</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2132035564840956</v>
+        <v>0.2060934526445722</v>
       </c>
       <c r="C72">
-        <v>-1844.791409199278</v>
+        <v>-1783.050451793621</v>
       </c>
       <c r="D72">
-        <v>1560.888590800722</v>
+        <v>1622.62954820638</v>
       </c>
       <c r="E72">
         <v>1384.48</v>
@@ -7197,37 +7197,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M72">
-        <v>1053.420144</v>
+        <v>1010.563344</v>
       </c>
       <c r="N72">
-        <v>-722.0160623673471</v>
+        <v>-679.1592623673471</v>
       </c>
       <c r="O72">
-        <v>-158.8435337208164</v>
+        <v>-149.4150377208164</v>
       </c>
       <c r="P72">
-        <v>-563.1725286465307</v>
+        <v>-529.7442246465307</v>
       </c>
       <c r="Q72">
-        <v>-339.3725286465307</v>
+        <v>-305.9442246465307</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1768403502860589</v>
+        <v>0.176473337487648</v>
       </c>
       <c r="T72">
-        <v>3.024390369323144</v>
+        <v>3.017859988167389</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06921160410160494</v>
+        <v>0.07214678663347963</v>
       </c>
       <c r="W72">
-        <v>0.2287877877118255</v>
+        <v>0.2187877877118255</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3145982004618406</v>
+        <v>0.3279399392430892</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2152035564840955</v>
+        <v>0.2079934526445723</v>
       </c>
       <c r="C73">
-        <v>-1922.605983760972</v>
+        <v>-1861.309633634713</v>
       </c>
       <c r="D73">
-        <v>1544.298016239027</v>
+        <v>1605.594366365287</v>
       </c>
       <c r="E73">
         <v>1445.704</v>
@@ -7279,37 +7279,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M73">
-        <v>1068.4690032</v>
+        <v>1024.9999632</v>
       </c>
       <c r="N73">
-        <v>-737.0649215673468</v>
+        <v>-693.5958815673469</v>
       </c>
       <c r="O73">
-        <v>-162.1542827448163</v>
+        <v>-152.5910939448163</v>
       </c>
       <c r="P73">
-        <v>-574.9106388225305</v>
+        <v>-541.0047876225306</v>
       </c>
       <c r="Q73">
-        <v>-351.1106388225305</v>
+        <v>-317.2047876225305</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1813589830545437</v>
+        <v>0.1809793146423944</v>
       </c>
       <c r="T73">
-        <v>3.128679692403251</v>
+        <v>3.121924125690402</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06823679277623025</v>
+        <v>0.07113063470906444</v>
       </c>
       <c r="W73">
-        <v>0.2290273963356026</v>
+        <v>0.2190273963356026</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3101672398919556</v>
+        <v>0.3233210668593838</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2172035564840955</v>
+        <v>0.2098934526445722</v>
       </c>
       <c r="C74">
-        <v>-2000.07158741981</v>
+        <v>-1939.214843819233</v>
       </c>
       <c r="D74">
-        <v>1528.05641258019</v>
+        <v>1588.913156180767</v>
       </c>
       <c r="E74">
         <v>1506.928</v>
@@ -7361,37 +7361,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M74">
-        <v>1083.5178624</v>
+        <v>1039.4365824</v>
       </c>
       <c r="N74">
-        <v>-752.113780767347</v>
+        <v>-708.0325007673468</v>
       </c>
       <c r="O74">
-        <v>-165.4650317688163</v>
+        <v>-155.7671501688163</v>
       </c>
       <c r="P74">
-        <v>-586.6487489985307</v>
+        <v>-552.2653505985305</v>
       </c>
       <c r="Q74">
-        <v>-362.8487489985307</v>
+        <v>-328.4653505985305</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1862003753064917</v>
+        <v>0.1858071473081942</v>
       </c>
       <c r="T74">
-        <v>3.240418252846224</v>
+        <v>3.233421415893631</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06728905954322704</v>
+        <v>0.0701427092269941</v>
       </c>
       <c r="W74">
-        <v>0.2292603491642748</v>
+        <v>0.2192603491642748</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3058593615601228</v>
+        <v>0.3188304964863368</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2192035564840955</v>
+        <v>0.2117934526445722</v>
       </c>
       <c r="C75">
-        <v>-2077.199116112723</v>
+        <v>-2016.777001593618</v>
       </c>
       <c r="D75">
-        <v>1512.152883887277</v>
+        <v>1572.574998406382</v>
       </c>
       <c r="E75">
         <v>1568.152</v>
@@ -7443,37 +7443,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M75">
-        <v>1098.5667216</v>
+        <v>1053.8732016</v>
       </c>
       <c r="N75">
-        <v>-767.1626399673469</v>
+        <v>-722.4691199673468</v>
       </c>
       <c r="O75">
-        <v>-168.7757807928163</v>
+        <v>-158.9432063928163</v>
       </c>
       <c r="P75">
-        <v>-598.3868591745306</v>
+        <v>-563.5259135745305</v>
       </c>
       <c r="Q75">
-        <v>-374.5868591745306</v>
+        <v>-339.7259135745305</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1914003892067321</v>
+        <v>0.1909925972084977</v>
       </c>
       <c r="T75">
-        <v>3.360433743692381</v>
+        <v>3.353177764630431</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06636729160427873</v>
+        <v>0.06918185019648733</v>
       </c>
       <c r="W75">
-        <v>0.2294869197236683</v>
+        <v>0.2194869197236683</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.301669507292176</v>
+        <v>0.3144629554385787</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2212035564840955</v>
+        <v>0.2136934526445722</v>
       </c>
       <c r="C76">
-        <v>-2153.999016843116</v>
+        <v>-2094.006581662393</v>
       </c>
       <c r="D76">
-        <v>1496.576983156884</v>
+        <v>1556.569418337607</v>
       </c>
       <c r="E76">
         <v>1629.376</v>
@@ -7525,37 +7525,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M76">
-        <v>1113.6155808</v>
+        <v>1068.3098208</v>
       </c>
       <c r="N76">
-        <v>-782.211499167347</v>
+        <v>-736.9057391673471</v>
       </c>
       <c r="O76">
-        <v>-172.0865298168164</v>
+        <v>-162.1192626168163</v>
       </c>
       <c r="P76">
-        <v>-610.1249693505307</v>
+        <v>-574.7864765505308</v>
       </c>
       <c r="Q76">
-        <v>-386.3249693505307</v>
+        <v>-350.9864765505308</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1970004041762218</v>
+        <v>0.196576927870363</v>
       </c>
       <c r="T76">
-        <v>3.489681195372857</v>
+        <v>3.48214614019314</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06547043631232902</v>
+        <v>0.06824696032896721</v>
       </c>
       <c r="W76">
-        <v>0.2297073667544295</v>
+        <v>0.2197073667544295</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2975928923287682</v>
+        <v>0.31021345604076</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2232035564840955</v>
+        <v>0.2155934526445722</v>
       </c>
       <c r="C77">
-        <v>-2230.481310566288</v>
+        <v>-2170.913636582857</v>
       </c>
       <c r="D77">
-        <v>1481.318689433712</v>
+        <v>1540.886363417142</v>
       </c>
       <c r="E77">
         <v>1690.599999999999</v>
@@ -7607,37 +7607,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M77">
-        <v>1128.66444</v>
+        <v>1082.74644</v>
       </c>
       <c r="N77">
-        <v>-797.260358367347</v>
+        <v>-751.3423583673468</v>
       </c>
       <c r="O77">
-        <v>-175.3972788408163</v>
+        <v>-165.2953188408163</v>
       </c>
       <c r="P77">
-        <v>-621.8630795265306</v>
+        <v>-586.0470395265305</v>
       </c>
       <c r="Q77">
-        <v>-398.0630795265305</v>
+        <v>-362.2470395265305</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2030484203432707</v>
+        <v>0.2026080049851775</v>
       </c>
       <c r="T77">
-        <v>3.629268443187772</v>
+        <v>3.621431985800866</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06459749716149796</v>
+        <v>0.06733700085791433</v>
       </c>
       <c r="W77">
-        <v>0.2299219351977038</v>
+        <v>0.2199219351977038</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.293624987097718</v>
+        <v>0.3060772766268833</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2252035564840955</v>
+        <v>0.2174934526445723</v>
       </c>
       <c r="C78">
-        <v>-2306.655613689025</v>
+        <v>-2247.507817819455</v>
       </c>
       <c r="D78">
-        <v>1466.368386310974</v>
+        <v>1525.516182180544</v>
       </c>
       <c r="E78">
         <v>1751.824</v>
@@ -7689,37 +7689,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M78">
-        <v>1143.7132992</v>
+        <v>1097.1830592</v>
       </c>
       <c r="N78">
-        <v>-812.3092175673469</v>
+        <v>-765.7789775673468</v>
       </c>
       <c r="O78">
-        <v>-178.7080278648163</v>
+        <v>-168.4713750648163</v>
       </c>
       <c r="P78">
-        <v>-633.6011897025305</v>
+        <v>-597.3076025025305</v>
       </c>
       <c r="Q78">
-        <v>-409.8011897025305</v>
+        <v>-373.5076025025305</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2096004378575737</v>
+        <v>0.2091416718595599</v>
       </c>
       <c r="T78">
-        <v>3.780487961653929</v>
+        <v>3.772324985209236</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06374753009358351</v>
+        <v>0.06645098768873124</v>
       </c>
       <c r="W78">
-        <v>0.2301308571029972</v>
+        <v>0.2201308571029972</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2897615004253796</v>
+        <v>0.3020499440396874</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2272035564840955</v>
+        <v>0.2193934526445722</v>
       </c>
       <c r="C79">
-        <v>-2382.531158280278</v>
+        <v>-2323.798395550504</v>
       </c>
       <c r="D79">
-        <v>1451.716841719722</v>
+        <v>1510.449604449496</v>
       </c>
       <c r="E79">
         <v>1813.048</v>
@@ -7771,37 +7771,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M79">
-        <v>1158.7621584</v>
+        <v>1111.6196784</v>
       </c>
       <c r="N79">
-        <v>-827.358076767347</v>
+        <v>-780.2155967673468</v>
       </c>
       <c r="O79">
-        <v>-182.0187768888163</v>
+        <v>-171.6474312888163</v>
       </c>
       <c r="P79">
-        <v>-645.3392998785307</v>
+        <v>-608.5681654785305</v>
       </c>
       <c r="Q79">
-        <v>-421.5392998785307</v>
+        <v>-384.7681654785305</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2167221960252942</v>
+        <v>0.2162434836795408</v>
       </c>
       <c r="T79">
-        <v>3.944857003464969</v>
+        <v>3.936339115000941</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06291964009236814</v>
+        <v>0.06558798784861787</v>
       </c>
       <c r="W79">
-        <v>0.2303343524652959</v>
+        <v>0.2203343524652959</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2859983640562188</v>
+        <v>0.2981272174937175</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2292035564840955</v>
+        <v>0.2212934526445722</v>
       </c>
       <c r="C80">
-        <v>-2458.116811082189</v>
+        <v>-2399.794277312686</v>
       </c>
       <c r="D80">
-        <v>1437.355188917811</v>
+        <v>1495.677722687314</v>
       </c>
       <c r="E80">
         <v>1874.272</v>
@@ -7853,37 +7853,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M80">
-        <v>1173.8110176</v>
+        <v>1126.0562976</v>
       </c>
       <c r="N80">
-        <v>-842.406935967347</v>
+        <v>-794.6522159673468</v>
       </c>
       <c r="O80">
-        <v>-185.3295259128163</v>
+        <v>-174.8234875128163</v>
       </c>
       <c r="P80">
-        <v>-657.0774100545307</v>
+        <v>-619.8287284545305</v>
       </c>
       <c r="Q80">
-        <v>-433.2774100545307</v>
+        <v>-396.0287284545305</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2244913867537167</v>
+        <v>0.2239909147558836</v>
       </c>
       <c r="T80">
-        <v>4.124168685440649</v>
+        <v>4.115263620228258</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06211297803990188</v>
+        <v>0.06474711620953302</v>
       </c>
       <c r="W80">
-        <v>0.2305326299977921</v>
+        <v>0.2205326299977921</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2823317183631904</v>
+        <v>0.2943050736796955</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2312035564840955</v>
+        <v>0.2231934526445722</v>
       </c>
       <c r="C81">
-        <v>-2533.42109140374</v>
+        <v>-2475.504025562105</v>
       </c>
       <c r="D81">
-        <v>1423.274908596259</v>
+        <v>1481.191974437895</v>
       </c>
       <c r="E81">
         <v>1935.496</v>
@@ -7935,37 +7935,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M81">
-        <v>1188.8598768</v>
+        <v>1140.4929168</v>
       </c>
       <c r="N81">
-        <v>-857.4557951673471</v>
+        <v>-809.088835167347</v>
       </c>
       <c r="O81">
-        <v>-188.6402749368164</v>
+        <v>-177.9995437368163</v>
       </c>
       <c r="P81">
-        <v>-668.8155202305308</v>
+        <v>-631.0892914305307</v>
       </c>
       <c r="Q81">
-        <v>-445.0155202305307</v>
+        <v>-407.2892914305307</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2330005004086556</v>
+        <v>0.2324761964109257</v>
       </c>
       <c r="T81">
-        <v>4.320557670461634</v>
+        <v>4.311228554524842</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0613267378115487</v>
+        <v>0.06392753246004525</v>
       </c>
       <c r="W81">
-        <v>0.2307258878459214</v>
+        <v>0.2207258878459213</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2787578991434031</v>
+        <v>0.2905796930002056</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2332035564840955</v>
+        <v>0.2250934526445723</v>
       </c>
       <c r="C82">
-        <v>-2608.452187972883</v>
+        <v>-2550.935874224645</v>
       </c>
       <c r="D82">
-        <v>1409.467812027117</v>
+        <v>1466.984125775355</v>
       </c>
       <c r="E82">
         <v>1996.72</v>
@@ -8017,37 +8017,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M82">
-        <v>1203.908736</v>
+        <v>1154.929536</v>
       </c>
       <c r="N82">
-        <v>-872.504654367347</v>
+        <v>-823.525454367347</v>
       </c>
       <c r="O82">
-        <v>-191.9510239608163</v>
+        <v>-181.1755999608164</v>
       </c>
       <c r="P82">
-        <v>-680.5536304065307</v>
+        <v>-642.3498544065307</v>
       </c>
       <c r="Q82">
-        <v>-456.7536304065307</v>
+        <v>-418.5498544065306</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2423605254290884</v>
+        <v>0.2418100062314719</v>
       </c>
       <c r="T82">
-        <v>4.536585553984716</v>
+        <v>4.526789982251084</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06056015358890433</v>
+        <v>0.06312843830429468</v>
       </c>
       <c r="W82">
-        <v>0.2309143142478473</v>
+        <v>0.2209143142478473</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2752734254041106</v>
+        <v>0.286947446837703</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2352035564840955</v>
+        <v>0.2269934526445722</v>
       </c>
       <c r="C83">
-        <v>-2683.217974817201</v>
+        <v>-2626.097744302864</v>
       </c>
       <c r="D83">
-        <v>1395.926025182799</v>
+        <v>1453.046255697136</v>
       </c>
       <c r="E83">
         <v>2057.944</v>
@@ -8099,37 +8099,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M83">
-        <v>1218.9575952</v>
+        <v>1169.3661552</v>
       </c>
       <c r="N83">
-        <v>-887.5535135673472</v>
+        <v>-837.962073567347</v>
       </c>
       <c r="O83">
-        <v>-195.2617729848164</v>
+        <v>-184.3516561848163</v>
       </c>
       <c r="P83">
-        <v>-692.2917405825308</v>
+        <v>-653.6104173825307</v>
       </c>
       <c r="Q83">
-        <v>-468.4917405825308</v>
+        <v>-429.8104173825307</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2527058162411456</v>
+        <v>0.2521263223489179</v>
       </c>
       <c r="T83">
-        <v>4.775353214720753</v>
+        <v>4.765042086580089</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05981249737175737</v>
+        <v>0.06234907486843919</v>
       </c>
       <c r="W83">
-        <v>0.2310980881460221</v>
+        <v>0.2210980881460221</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2718749880534425</v>
+        <v>0.2834048857656326</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2372035564840955</v>
+        <v>0.2288934526445722</v>
       </c>
       <c r="C84">
-        <v>-2757.726026237835</v>
+        <v>-2700.997258601561</v>
       </c>
       <c r="D84">
-        <v>1382.641973762166</v>
+        <v>1439.37074139844</v>
       </c>
       <c r="E84">
         <v>2119.168000000001</v>
@@ -8181,37 +8181,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M84">
-        <v>1234.0064544</v>
+        <v>1183.8027744</v>
       </c>
       <c r="N84">
-        <v>-902.6023727673471</v>
+        <v>-852.398692767347</v>
       </c>
       <c r="O84">
-        <v>-198.5725220088164</v>
+        <v>-187.5277124088163</v>
       </c>
       <c r="P84">
-        <v>-704.0298507585308</v>
+        <v>-664.8709803585307</v>
       </c>
       <c r="Q84">
-        <v>-480.2298507585307</v>
+        <v>-441.0709803585307</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2642005838100982</v>
+        <v>0.2635888958127466</v>
       </c>
       <c r="T84">
-        <v>5.040650615538573</v>
+        <v>5.029766646945649</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05908307667210178</v>
+        <v>0.06158872029687286</v>
       </c>
       <c r="W84">
-        <v>0.2312773797539974</v>
+        <v>0.2212773797539974</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2685594394186445</v>
+        <v>0.2799487286221493</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2392035564840956</v>
+        <v>0.2307934526445722</v>
       </c>
       <c r="C85">
-        <v>-2831.98363093647</v>
+        <v>-2775.641755629553</v>
       </c>
       <c r="D85">
-        <v>1369.608369063531</v>
+        <v>1425.950244370448</v>
       </c>
       <c r="E85">
         <v>2180.392000000001</v>
@@ -8263,37 +8263,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M85">
-        <v>1249.0553136</v>
+        <v>1198.2393936</v>
       </c>
       <c r="N85">
-        <v>-917.6512319673473</v>
+        <v>-866.835311967347</v>
       </c>
       <c r="O85">
-        <v>-201.8832710328164</v>
+        <v>-190.7037686328163</v>
       </c>
       <c r="P85">
-        <v>-715.7679609345308</v>
+        <v>-676.1315433345306</v>
       </c>
       <c r="Q85">
-        <v>-491.9679609345308</v>
+        <v>-452.3315433345306</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2770476769753981</v>
+        <v>0.2764000073311434</v>
       </c>
       <c r="T85">
-        <v>5.337159475276136</v>
+        <v>5.325635273236569</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05837123237484754</v>
+        <v>0.06084668752221174</v>
       </c>
       <c r="W85">
-        <v>0.2314523510822625</v>
+        <v>0.2214523510822625</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2653237835220342</v>
+        <v>0.2765758523736896</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2412035564840956</v>
+        <v>0.2326934526445722</v>
       </c>
       <c r="C86">
-        <v>-2905.997805350786</v>
+        <v>-2850.038302730927</v>
       </c>
       <c r="D86">
-        <v>1356.818194649214</v>
+        <v>1412.777697269073</v>
       </c>
       <c r="E86">
         <v>2241.616</v>
@@ -8345,37 +8345,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M86">
-        <v>1264.1041728</v>
+        <v>1212.6760128</v>
       </c>
       <c r="N86">
-        <v>-932.700091167347</v>
+        <v>-881.271931167347</v>
       </c>
       <c r="O86">
-        <v>-205.1940200568163</v>
+        <v>-193.8798248568164</v>
       </c>
       <c r="P86">
-        <v>-727.5060711105307</v>
+        <v>-687.3921063105306</v>
       </c>
       <c r="Q86">
-        <v>-503.7060711105307</v>
+        <v>-463.5921063105306</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2915006567863604</v>
+        <v>0.2908125077893398</v>
       </c>
       <c r="T86">
-        <v>5.670731942480892</v>
+        <v>5.658487477813853</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05767633675133747</v>
+        <v>0.06012232219456635</v>
       </c>
       <c r="W86">
-        <v>0.2316231564265213</v>
+        <v>0.2216231564265213</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2621651670515339</v>
+        <v>0.2732832827025743</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2432035564840955</v>
+        <v>0.2345934526445722</v>
       </c>
       <c r="C87">
-        <v>-2979.775306249609</v>
+        <v>-2924.193708495141</v>
       </c>
       <c r="D87">
-        <v>1344.26469375039</v>
+        <v>1399.846291504859</v>
       </c>
       <c r="E87">
         <v>2302.84</v>
@@ -8427,37 +8427,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M87">
-        <v>1279.153032</v>
+        <v>1227.112632</v>
       </c>
       <c r="N87">
-        <v>-947.7489503673471</v>
+        <v>-895.708550367347</v>
       </c>
       <c r="O87">
-        <v>-208.5047690808164</v>
+        <v>-197.0558810808163</v>
       </c>
       <c r="P87">
-        <v>-739.2441812865308</v>
+        <v>-698.6526692865307</v>
       </c>
       <c r="Q87">
-        <v>-515.4441812865307</v>
+        <v>-474.8526692865307</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3078807005721177</v>
+        <v>0.3071466749752959</v>
       </c>
       <c r="T87">
-        <v>6.048780738646285</v>
+        <v>6.035719976334777</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05699779161308643</v>
+        <v>0.05941500075698323</v>
       </c>
       <c r="W87">
-        <v>0.2317899428215034</v>
+        <v>0.2217899428215034</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2590808709685747</v>
+        <v>0.2700681852590147</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2452035564840955</v>
+        <v>0.2364934526445722</v>
       </c>
       <c r="C88">
-        <v>-3053.322642635278</v>
+        <v>-2998.114534491737</v>
       </c>
       <c r="D88">
-        <v>1331.941357364722</v>
+        <v>1387.149465508262</v>
       </c>
       <c r="E88">
         <v>2364.063999999999</v>
@@ -8509,37 +8509,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M88">
-        <v>1294.2018912</v>
+        <v>1241.5492512</v>
       </c>
       <c r="N88">
-        <v>-962.7978095673468</v>
+        <v>-910.1451695673468</v>
       </c>
       <c r="O88">
-        <v>-211.8155181048163</v>
+        <v>-200.2319373048163</v>
       </c>
       <c r="P88">
-        <v>-750.9822914625305</v>
+        <v>-709.9132322625305</v>
       </c>
       <c r="Q88">
-        <v>-527.1822914625304</v>
+        <v>-486.1132322625305</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3266007506129833</v>
+        <v>0.3258142946163884</v>
       </c>
       <c r="T88">
-        <v>6.480836505692449</v>
+        <v>6.466842831787261</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05633502659432962</v>
+        <v>0.05872412865515785</v>
       </c>
       <c r="W88">
-        <v>0.2319528504631138</v>
+        <v>0.2219528504631138</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2560683027014983</v>
+        <v>0.2669278575234447</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2472035564840955</v>
+        <v>0.2383934526445722</v>
       </c>
       <c r="C89">
-        <v>-3126.646086997281</v>
+        <v>-3071.807106372208</v>
       </c>
       <c r="D89">
-        <v>1319.841913002719</v>
+        <v>1374.680893627791</v>
       </c>
       <c r="E89">
         <v>2425.288</v>
@@ -8591,37 +8591,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M89">
-        <v>1309.2507504</v>
+        <v>1255.9858704</v>
       </c>
       <c r="N89">
-        <v>-977.846668767347</v>
+        <v>-924.5817887673468</v>
       </c>
       <c r="O89">
-        <v>-215.1262671288163</v>
+        <v>-203.4079935288163</v>
       </c>
       <c r="P89">
-        <v>-762.7204016385306</v>
+        <v>-721.1737952385305</v>
       </c>
       <c r="Q89">
-        <v>-538.9204016385306</v>
+        <v>-497.3737952385305</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3482008083524435</v>
+        <v>0.347353855740726</v>
       </c>
       <c r="T89">
-        <v>6.979362390745714</v>
+        <v>6.964292280386282</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05568749755301548</v>
+        <v>0.05804913867061581</v>
       </c>
       <c r="W89">
-        <v>0.2321120131014688</v>
+        <v>0.2221120131014688</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.253124988877343</v>
+        <v>0.2638597212300718</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2492035564840956</v>
+        <v>0.2402934526445722</v>
       </c>
       <c r="C90">
-        <v>-3199.751685958041</v>
+        <v>-3145.277524378429</v>
       </c>
       <c r="D90">
-        <v>1307.960314041958</v>
+        <v>1362.434475621571</v>
       </c>
       <c r="E90">
         <v>2486.512</v>
@@ -8673,37 +8673,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M90">
-        <v>1324.2996096</v>
+        <v>1270.4224896</v>
       </c>
       <c r="N90">
-        <v>-992.8955279673469</v>
+        <v>-939.0184079673468</v>
       </c>
       <c r="O90">
-        <v>-218.4370161528163</v>
+        <v>-206.5840497528163</v>
       </c>
       <c r="P90">
-        <v>-774.4585118145305</v>
+        <v>-732.4343582145304</v>
       </c>
       <c r="Q90">
-        <v>-550.6585118145306</v>
+        <v>-508.6343582145304</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3734008757151472</v>
+        <v>0.3724833437191198</v>
       </c>
       <c r="T90">
-        <v>7.560975923307858</v>
+        <v>7.544649970418472</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05505468508082213</v>
+        <v>0.05738948936754062</v>
       </c>
       <c r="W90">
-        <v>0.232267558407134</v>
+        <v>0.2222675584071339</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2502485685491914</v>
+        <v>0.2608613153070029</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2512035564840955</v>
+        <v>0.2421934526445722</v>
       </c>
       <c r="C91">
-        <v>-3272.645270348816</v>
+        <v>-3218.531673294373</v>
       </c>
       <c r="D91">
-        <v>1296.290729651184</v>
+        <v>1350.404326705627</v>
       </c>
       <c r="E91">
         <v>2547.736</v>
@@ -8755,37 +8755,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M91">
-        <v>1339.3484688</v>
+        <v>1284.8591088</v>
       </c>
       <c r="N91">
-        <v>-1007.944387167347</v>
+        <v>-953.455027167347</v>
       </c>
       <c r="O91">
-        <v>-221.7477651768164</v>
+        <v>-209.7601059768163</v>
       </c>
       <c r="P91">
-        <v>-786.1966219905307</v>
+        <v>-743.6949211905306</v>
       </c>
       <c r="Q91">
-        <v>-562.3966219905308</v>
+        <v>-519.8949211905306</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4031827735074333</v>
+        <v>0.4021818295117671</v>
       </c>
       <c r="T91">
-        <v>8.248337370881298</v>
+        <v>8.230527240456516</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05443609311362187</v>
+        <v>0.05674466364430982</v>
       </c>
       <c r="W91">
-        <v>0.2324196083126718</v>
+        <v>0.2224196083126717</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2474367868800994</v>
+        <v>0.2579302892923173</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2532035564840955</v>
+        <v>0.2440934526445722</v>
       </c>
       <c r="C92">
-        <v>-3345.332464750981</v>
+        <v>-3291.575231875206</v>
       </c>
       <c r="D92">
-        <v>1284.827535249019</v>
+        <v>1338.584768124794</v>
       </c>
       <c r="E92">
         <v>2608.96</v>
@@ -8837,37 +8837,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M92">
-        <v>1354.397328</v>
+        <v>1299.295728</v>
       </c>
       <c r="N92">
-        <v>-1022.993246367347</v>
+        <v>-967.891646367347</v>
       </c>
       <c r="O92">
-        <v>-225.0585142008163</v>
+        <v>-212.9361622008163</v>
       </c>
       <c r="P92">
-        <v>-797.9347321665307</v>
+        <v>-754.9554841665306</v>
       </c>
       <c r="Q92">
-        <v>-574.1347321665307</v>
+        <v>-531.1554841665306</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4389210508581767</v>
+        <v>0.4378200124629439</v>
       </c>
       <c r="T92">
-        <v>9.073171107969431</v>
+        <v>9.053579964502168</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05383124763458163</v>
+        <v>0.05611416738159528</v>
       </c>
       <c r="W92">
-        <v>0.2325682793314199</v>
+        <v>0.2225682793314198</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2446874892480982</v>
+        <v>0.2550643971890694</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2552035564840955</v>
+        <v>0.2459934526445722</v>
       </c>
       <c r="C93">
-        <v>-3417.818696535508</v>
+        <v>-3364.413681785497</v>
       </c>
       <c r="D93">
-        <v>1273.565303464492</v>
+        <v>1326.970318214503</v>
       </c>
       <c r="E93">
         <v>2670.184</v>
@@ -8919,37 +8919,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M93">
-        <v>1369.4461872</v>
+        <v>1313.7323472</v>
       </c>
       <c r="N93">
-        <v>-1038.042105567347</v>
+        <v>-982.328265567347</v>
       </c>
       <c r="O93">
-        <v>-228.3692632248164</v>
+        <v>-216.1122184248163</v>
       </c>
       <c r="P93">
-        <v>-809.6728423425308</v>
+        <v>-766.2160471425307</v>
       </c>
       <c r="Q93">
-        <v>-585.8728423425307</v>
+        <v>-542.4160471425307</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4826011676201963</v>
+        <v>0.4813777916254932</v>
       </c>
       <c r="T93">
-        <v>10.08130123107714</v>
+        <v>10.0595332938913</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05323969546277304</v>
+        <v>0.05549752817959971</v>
       </c>
       <c r="W93">
-        <v>0.2327136828552504</v>
+        <v>0.2227136828552504</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2419986157398774</v>
+        <v>0.2522614917254532</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2572035564840955</v>
+        <v>0.2478934526445723</v>
       </c>
       <c r="C94">
-        <v>-3490.109204431159</v>
+        <v>-3437.052316076114</v>
       </c>
       <c r="D94">
-        <v>1262.498795568841</v>
+        <v>1315.555683923887</v>
       </c>
       <c r="E94">
         <v>2731.408</v>
@@ -9001,37 +9001,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M94">
-        <v>1384.4950464</v>
+        <v>1328.1689664</v>
       </c>
       <c r="N94">
-        <v>-1053.090964767347</v>
+        <v>-996.764884767347</v>
       </c>
       <c r="O94">
-        <v>-231.6800122488164</v>
+        <v>-219.2882746488163</v>
       </c>
       <c r="P94">
-        <v>-821.4109525185306</v>
+        <v>-777.4766101185306</v>
       </c>
       <c r="Q94">
-        <v>-597.6109525185307</v>
+        <v>-553.6766101185306</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5372013135727212</v>
+        <v>0.53582501557868</v>
       </c>
       <c r="T94">
-        <v>11.34146388496179</v>
+        <v>11.31697495562771</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05266100312078638</v>
+        <v>0.05489429417764755</v>
       </c>
       <c r="W94">
-        <v>0.2328559254329107</v>
+        <v>0.2228559254329107</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2393681960035744</v>
+        <v>0.249519518989307</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2592035564840955</v>
+        <v>0.2497934526445723</v>
       </c>
       <c r="C95">
-        <v>-3562.209046649809</v>
+        <v>-3509.496247227331</v>
       </c>
       <c r="D95">
-        <v>1251.622953350191</v>
+        <v>1304.33575277267</v>
       </c>
       <c r="E95">
         <v>2792.632000000001</v>
@@ -9083,37 +9083,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M95">
-        <v>1399.5439056</v>
+        <v>1342.6055856</v>
       </c>
       <c r="N95">
-        <v>-1068.139823967347</v>
+        <v>-1011.201503967347</v>
       </c>
       <c r="O95">
-        <v>-234.9907612728164</v>
+        <v>-222.4643308728163</v>
       </c>
       <c r="P95">
-        <v>-833.1490626945308</v>
+        <v>-788.7371730945306</v>
       </c>
       <c r="Q95">
-        <v>-609.3490626945309</v>
+        <v>-564.9371730945306</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.607401501225967</v>
+        <v>0.6058285892327772</v>
       </c>
       <c r="T95">
-        <v>12.96167301138491</v>
+        <v>12.93368566357453</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05209475577540157</v>
+        <v>0.05430403294993091</v>
       </c>
       <c r="W95">
-        <v>0.2329951090304063</v>
+        <v>0.2229951090304063</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2367943444336434</v>
+        <v>0.2468365134087768</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2612035564840955</v>
+        <v>0.2516934526445722</v>
       </c>
       <c r="C96">
-        <v>-3634.123108595388</v>
+        <v>-3581.750414783846</v>
       </c>
       <c r="D96">
-        <v>1240.932891404612</v>
+        <v>1293.305585216153</v>
       </c>
       <c r="E96">
         <v>2853.856</v>
@@ -9165,37 +9165,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M96">
-        <v>1414.5927648</v>
+        <v>1357.0422048</v>
       </c>
       <c r="N96">
-        <v>-1083.188683167347</v>
+        <v>-1025.638123167347</v>
       </c>
       <c r="O96">
-        <v>-238.3015102968163</v>
+        <v>-225.6403870968163</v>
       </c>
       <c r="P96">
-        <v>-844.8871728705305</v>
+        <v>-799.9977360705307</v>
       </c>
       <c r="Q96">
-        <v>-621.0871728705306</v>
+        <v>-576.1977360705307</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.701001751430295</v>
+        <v>0.6991666874382402</v>
       </c>
       <c r="T96">
-        <v>15.12195184661573</v>
+        <v>15.08929994083696</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05154055624587604</v>
+        <v>0.05372633047174016</v>
       </c>
       <c r="W96">
-        <v>0.2331313312747637</v>
+        <v>0.2231313312747637</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2342752556630728</v>
+        <v>0.2442105930533643</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2632035564840955</v>
+        <v>0.2535934526445723</v>
       </c>
       <c r="C97">
-        <v>-3705.856110181111</v>
+        <v>-3653.819592605653</v>
       </c>
       <c r="D97">
-        <v>1230.423889818888</v>
+        <v>1282.460407394346</v>
       </c>
       <c r="E97">
         <v>2915.08</v>
@@ -9247,37 +9247,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M97">
-        <v>1429.641624</v>
+        <v>1371.478824</v>
       </c>
       <c r="N97">
-        <v>-1098.237542367347</v>
+        <v>-1040.074742367347</v>
       </c>
       <c r="O97">
-        <v>-241.6122593208163</v>
+        <v>-228.8164433208163</v>
       </c>
       <c r="P97">
-        <v>-856.6252830465307</v>
+        <v>-811.2582990465306</v>
       </c>
       <c r="Q97">
-        <v>-632.8252830465308</v>
+        <v>-587.4582990465306</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8320421017163544</v>
+        <v>0.8298400249258886</v>
       </c>
       <c r="T97">
-        <v>18.14634221593888</v>
+        <v>18.10715992900436</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05099802407486681</v>
+        <v>0.05316079015098499</v>
       </c>
       <c r="W97">
-        <v>0.2332646856823977</v>
+        <v>0.2232646856823978</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2318092003403036</v>
+        <v>0.24163995523175</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2652035564840955</v>
+        <v>0.2554934526445722</v>
       </c>
       <c r="C98">
-        <v>-3777.412612778031</v>
+        <v>-3725.708395757106</v>
       </c>
       <c r="D98">
-        <v>1220.091387221968</v>
+        <v>1271.795604242893</v>
       </c>
       <c r="E98">
         <v>2976.303999999999</v>
@@ -9329,37 +9329,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M98">
-        <v>1444.6904832</v>
+        <v>1385.9154432</v>
       </c>
       <c r="N98">
-        <v>-1113.286401567347</v>
+        <v>-1054.511361567347</v>
       </c>
       <c r="O98">
-        <v>-244.9230083448163</v>
+        <v>-231.9924995448163</v>
       </c>
       <c r="P98">
-        <v>-868.3633932225305</v>
+        <v>-822.5188620225305</v>
       </c>
       <c r="Q98">
-        <v>-644.5633932225305</v>
+        <v>-598.7188620225304</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.028602627145441</v>
+        <v>1.025850031157358</v>
       </c>
       <c r="T98">
-        <v>22.68292776992355</v>
+        <v>22.63394991125539</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05046679465742029</v>
+        <v>0.05260703192024558</v>
       </c>
       <c r="W98">
-        <v>0.2333952618732061</v>
+        <v>0.2233952618732061</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2293945211700922</v>
+        <v>0.2391228723647526</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2672035564840956</v>
+        <v>0.2573934526445723</v>
       </c>
       <c r="C99">
-        <v>-3848.797025816409</v>
+        <v>-3797.421287055118</v>
       </c>
       <c r="D99">
-        <v>1209.93097418359</v>
+        <v>1261.306712944881</v>
       </c>
       <c r="E99">
         <v>3037.527999999999</v>
@@ -9411,37 +9411,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M99">
-        <v>1459.7393424</v>
+        <v>1400.3520624</v>
       </c>
       <c r="N99">
-        <v>-1128.335260767347</v>
+        <v>-1068.947980767347</v>
       </c>
       <c r="O99">
-        <v>-248.2337573688163</v>
+        <v>-235.1685557688163</v>
       </c>
       <c r="P99">
-        <v>-880.1015033985306</v>
+        <v>-833.7794249985304</v>
       </c>
       <c r="Q99">
-        <v>-656.3015033985305</v>
+        <v>-609.9794249985305</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.356203502860588</v>
+        <v>1.352533374876478</v>
       </c>
       <c r="T99">
-        <v>30.24390369323141</v>
+        <v>30.17859988167386</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04994651842383863</v>
+        <v>0.05206469138498531</v>
       </c>
       <c r="W99">
-        <v>0.2335231457714205</v>
+        <v>0.2235231457714205</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2270296291992665</v>
+        <v>0.2366576881135696</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2692035564840956</v>
+        <v>0.2592934526445722</v>
       </c>
       <c r="C100">
-        <v>-3920.013613059956</v>
+        <v>-3868.962583295959</v>
       </c>
       <c r="D100">
-        <v>1199.938386940043</v>
+        <v>1250.98941670404</v>
       </c>
       <c r="E100">
         <v>3098.751999999999</v>
@@ -9493,37 +9493,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M100">
-        <v>1474.7882016</v>
+        <v>1414.7886816</v>
       </c>
       <c r="N100">
-        <v>-1143.384119967347</v>
+        <v>-1083.384599967347</v>
       </c>
       <c r="O100">
-        <v>-251.5445063928163</v>
+        <v>-238.3446119928163</v>
       </c>
       <c r="P100">
-        <v>-891.8396135745305</v>
+        <v>-845.0399879745305</v>
       </c>
       <c r="Q100">
-        <v>-668.0396135745304</v>
+        <v>-621.2399879745305</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.011405254290882</v>
+        <v>2.005900062314717</v>
       </c>
       <c r="T100">
-        <v>45.3658555398471</v>
+        <v>45.26789982251078</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04943686007257497</v>
+        <v>0.05153341902391403</v>
       </c>
       <c r="W100">
-        <v>0.2336484197941611</v>
+        <v>0.2236484197941611</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2247130003298862</v>
+        <v>0.2342428137450637</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2712035564840956</v>
+        <v>0.2611934526445723</v>
       </c>
       <c r="C101">
-        <v>-3991.066498571727</v>
+        <v>-3940.336461178933</v>
       </c>
       <c r="D101">
-        <v>1190.109501428273</v>
+        <v>1240.839538821067</v>
       </c>
       <c r="E101">
         <v>3159.976</v>
@@ -9575,37 +9575,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M101">
-        <v>1489.8370608</v>
+        <v>1429.2253008</v>
       </c>
       <c r="N101">
-        <v>-1158.432979167347</v>
+        <v>-1097.821219167347</v>
       </c>
       <c r="O101">
-        <v>-254.8552554168163</v>
+        <v>-241.5206682168163</v>
       </c>
       <c r="P101">
-        <v>-903.5777237505306</v>
+        <v>-856.3005509505306</v>
       </c>
       <c r="Q101">
-        <v>-679.7777237505306</v>
+        <v>-632.5005509505306</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.977010508581763</v>
+        <v>3.966000124629434</v>
       </c>
       <c r="T101">
-        <v>90.73171107969421</v>
+        <v>90.53579964502158</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.04893749784961967</v>
+        <v>0.05101287943781389</v>
       </c>
       <c r="W101">
-        <v>0.2337711630285635</v>
+        <v>0.2237711630285635</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2224431720437258</v>
+        <v>0.2318767247173358</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/denmark/denmark_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_business_consumer_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08708711407311603</v>
+        <v>0.0869306224221552</v>
       </c>
       <c r="C2">
-        <v>5717.167489285272</v>
+        <v>5668.577586835087</v>
       </c>
       <c r="D2">
-        <v>4837.167489285272</v>
+        <v>4849.801586835088</v>
       </c>
       <c r="E2">
-        <v>-2901.2</v>
+        <v>-2839.976</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>61.224</v>
       </c>
       <c r="G2">
         <v>880</v>
@@ -1457,28 +1457,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.0795672</v>
       </c>
       <c r="N2">
-        <v>331.4040816326531</v>
+        <v>328.3245144326531</v>
       </c>
       <c r="O2">
-        <v>72.90889795918369</v>
+        <v>72.23139317518368</v>
       </c>
       <c r="P2">
-        <v>258.4951836734695</v>
+        <v>256.0931212574694</v>
       </c>
       <c r="Q2">
-        <v>482.2951836734695</v>
+        <v>479.8931212574694</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08708711407311603</v>
+        <v>0.08741240648702545</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9610255539728739</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>107.6138496450583</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0869306224221552</v>
+        <v>0.08677413077119434</v>
       </c>
       <c r="C3">
-        <v>5668.577586835087</v>
+        <v>5620.053854689033</v>
       </c>
       <c r="D3">
-        <v>4849.801586835088</v>
+        <v>4862.501854689033</v>
       </c>
       <c r="E3">
-        <v>-2839.976</v>
+        <v>-2778.752</v>
       </c>
       <c r="F3">
-        <v>61.224</v>
+        <v>122.448</v>
       </c>
       <c r="G3">
         <v>880</v>
@@ -1539,28 +1539,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M3">
-        <v>3.0795672</v>
+        <v>6.1591344</v>
       </c>
       <c r="N3">
-        <v>328.3245144326531</v>
+        <v>325.2449472326531</v>
       </c>
       <c r="O3">
-        <v>72.23139317518368</v>
+        <v>71.55388839118368</v>
       </c>
       <c r="P3">
-        <v>256.0931212574694</v>
+        <v>253.6910588414694</v>
       </c>
       <c r="Q3">
-        <v>479.8931212574694</v>
+        <v>477.4910588414695</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08741240648702545</v>
+        <v>0.08774433752162687</v>
       </c>
       <c r="T3">
-        <v>0.9610255539728739</v>
+        <v>0.9686913977281033</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>107.6138496450583</v>
+        <v>53.80692482252913</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08677413077119434</v>
+        <v>0.08661763912023347</v>
       </c>
       <c r="C4">
-        <v>5620.053854689033</v>
+        <v>5571.596814056315</v>
       </c>
       <c r="D4">
-        <v>4862.501854689033</v>
+        <v>4875.268814056314</v>
       </c>
       <c r="E4">
-        <v>-2778.752</v>
+        <v>-2717.528</v>
       </c>
       <c r="F4">
-        <v>122.448</v>
+        <v>183.672</v>
       </c>
       <c r="G4">
         <v>880</v>
@@ -1621,28 +1621,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M4">
-        <v>6.1591344</v>
+        <v>9.238701599999999</v>
       </c>
       <c r="N4">
-        <v>325.2449472326531</v>
+        <v>322.1653800326531</v>
       </c>
       <c r="O4">
-        <v>71.55388839118368</v>
+        <v>70.87638360718368</v>
       </c>
       <c r="P4">
-        <v>253.6910588414694</v>
+        <v>251.2889964254694</v>
       </c>
       <c r="Q4">
-        <v>477.4910588414695</v>
+        <v>475.0889964254694</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08774433752162687</v>
+        <v>0.08808311249508606</v>
       </c>
       <c r="T4">
-        <v>0.9686913977281033</v>
+        <v>0.976515300117461</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.80692482252913</v>
+        <v>35.87128321501943</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08661763912023347</v>
+        <v>0.08646114746927261</v>
       </c>
       <c r="C5">
-        <v>5571.596814056315</v>
+        <v>5523.20699163449</v>
       </c>
       <c r="D5">
-        <v>4875.268814056314</v>
+        <v>4888.10299163449</v>
       </c>
       <c r="E5">
-        <v>-2717.528</v>
+        <v>-2656.304</v>
       </c>
       <c r="F5">
-        <v>183.672</v>
+        <v>244.896</v>
       </c>
       <c r="G5">
         <v>880</v>
@@ -1703,28 +1703,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M5">
-        <v>9.238701599999999</v>
+        <v>12.3182688</v>
       </c>
       <c r="N5">
-        <v>322.1653800326531</v>
+        <v>319.0858128326531</v>
       </c>
       <c r="O5">
-        <v>70.87638360718368</v>
+        <v>70.19887882318369</v>
       </c>
       <c r="P5">
-        <v>251.2889964254694</v>
+        <v>248.8869340094694</v>
       </c>
       <c r="Q5">
-        <v>475.0889964254694</v>
+        <v>472.6869340094694</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08808311249508606</v>
+        <v>0.0884289452804923</v>
       </c>
       <c r="T5">
-        <v>0.976515300117461</v>
+        <v>0.9845022004732636</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.87128321501943</v>
+        <v>26.90346241126457</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08646114746927261</v>
+        <v>0.08630465581831177</v>
       </c>
       <c r="C6">
-        <v>5523.20699163449</v>
+        <v>5474.884919681891</v>
       </c>
       <c r="D6">
-        <v>4888.10299163449</v>
+        <v>4901.004919681891</v>
       </c>
       <c r="E6">
-        <v>-2656.304</v>
+        <v>-2595.08</v>
       </c>
       <c r="F6">
-        <v>244.896</v>
+        <v>306.12</v>
       </c>
       <c r="G6">
         <v>880</v>
@@ -1785,28 +1785,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M6">
-        <v>12.3182688</v>
+        <v>15.397836</v>
       </c>
       <c r="N6">
-        <v>319.0858128326531</v>
+        <v>316.0062456326531</v>
       </c>
       <c r="O6">
-        <v>70.19887882318369</v>
+        <v>69.52137403918368</v>
       </c>
       <c r="P6">
-        <v>248.8869340094694</v>
+        <v>246.4848715934694</v>
       </c>
       <c r="Q6">
-        <v>472.6869340094694</v>
+        <v>470.2848715934695</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0884289452804923</v>
+        <v>0.08878205875611767</v>
       </c>
       <c r="T6">
-        <v>0.9845022004732636</v>
+        <v>0.992657246099715</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.90346241126457</v>
+        <v>21.52276992901166</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08630465581831177</v>
+        <v>0.08614816416735091</v>
       </c>
       <c r="C7">
-        <v>5474.884919681891</v>
+        <v>5426.631136091219</v>
       </c>
       <c r="D7">
-        <v>4901.004919681891</v>
+        <v>4913.975136091219</v>
       </c>
       <c r="E7">
-        <v>-2595.08</v>
+        <v>-2533.856</v>
       </c>
       <c r="F7">
-        <v>306.12</v>
+        <v>367.344</v>
       </c>
       <c r="G7">
         <v>880</v>
@@ -1867,28 +1867,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M7">
-        <v>15.397836</v>
+        <v>18.4774032</v>
       </c>
       <c r="N7">
-        <v>316.0062456326531</v>
+        <v>312.9266784326531</v>
       </c>
       <c r="O7">
-        <v>69.52137403918368</v>
+        <v>68.84386925518368</v>
       </c>
       <c r="P7">
-        <v>246.4848715934694</v>
+        <v>244.0828091774694</v>
       </c>
       <c r="Q7">
-        <v>470.2848715934695</v>
+        <v>467.8828091774694</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08878205875611767</v>
+        <v>0.08914268528441587</v>
       </c>
       <c r="T7">
-        <v>0.992657246099715</v>
+        <v>1.000985803335239</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.52276992901166</v>
+        <v>17.93564160750971</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08614816416735091</v>
+        <v>0.08599167251639006</v>
       </c>
       <c r="C8">
-        <v>5426.631136091219</v>
+        <v>5378.446184464276</v>
       </c>
       <c r="D8">
-        <v>4913.975136091219</v>
+        <v>4927.014184464276</v>
       </c>
       <c r="E8">
-        <v>-2533.856</v>
+        <v>-2472.632</v>
       </c>
       <c r="F8">
-        <v>367.3439999999999</v>
+        <v>428.5679999999999</v>
       </c>
       <c r="G8">
         <v>880</v>
@@ -1949,28 +1949,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M8">
-        <v>18.4774032</v>
+        <v>21.5569704</v>
       </c>
       <c r="N8">
-        <v>312.9266784326531</v>
+        <v>309.8471112326531</v>
       </c>
       <c r="O8">
-        <v>68.84386925518369</v>
+        <v>68.16636447118368</v>
       </c>
       <c r="P8">
-        <v>244.0828091774695</v>
+        <v>241.6807467614694</v>
       </c>
       <c r="Q8">
-        <v>467.8828091774695</v>
+        <v>465.4807467614694</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08914268528441587</v>
+        <v>0.08951106722192478</v>
       </c>
       <c r="T8">
-        <v>1.000985803335239</v>
+        <v>1.009493469328517</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.93564160750972</v>
+        <v>15.37340709215118</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08599167251639006</v>
+        <v>0.08583518086542921</v>
       </c>
       <c r="C9">
-        <v>5378.446184464276</v>
+        <v>5330.330614187928</v>
       </c>
       <c r="D9">
-        <v>4927.014184464276</v>
+        <v>4940.122614187929</v>
       </c>
       <c r="E9">
-        <v>-2472.632</v>
+        <v>-2411.408</v>
       </c>
       <c r="F9">
-        <v>428.568</v>
+        <v>489.792</v>
       </c>
       <c r="G9">
         <v>880</v>
@@ -2031,28 +2031,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M9">
-        <v>21.5569704</v>
+        <v>24.6365376</v>
       </c>
       <c r="N9">
-        <v>309.8471112326531</v>
+        <v>306.7675440326531</v>
       </c>
       <c r="O9">
-        <v>68.16636447118368</v>
+        <v>67.48885968718369</v>
       </c>
       <c r="P9">
-        <v>241.6807467614694</v>
+        <v>239.2786843454694</v>
       </c>
       <c r="Q9">
-        <v>465.4807467614694</v>
+        <v>463.0786843454695</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0895110672219248</v>
+        <v>0.08988745746242305</v>
       </c>
       <c r="T9">
-        <v>1.009493469328517</v>
+        <v>1.018186084582518</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.37340709215118</v>
+        <v>13.45173120563229</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08583518086542921</v>
+        <v>0.08578398921446836</v>
       </c>
       <c r="C10">
-        <v>5330.330614187928</v>
+        <v>5273.409805809099</v>
       </c>
       <c r="D10">
-        <v>4940.122614187929</v>
+        <v>4944.425805809099</v>
       </c>
       <c r="E10">
-        <v>-2411.408</v>
+        <v>-2350.184</v>
       </c>
       <c r="F10">
-        <v>489.792</v>
+        <v>551.016</v>
       </c>
       <c r="G10">
         <v>880</v>
@@ -2113,45 +2113,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M10">
-        <v>24.6365376</v>
+        <v>28.5426288</v>
       </c>
       <c r="N10">
-        <v>306.7675440326531</v>
+        <v>302.8614528326531</v>
       </c>
       <c r="O10">
-        <v>67.48885968718369</v>
+        <v>66.62951962318368</v>
       </c>
       <c r="P10">
-        <v>239.2786843454694</v>
+        <v>236.2319332094694</v>
       </c>
       <c r="Q10">
-        <v>463.0786843454695</v>
+        <v>460.0319332094695</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08988745746242305</v>
+        <v>0.09027212001589929</v>
       </c>
       <c r="T10">
-        <v>1.018186084582518</v>
+        <v>1.027069746325619</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.45173120563229</v>
+        <v>11.61084649752559</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08578398921446836</v>
+        <v>0.08563919756350749</v>
       </c>
       <c r="C11">
-        <v>5273.409805809099</v>
+        <v>5224.397741845968</v>
       </c>
       <c r="D11">
-        <v>4944.425805809099</v>
+        <v>4956.637741845968</v>
       </c>
       <c r="E11">
-        <v>-2350.184</v>
+        <v>-2288.96</v>
       </c>
       <c r="F11">
-        <v>551.016</v>
+        <v>612.2399999999999</v>
       </c>
       <c r="G11">
         <v>880</v>
@@ -2195,28 +2195,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M11">
-        <v>28.5426288</v>
+        <v>31.714032</v>
       </c>
       <c r="N11">
-        <v>302.8614528326531</v>
+        <v>299.6900496326531</v>
       </c>
       <c r="O11">
-        <v>66.62951962318368</v>
+        <v>65.93181091918369</v>
       </c>
       <c r="P11">
-        <v>236.2319332094694</v>
+        <v>233.7582387134694</v>
       </c>
       <c r="Q11">
-        <v>460.0319332094695</v>
+        <v>457.5582387134694</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09027212001589929</v>
+        <v>0.09066533062611944</v>
       </c>
       <c r="T11">
-        <v>1.027069746325619</v>
+        <v>1.036150822774121</v>
       </c>
       <c r="U11">
         <v>0.05180000000000001</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.61084649752559</v>
+        <v>10.44976184777303</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08563919756350749</v>
+        <v>0.08564026591254666</v>
       </c>
       <c r="C12">
-        <v>5224.397741845968</v>
+        <v>5163.08341485038</v>
       </c>
       <c r="D12">
-        <v>4956.637741845968</v>
+        <v>4956.54741485038</v>
       </c>
       <c r="E12">
-        <v>-2288.96</v>
+        <v>-2227.736</v>
       </c>
       <c r="F12">
-        <v>612.24</v>
+        <v>673.4639999999999</v>
       </c>
       <c r="G12">
         <v>880</v>
@@ -2277,45 +2277,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M12">
-        <v>31.714032</v>
+        <v>36.030324</v>
       </c>
       <c r="N12">
-        <v>299.6900496326531</v>
+        <v>295.3737576326531</v>
       </c>
       <c r="O12">
-        <v>65.93181091918368</v>
+        <v>64.98222667918368</v>
       </c>
       <c r="P12">
-        <v>233.7582387134694</v>
+        <v>230.3915309534694</v>
       </c>
       <c r="Q12">
-        <v>457.5582387134694</v>
+        <v>454.1915309534695</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09066533062611944</v>
+        <v>0.09106737742982769</v>
       </c>
       <c r="T12">
-        <v>1.036150822774121</v>
+        <v>1.045435968356298</v>
       </c>
       <c r="U12">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.44976184777303</v>
+        <v>9.197921218600563</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08564026591254666</v>
+        <v>0.08550873426158578</v>
       </c>
       <c r="C13">
-        <v>5163.08341485038</v>
+        <v>5113.00498374607</v>
       </c>
       <c r="D13">
-        <v>4956.54741485038</v>
+        <v>4967.69298374607</v>
       </c>
       <c r="E13">
-        <v>-2227.736</v>
+        <v>-2166.512</v>
       </c>
       <c r="F13">
-        <v>673.4639999999999</v>
+        <v>734.6879999999999</v>
       </c>
       <c r="G13">
         <v>880</v>
@@ -2359,28 +2359,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M13">
-        <v>36.030324</v>
+        <v>39.305808</v>
       </c>
       <c r="N13">
-        <v>295.3737576326531</v>
+        <v>292.0982736326531</v>
       </c>
       <c r="O13">
-        <v>64.98222667918368</v>
+        <v>64.26162019918368</v>
       </c>
       <c r="P13">
-        <v>230.3915309534694</v>
+        <v>227.8366534334694</v>
       </c>
       <c r="Q13">
-        <v>454.1915309534695</v>
+        <v>451.6366534334694</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09106737742982769</v>
+        <v>0.09147856166089294</v>
       </c>
       <c r="T13">
-        <v>1.045435968356298</v>
+        <v>1.054932139974433</v>
       </c>
       <c r="U13">
         <v>0.05350000000000001</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.197921218600563</v>
+        <v>8.431427783717183</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08550873426158578</v>
+        <v>0.08537720261062492</v>
       </c>
       <c r="C14">
-        <v>5113.00498374607</v>
+        <v>5062.976790705267</v>
       </c>
       <c r="D14">
-        <v>4967.69298374607</v>
+        <v>4978.888790705268</v>
       </c>
       <c r="E14">
-        <v>-2166.512</v>
+        <v>-2105.288</v>
       </c>
       <c r="F14">
-        <v>734.6879999999999</v>
+        <v>795.912</v>
       </c>
       <c r="G14">
         <v>880</v>
@@ -2441,28 +2441,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M14">
-        <v>39.305808</v>
+        <v>42.581292</v>
       </c>
       <c r="N14">
-        <v>292.0982736326531</v>
+        <v>288.8227896326531</v>
       </c>
       <c r="O14">
-        <v>64.26162019918368</v>
+        <v>63.54101371918368</v>
       </c>
       <c r="P14">
-        <v>227.8366534334694</v>
+        <v>225.2817759134694</v>
       </c>
       <c r="Q14">
-        <v>451.6366534334694</v>
+        <v>449.0817759134694</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09147856166089294</v>
+        <v>0.09189919840301716</v>
       </c>
       <c r="T14">
-        <v>1.054932139974433</v>
+        <v>1.064646614388387</v>
       </c>
       <c r="U14">
         <v>0.05350000000000001</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.431427783717183</v>
+        <v>7.782856415738937</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08537720261062492</v>
+        <v>0.08533303095966409</v>
       </c>
       <c r="C15">
-        <v>5062.976790705267</v>
+        <v>5005.523953355429</v>
       </c>
       <c r="D15">
-        <v>4978.888790705268</v>
+        <v>4982.659953355429</v>
       </c>
       <c r="E15">
-        <v>-2105.288</v>
+        <v>-2044.064</v>
       </c>
       <c r="F15">
-        <v>795.912</v>
+        <v>857.1360000000001</v>
       </c>
       <c r="G15">
         <v>880</v>
@@ -2523,45 +2523,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M15">
-        <v>42.581292</v>
+        <v>46.54248480000001</v>
       </c>
       <c r="N15">
-        <v>288.8227896326531</v>
+        <v>284.8615968326531</v>
       </c>
       <c r="O15">
-        <v>63.54101371918368</v>
+        <v>62.66955130318368</v>
       </c>
       <c r="P15">
-        <v>225.2817759134694</v>
+        <v>222.1920455294694</v>
       </c>
       <c r="Q15">
-        <v>449.0817759134694</v>
+        <v>445.9920455294695</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09189919840301716</v>
+        <v>0.09232961739495824</v>
       </c>
       <c r="T15">
-        <v>1.064646614388387</v>
+        <v>1.074587006811968</v>
       </c>
       <c r="U15">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04173</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.782856415738937</v>
+        <v>7.120463874173152</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08533303095966409</v>
+        <v>0.08520773930870321</v>
       </c>
       <c r="C16">
-        <v>5005.523953355429</v>
+        <v>4955.027900937132</v>
       </c>
       <c r="D16">
-        <v>4982.659953355429</v>
+        <v>4993.387900937132</v>
       </c>
       <c r="E16">
-        <v>-2044.064</v>
+        <v>-1982.84</v>
       </c>
       <c r="F16">
-        <v>857.1360000000001</v>
+        <v>918.3600000000001</v>
       </c>
       <c r="G16">
         <v>880</v>
@@ -2605,28 +2605,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M16">
-        <v>46.54248480000001</v>
+        <v>49.86694800000001</v>
       </c>
       <c r="N16">
-        <v>284.8615968326531</v>
+        <v>281.5371336326531</v>
       </c>
       <c r="O16">
-        <v>62.66955130318368</v>
+        <v>61.93816939918368</v>
       </c>
       <c r="P16">
-        <v>222.1920455294694</v>
+        <v>219.5989642334694</v>
       </c>
       <c r="Q16">
-        <v>445.9920455294695</v>
+        <v>443.3989642334694</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09232961739495824</v>
+        <v>0.09277016389259202</v>
       </c>
       <c r="T16">
-        <v>1.074587006811968</v>
+        <v>1.084761290821987</v>
       </c>
       <c r="U16">
         <v>0.05430000000000001</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.120463874173152</v>
+        <v>6.645766282561608</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08520773930870321</v>
+        <v>0.08508244765774235</v>
       </c>
       <c r="C17">
-        <v>4955.027900937132</v>
+        <v>4904.57814394652</v>
       </c>
       <c r="D17">
-        <v>4993.387900937132</v>
+        <v>5004.16214394652</v>
       </c>
       <c r="E17">
-        <v>-1982.84</v>
+        <v>-1921.616</v>
       </c>
       <c r="F17">
-        <v>918.3599999999999</v>
+        <v>979.5839999999999</v>
       </c>
       <c r="G17">
         <v>880</v>
@@ -2687,28 +2687,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M17">
-        <v>49.866948</v>
+        <v>53.1914112</v>
       </c>
       <c r="N17">
-        <v>281.5371336326531</v>
+        <v>278.2126704326531</v>
       </c>
       <c r="O17">
-        <v>61.93816939918369</v>
+        <v>61.20678749518368</v>
       </c>
       <c r="P17">
-        <v>219.5989642334694</v>
+        <v>217.0058829374694</v>
       </c>
       <c r="Q17">
-        <v>443.3989642334694</v>
+        <v>440.8058829374694</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09277016389259202</v>
+        <v>0.09322119959255043</v>
       </c>
       <c r="T17">
-        <v>1.084761290821987</v>
+        <v>1.095177819689386</v>
       </c>
       <c r="U17">
         <v>0.05430000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.645766282561611</v>
+        <v>6.230405889901509</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08508244765774235</v>
+        <v>0.08508975600678151</v>
       </c>
       <c r="C18">
-        <v>4904.57814394652</v>
+        <v>4842.724398078037</v>
       </c>
       <c r="D18">
-        <v>5004.16214394652</v>
+        <v>5003.532398078037</v>
       </c>
       <c r="E18">
-        <v>-1921.616</v>
+        <v>-1860.392</v>
       </c>
       <c r="F18">
-        <v>979.5839999999999</v>
+        <v>1040.808</v>
       </c>
       <c r="G18">
         <v>880</v>
@@ -2769,45 +2769,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M18">
-        <v>53.1914112</v>
+        <v>57.55668240000001</v>
       </c>
       <c r="N18">
-        <v>278.2126704326531</v>
+        <v>273.8473992326531</v>
       </c>
       <c r="O18">
-        <v>61.20678749518368</v>
+        <v>60.24642783118369</v>
       </c>
       <c r="P18">
-        <v>217.0058829374694</v>
+        <v>213.6009714014694</v>
       </c>
       <c r="Q18">
-        <v>440.8058829374694</v>
+        <v>437.4009714014694</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09322119959255043</v>
+        <v>0.09368310362262833</v>
       </c>
       <c r="T18">
-        <v>1.095177819689386</v>
+        <v>1.105845349252386</v>
       </c>
       <c r="U18">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04235400000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.230405889901509</v>
+        <v>5.75787324449147</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08508975600678151</v>
+        <v>0.08497226435582066</v>
       </c>
       <c r="C19">
-        <v>4842.724398078037</v>
+        <v>4791.643666436574</v>
       </c>
       <c r="D19">
-        <v>5003.532398078037</v>
+        <v>5013.675666436574</v>
       </c>
       <c r="E19">
-        <v>-1860.392</v>
+        <v>-1799.168</v>
       </c>
       <c r="F19">
-        <v>1040.808</v>
+        <v>1102.032</v>
       </c>
       <c r="G19">
         <v>880</v>
@@ -2851,28 +2851,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M19">
-        <v>57.55668240000001</v>
+        <v>60.94236960000002</v>
       </c>
       <c r="N19">
-        <v>273.8473992326531</v>
+        <v>270.4617120326531</v>
       </c>
       <c r="O19">
-        <v>60.24642783118369</v>
+        <v>59.50157664718368</v>
       </c>
       <c r="P19">
-        <v>213.6009714014694</v>
+        <v>210.9601353854694</v>
       </c>
       <c r="Q19">
-        <v>437.4009714014694</v>
+        <v>434.7601353854694</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09368310362262833</v>
+        <v>0.09415627360465934</v>
       </c>
       <c r="T19">
-        <v>1.105845349252386</v>
+        <v>1.116773062463264</v>
       </c>
       <c r="U19">
         <v>0.05530000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.75787324449147</v>
+        <v>5.437991397575276</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08497226435582066</v>
+        <v>0.0848547727048598</v>
       </c>
       <c r="C20">
-        <v>4791.643666436574</v>
+        <v>4740.604143637571</v>
       </c>
       <c r="D20">
-        <v>5013.675666436574</v>
+        <v>5023.860143637571</v>
       </c>
       <c r="E20">
-        <v>-1799.168</v>
+        <v>-1737.944</v>
       </c>
       <c r="F20">
-        <v>1102.032</v>
+        <v>1163.256</v>
       </c>
       <c r="G20">
         <v>880</v>
@@ -2933,28 +2933,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M20">
-        <v>60.94236960000001</v>
+        <v>64.3280568</v>
       </c>
       <c r="N20">
-        <v>270.4617120326531</v>
+        <v>267.0760248326531</v>
       </c>
       <c r="O20">
-        <v>59.50157664718368</v>
+        <v>58.75672546318368</v>
       </c>
       <c r="P20">
-        <v>210.9601353854694</v>
+        <v>208.3192993694694</v>
       </c>
       <c r="Q20">
-        <v>434.7601353854694</v>
+        <v>432.1192993694694</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09415627360465934</v>
+        <v>0.0946411267961232</v>
       </c>
       <c r="T20">
-        <v>1.116773062463264</v>
+        <v>1.127970595753423</v>
       </c>
       <c r="U20">
         <v>0.05530000000000001</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.437991397575277</v>
+        <v>5.151781324018684</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0848547727048598</v>
+        <v>0.08473728105389895</v>
       </c>
       <c r="C21">
-        <v>4740.604143637571</v>
+        <v>4689.606081319635</v>
       </c>
       <c r="D21">
-        <v>5023.860143637571</v>
+        <v>5034.086081319634</v>
       </c>
       <c r="E21">
-        <v>-1737.944</v>
+        <v>-1676.72</v>
       </c>
       <c r="F21">
-        <v>1163.256</v>
+        <v>1224.48</v>
       </c>
       <c r="G21">
         <v>880</v>
@@ -3015,28 +3015,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M21">
-        <v>64.3280568</v>
+        <v>67.71374400000001</v>
       </c>
       <c r="N21">
-        <v>267.0760248326531</v>
+        <v>263.6903376326531</v>
       </c>
       <c r="O21">
-        <v>58.75672546318368</v>
+        <v>58.01187427918368</v>
       </c>
       <c r="P21">
-        <v>208.3192993694694</v>
+        <v>205.6784633534694</v>
       </c>
       <c r="Q21">
-        <v>432.1192993694694</v>
+        <v>429.4784633534695</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0946411267961232</v>
+        <v>0.09513810131737369</v>
       </c>
       <c r="T21">
-        <v>1.127970595753423</v>
+        <v>1.139448067375836</v>
       </c>
       <c r="U21">
         <v>0.05530000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.151781324018684</v>
+        <v>4.89419225781775</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08473728105389895</v>
+        <v>0.0846197894029381</v>
       </c>
       <c r="C22">
-        <v>4689.606081319635</v>
+        <v>4638.649733174364</v>
       </c>
       <c r="D22">
-        <v>5034.086081319634</v>
+        <v>5044.353733174364</v>
       </c>
       <c r="E22">
-        <v>-1676.72</v>
+        <v>-1615.496</v>
       </c>
       <c r="F22">
-        <v>1224.48</v>
+        <v>1285.704</v>
       </c>
       <c r="G22">
         <v>880</v>
@@ -3097,28 +3097,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M22">
-        <v>67.71374400000001</v>
+        <v>71.09943120000001</v>
       </c>
       <c r="N22">
-        <v>263.6903376326531</v>
+        <v>260.3046504326531</v>
       </c>
       <c r="O22">
-        <v>58.01187427918368</v>
+        <v>57.26702309518368</v>
       </c>
       <c r="P22">
-        <v>205.6784633534694</v>
+        <v>203.0376273374694</v>
       </c>
       <c r="Q22">
-        <v>429.4784633534695</v>
+        <v>426.8376273374694</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09513810131737369</v>
+        <v>0.09564765747207353</v>
       </c>
       <c r="T22">
-        <v>1.139448067375836</v>
+        <v>1.151216107900082</v>
       </c>
       <c r="U22">
         <v>0.05530000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.89419225781775</v>
+        <v>4.661135483635951</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08461978940293809</v>
+        <v>0.08493129775197723</v>
       </c>
       <c r="C23">
-        <v>4638.649733174365</v>
+        <v>4550.294064480369</v>
       </c>
       <c r="D23">
-        <v>5044.353733174365</v>
+        <v>5017.222064480369</v>
       </c>
       <c r="E23">
-        <v>-1615.496</v>
+        <v>-1554.272</v>
       </c>
       <c r="F23">
-        <v>1285.704</v>
+        <v>1346.928</v>
       </c>
       <c r="G23">
         <v>880</v>
@@ -3179,45 +3179,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M23">
-        <v>71.09943120000001</v>
+        <v>77.8524384</v>
       </c>
       <c r="N23">
-        <v>260.3046504326531</v>
+        <v>253.5516432326531</v>
       </c>
       <c r="O23">
-        <v>57.26702309518368</v>
+        <v>55.78136151118369</v>
       </c>
       <c r="P23">
-        <v>203.0376273374694</v>
+        <v>197.7702817214694</v>
       </c>
       <c r="Q23">
-        <v>426.8376273374694</v>
+        <v>421.5702817214694</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09564765747207352</v>
+        <v>0.09617027916920157</v>
       </c>
       <c r="T23">
-        <v>1.151216107900081</v>
+        <v>1.163285893053154</v>
       </c>
       <c r="U23">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.661135483635951</v>
+        <v>4.256823401341956</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08493129775197723</v>
+        <v>0.08483330610101637</v>
       </c>
       <c r="C24">
-        <v>4550.294064480369</v>
+        <v>4497.573395982321</v>
       </c>
       <c r="D24">
-        <v>5017.222064480369</v>
+        <v>5025.725395982321</v>
       </c>
       <c r="E24">
-        <v>-1554.272</v>
+        <v>-1493.048</v>
       </c>
       <c r="F24">
-        <v>1346.928</v>
+        <v>1408.152</v>
       </c>
       <c r="G24">
         <v>880</v>
@@ -3261,28 +3261,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M24">
-        <v>77.8524384</v>
+        <v>81.39118560000001</v>
       </c>
       <c r="N24">
-        <v>253.5516432326531</v>
+        <v>250.0128960326531</v>
       </c>
       <c r="O24">
-        <v>55.78136151118369</v>
+        <v>55.00283712718368</v>
       </c>
       <c r="P24">
-        <v>197.7702817214694</v>
+        <v>195.0100589054694</v>
       </c>
       <c r="Q24">
-        <v>421.5702817214694</v>
+        <v>418.8100589054694</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09617027916920157</v>
+        <v>0.09670647545586541</v>
       </c>
       <c r="T24">
-        <v>1.163285893053154</v>
+        <v>1.175669179119294</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.256823401341956</v>
+        <v>4.071744123022739</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08483330610101637</v>
+        <v>0.08539051445005552</v>
       </c>
       <c r="C25">
-        <v>4497.573395982321</v>
+        <v>4388.377409157563</v>
       </c>
       <c r="D25">
-        <v>5025.725395982321</v>
+        <v>4977.753409157564</v>
       </c>
       <c r="E25">
-        <v>-1493.048</v>
+        <v>-1431.824</v>
       </c>
       <c r="F25">
-        <v>1408.152</v>
+        <v>1469.376</v>
       </c>
       <c r="G25">
         <v>880</v>
@@ -3343,45 +3343,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M25">
-        <v>81.39118560000001</v>
+        <v>90.07274880000001</v>
       </c>
       <c r="N25">
-        <v>250.0128960326531</v>
+        <v>241.3313328326531</v>
       </c>
       <c r="O25">
-        <v>55.00283712718368</v>
+        <v>53.09289322318369</v>
       </c>
       <c r="P25">
-        <v>195.0100589054694</v>
+        <v>188.2384396094694</v>
       </c>
       <c r="Q25">
-        <v>418.8100589054694</v>
+        <v>412.0384396094694</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09670647545586541</v>
+        <v>0.09725678217112568</v>
       </c>
       <c r="T25">
-        <v>1.175669179119294</v>
+        <v>1.188378341134542</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04508400000000001</v>
+        <v>0.04781400000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.071744123022739</v>
+        <v>3.679293527152278</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08539051445005552</v>
+        <v>0.08531982279909467</v>
       </c>
       <c r="C26">
-        <v>4388.377409157563</v>
+        <v>4333.18871220515</v>
       </c>
       <c r="D26">
-        <v>4977.753409157564</v>
+        <v>4983.788712205151</v>
       </c>
       <c r="E26">
-        <v>-1431.824</v>
+        <v>-1370.6</v>
       </c>
       <c r="F26">
-        <v>1469.376</v>
+        <v>1530.6</v>
       </c>
       <c r="G26">
         <v>880</v>
@@ -3425,28 +3425,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M26">
-        <v>90.0727488</v>
+        <v>93.82578000000001</v>
       </c>
       <c r="N26">
-        <v>241.3313328326531</v>
+        <v>237.5783016326531</v>
       </c>
       <c r="O26">
-        <v>53.09289322318369</v>
+        <v>52.26722635918368</v>
       </c>
       <c r="P26">
-        <v>188.2384396094694</v>
+        <v>185.3110752734694</v>
       </c>
       <c r="Q26">
-        <v>412.0384396094694</v>
+        <v>409.1110752734695</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09725678217112568</v>
+        <v>0.09782176373212623</v>
       </c>
       <c r="T26">
-        <v>1.188378341134542</v>
+        <v>1.201426414136864</v>
       </c>
       <c r="U26">
         <v>0.06130000000000001</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.679293527152278</v>
+        <v>3.532121786066186</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08531982279909467</v>
+        <v>0.08581697114813382</v>
       </c>
       <c r="C27">
-        <v>4333.18871220515</v>
+        <v>4229.828472070334</v>
       </c>
       <c r="D27">
-        <v>4983.788712205151</v>
+        <v>4941.652472070335</v>
       </c>
       <c r="E27">
-        <v>-1370.6</v>
+        <v>-1309.376</v>
       </c>
       <c r="F27">
-        <v>1530.6</v>
+        <v>1591.824</v>
       </c>
       <c r="G27">
         <v>880</v>
@@ -3507,45 +3507,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M27">
-        <v>93.82578000000001</v>
+        <v>102.0359184</v>
       </c>
       <c r="N27">
-        <v>237.5783016326531</v>
+        <v>229.3681632326531</v>
       </c>
       <c r="O27">
-        <v>52.26722635918368</v>
+        <v>50.46099591118368</v>
       </c>
       <c r="P27">
-        <v>185.3110752734694</v>
+        <v>178.9071673214694</v>
       </c>
       <c r="Q27">
-        <v>409.1110752734695</v>
+        <v>402.7071673214695</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09782176373212623</v>
+        <v>0.09840201506504569</v>
       </c>
       <c r="T27">
-        <v>1.201426414136864</v>
+        <v>1.21482713776087</v>
       </c>
       <c r="U27">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.04781400000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.532121786066186</v>
+        <v>3.247915898923815</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08581697114813382</v>
+        <v>0.08576811949717296</v>
       </c>
       <c r="C28">
-        <v>4229.828472070334</v>
+        <v>4172.713343556555</v>
       </c>
       <c r="D28">
-        <v>4941.652472070335</v>
+        <v>4945.761343556554</v>
       </c>
       <c r="E28">
-        <v>-1309.376</v>
+        <v>-1248.152</v>
       </c>
       <c r="F28">
-        <v>1591.824</v>
+        <v>1653.048</v>
       </c>
       <c r="G28">
         <v>880</v>
@@ -3589,28 +3589,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M28">
-        <v>102.0359184</v>
+        <v>105.9603768</v>
       </c>
       <c r="N28">
-        <v>229.3681632326531</v>
+        <v>225.4437048326531</v>
       </c>
       <c r="O28">
-        <v>50.46099591118368</v>
+        <v>49.59761506318368</v>
       </c>
       <c r="P28">
-        <v>178.9071673214694</v>
+        <v>175.8460897694694</v>
       </c>
       <c r="Q28">
-        <v>402.7071673214695</v>
+        <v>399.6460897694694</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09840201506504569</v>
+        <v>0.09899816369475747</v>
       </c>
       <c r="T28">
-        <v>1.21482713776087</v>
+        <v>1.228595004497863</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.247915898923815</v>
+        <v>3.127622717482193</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08576811949717296</v>
+        <v>0.0857192678462121</v>
       </c>
       <c r="C29">
-        <v>4172.713343556555</v>
+        <v>4115.605053595</v>
       </c>
       <c r="D29">
-        <v>4945.761343556554</v>
+        <v>4949.877053595</v>
       </c>
       <c r="E29">
-        <v>-1248.152</v>
+        <v>-1186.928</v>
       </c>
       <c r="F29">
-        <v>1653.048</v>
+        <v>1714.272</v>
       </c>
       <c r="G29">
         <v>880</v>
@@ -3671,28 +3671,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M29">
-        <v>105.9603768</v>
+        <v>109.8848352</v>
       </c>
       <c r="N29">
-        <v>225.4437048326531</v>
+        <v>221.5192464326531</v>
       </c>
       <c r="O29">
-        <v>49.59761506318368</v>
+        <v>48.73423421518368</v>
       </c>
       <c r="P29">
-        <v>175.8460897694694</v>
+        <v>172.7850122174694</v>
       </c>
       <c r="Q29">
-        <v>399.6460897694694</v>
+        <v>396.5850122174695</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09899816369475747</v>
+        <v>0.09961087200862792</v>
       </c>
       <c r="T29">
-        <v>1.228595004497863</v>
+        <v>1.24274531197755</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.127622717482193</v>
+        <v>3.015921906143543</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0857192678462121</v>
+        <v>0.08743477619525125</v>
       </c>
       <c r="C30">
-        <v>4115.605053595</v>
+        <v>3913.837761429974</v>
       </c>
       <c r="D30">
-        <v>4949.877053595</v>
+        <v>4809.333761429974</v>
       </c>
       <c r="E30">
-        <v>-1186.928</v>
+        <v>-1125.704</v>
       </c>
       <c r="F30">
-        <v>1714.272</v>
+        <v>1775.496</v>
       </c>
       <c r="G30">
         <v>880</v>
@@ -3753,45 +3753,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M30">
-        <v>109.8848352</v>
+        <v>127.6581624</v>
       </c>
       <c r="N30">
-        <v>221.5192464326531</v>
+        <v>203.7459192326531</v>
       </c>
       <c r="O30">
-        <v>48.73423421518368</v>
+        <v>44.82410223118368</v>
       </c>
       <c r="P30">
-        <v>172.7850122174694</v>
+        <v>158.9218170014694</v>
       </c>
       <c r="Q30">
-        <v>396.5850122174695</v>
+        <v>382.7218170014694</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09961087200862792</v>
+        <v>0.1002408397116215</v>
       </c>
       <c r="T30">
-        <v>1.24274531197755</v>
+        <v>1.257294219667932</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.015921906143543</v>
+        <v>2.596027354633557</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08743477619525125</v>
+        <v>0.08744676454429037</v>
       </c>
       <c r="C31">
-        <v>3913.837761429974</v>
+        <v>3851.659689744032</v>
       </c>
       <c r="D31">
-        <v>4809.333761429974</v>
+        <v>4808.379689744032</v>
       </c>
       <c r="E31">
-        <v>-1125.704</v>
+        <v>-1064.48</v>
       </c>
       <c r="F31">
-        <v>1775.496</v>
+        <v>1836.72</v>
       </c>
       <c r="G31">
         <v>880</v>
@@ -3835,28 +3835,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M31">
-        <v>127.6581624</v>
+        <v>132.060168</v>
       </c>
       <c r="N31">
-        <v>203.7459192326531</v>
+        <v>199.3439136326531</v>
       </c>
       <c r="O31">
-        <v>44.82410223118369</v>
+        <v>43.85566099918368</v>
       </c>
       <c r="P31">
-        <v>158.9218170014694</v>
+        <v>155.4882526334694</v>
       </c>
       <c r="Q31">
-        <v>382.7218170014694</v>
+        <v>379.2882526334694</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1002408397116215</v>
+        <v>0.1008888064918434</v>
       </c>
       <c r="T31">
-        <v>1.257294219667932</v>
+        <v>1.272258810435183</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.596027354633558</v>
+        <v>2.509493109479106</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08744676454429037</v>
+        <v>0.08840177289332952</v>
       </c>
       <c r="C32">
-        <v>3851.659689744032</v>
+        <v>3715.630268171059</v>
       </c>
       <c r="D32">
-        <v>4808.379689744032</v>
+        <v>4733.574268171059</v>
       </c>
       <c r="E32">
-        <v>-1064.48</v>
+        <v>-1003.256</v>
       </c>
       <c r="F32">
-        <v>1836.72</v>
+        <v>1897.944</v>
       </c>
       <c r="G32">
         <v>880</v>
@@ -3917,45 +3917,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M32">
-        <v>132.060168</v>
+        <v>143.8641552</v>
       </c>
       <c r="N32">
-        <v>199.3439136326531</v>
+        <v>187.5399264326531</v>
       </c>
       <c r="O32">
-        <v>43.85566099918368</v>
+        <v>41.25878381518368</v>
       </c>
       <c r="P32">
-        <v>155.4882526334694</v>
+        <v>146.2811426174694</v>
       </c>
       <c r="Q32">
-        <v>379.2882526334694</v>
+        <v>370.0811426174695</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1008888064918434</v>
+        <v>0.1015555549178689</v>
       </c>
       <c r="T32">
-        <v>1.272258810435183</v>
+        <v>1.287657157456556</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.509493109479106</v>
+        <v>2.303590363923071</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08840177289332952</v>
+        <v>0.08844418124236868</v>
       </c>
       <c r="C33">
-        <v>3715.630268171059</v>
+        <v>3651.138375470006</v>
       </c>
       <c r="D33">
-        <v>4733.574268171059</v>
+        <v>4730.306375470006</v>
       </c>
       <c r="E33">
-        <v>-1003.256</v>
+        <v>-942.0319999999999</v>
       </c>
       <c r="F33">
-        <v>1897.944</v>
+        <v>1959.168</v>
       </c>
       <c r="G33">
         <v>880</v>
@@ -3999,28 +3999,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M33">
-        <v>143.8641552</v>
+        <v>148.5049344</v>
       </c>
       <c r="N33">
-        <v>187.5399264326531</v>
+        <v>182.8991472326531</v>
       </c>
       <c r="O33">
-        <v>41.25878381518368</v>
+        <v>40.23781239118369</v>
       </c>
       <c r="P33">
-        <v>146.2811426174694</v>
+        <v>142.6613348414694</v>
       </c>
       <c r="Q33">
-        <v>370.0811426174695</v>
+        <v>366.4613348414695</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1015555549178689</v>
+        <v>0.1022419135917187</v>
       </c>
       <c r="T33">
-        <v>1.287657157456556</v>
+        <v>1.303508397037382</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.303590363923071</v>
+        <v>2.231603165050475</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08844418124236868</v>
+        <v>0.08848658959140782</v>
       </c>
       <c r="C34">
-        <v>3651.138375470006</v>
+        <v>3586.650991731822</v>
       </c>
       <c r="D34">
-        <v>4730.306375470006</v>
+        <v>4727.042991731822</v>
       </c>
       <c r="E34">
-        <v>-942.0319999999999</v>
+        <v>-880.8079999999998</v>
       </c>
       <c r="F34">
-        <v>1959.168</v>
+        <v>2020.392</v>
       </c>
       <c r="G34">
         <v>880</v>
@@ -4081,28 +4081,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M34">
-        <v>148.5049344</v>
+        <v>153.1457136</v>
       </c>
       <c r="N34">
-        <v>182.8991472326531</v>
+        <v>178.2583680326531</v>
       </c>
       <c r="O34">
-        <v>40.23781239118369</v>
+        <v>39.21684096718368</v>
       </c>
       <c r="P34">
-        <v>142.6613348414694</v>
+        <v>139.0415270654694</v>
       </c>
       <c r="Q34">
-        <v>366.4613348414695</v>
+        <v>362.8415270654694</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1022419135917187</v>
+        <v>0.1029487605841908</v>
       </c>
       <c r="T34">
-        <v>1.303508397037382</v>
+        <v>1.319832807948979</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.231603165050475</v>
+        <v>2.163978826715612</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08848658959140782</v>
+        <v>0.08852899794044697</v>
       </c>
       <c r="C35">
-        <v>3586.650991731822</v>
+        <v>3522.168107630893</v>
       </c>
       <c r="D35">
-        <v>4727.042991731822</v>
+        <v>4723.784107630893</v>
       </c>
       <c r="E35">
-        <v>-880.8079999999998</v>
+        <v>-819.5839999999998</v>
       </c>
       <c r="F35">
-        <v>2020.392</v>
+        <v>2081.616</v>
       </c>
       <c r="G35">
         <v>880</v>
@@ -4163,28 +4163,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M35">
-        <v>153.1457136</v>
+        <v>157.7864928</v>
       </c>
       <c r="N35">
-        <v>178.2583680326531</v>
+        <v>173.6175888326531</v>
       </c>
       <c r="O35">
-        <v>39.21684096718368</v>
+        <v>38.19586954318368</v>
       </c>
       <c r="P35">
-        <v>139.0415270654694</v>
+        <v>135.4217192894694</v>
       </c>
       <c r="Q35">
-        <v>362.8415270654694</v>
+        <v>359.2217192894694</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1029487605841908</v>
+        <v>0.1036770271824954</v>
       </c>
       <c r="T35">
-        <v>1.319832807948979</v>
+        <v>1.336651897979109</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.163978826715612</v>
+        <v>2.100332390635741</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08852899794044697</v>
+        <v>0.08857140628948611</v>
       </c>
       <c r="C36">
-        <v>3522.168107630893</v>
+        <v>3457.68971386731</v>
       </c>
       <c r="D36">
-        <v>4723.784107630893</v>
+        <v>4720.52971386731</v>
       </c>
       <c r="E36">
-        <v>-819.5839999999998</v>
+        <v>-758.3599999999997</v>
       </c>
       <c r="F36">
-        <v>2081.616</v>
+        <v>2142.84</v>
       </c>
       <c r="G36">
         <v>880</v>
@@ -4245,28 +4245,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M36">
-        <v>157.7864928</v>
+        <v>162.427272</v>
       </c>
       <c r="N36">
-        <v>173.6175888326531</v>
+        <v>168.9768096326531</v>
       </c>
       <c r="O36">
-        <v>38.19586954318368</v>
+        <v>37.17489811918368</v>
       </c>
       <c r="P36">
-        <v>135.4217192894694</v>
+        <v>131.8019115134694</v>
       </c>
       <c r="Q36">
-        <v>359.2217192894694</v>
+        <v>355.6019115134694</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1036770271824954</v>
+        <v>0.1044277019838248</v>
       </c>
       <c r="T36">
-        <v>1.336651897979109</v>
+        <v>1.353988498471704</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.100332390635741</v>
+        <v>2.040322893760434</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08857140628948611</v>
+        <v>0.09260117463852525</v>
       </c>
       <c r="C37">
-        <v>3457.68971386731</v>
+        <v>3106.424077744265</v>
       </c>
       <c r="D37">
-        <v>4720.52971386731</v>
+        <v>4430.488077744265</v>
       </c>
       <c r="E37">
-        <v>-758.3599999999997</v>
+        <v>-697.1359999999995</v>
       </c>
       <c r="F37">
-        <v>2142.84</v>
+        <v>2204.064</v>
       </c>
       <c r="G37">
         <v>880</v>
@@ -4327,45 +4327,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M37">
-        <v>162.427272</v>
+        <v>198.3657600000001</v>
       </c>
       <c r="N37">
-        <v>168.9768096326531</v>
+        <v>133.0383216326531</v>
       </c>
       <c r="O37">
-        <v>37.17489811918368</v>
+        <v>29.26843075918368</v>
       </c>
       <c r="P37">
-        <v>131.8019115134694</v>
+        <v>103.7698908734694</v>
       </c>
       <c r="Q37">
-        <v>355.6019115134694</v>
+        <v>327.5698908734694</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1044277019838248</v>
+        <v>0.1052018353726957</v>
       </c>
       <c r="T37">
-        <v>1.353988498471704</v>
+        <v>1.371866867729693</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.05912400000000001</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.040322893760434</v>
+        <v>1.670671801588404</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09260117463852525</v>
+        <v>0.09275434298756441</v>
       </c>
       <c r="C38">
-        <v>3106.424077744265</v>
+        <v>3034.877288274719</v>
       </c>
       <c r="D38">
-        <v>4430.488077744265</v>
+        <v>4420.165288274719</v>
       </c>
       <c r="E38">
-        <v>-697.136</v>
+        <v>-635.9119999999998</v>
       </c>
       <c r="F38">
-        <v>2204.064</v>
+        <v>2265.288</v>
       </c>
       <c r="G38">
         <v>880</v>
@@ -4409,28 +4409,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M38">
-        <v>198.36576</v>
+        <v>203.87592</v>
       </c>
       <c r="N38">
-        <v>133.0383216326531</v>
+        <v>127.5281616326531</v>
       </c>
       <c r="O38">
-        <v>29.26843075918368</v>
+        <v>28.05619555918368</v>
       </c>
       <c r="P38">
-        <v>103.7698908734694</v>
+        <v>99.4719660734694</v>
       </c>
       <c r="Q38">
-        <v>327.5698908734694</v>
+        <v>323.2719660734694</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1052018353726957</v>
+        <v>0.1060005444247054</v>
       </c>
       <c r="T38">
-        <v>1.371866867729693</v>
+        <v>1.390312804265714</v>
       </c>
       <c r="U38">
         <v>0.09000000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.670671801588405</v>
+        <v>1.625518509653583</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09275434298756441</v>
+        <v>0.09290751133660355</v>
       </c>
       <c r="C39">
-        <v>3034.877288274719</v>
+        <v>2963.378490032731</v>
       </c>
       <c r="D39">
-        <v>4420.165288274719</v>
+        <v>4409.890490032731</v>
       </c>
       <c r="E39">
-        <v>-635.9119999999998</v>
+        <v>-574.6880000000001</v>
       </c>
       <c r="F39">
-        <v>2265.288</v>
+        <v>2326.512</v>
       </c>
       <c r="G39">
         <v>880</v>
@@ -4491,28 +4491,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M39">
-        <v>203.87592</v>
+        <v>209.38608</v>
       </c>
       <c r="N39">
-        <v>127.5281616326531</v>
+        <v>122.0180016326531</v>
       </c>
       <c r="O39">
-        <v>28.05619555918368</v>
+        <v>26.84396035918369</v>
       </c>
       <c r="P39">
-        <v>99.4719660734694</v>
+        <v>95.17404127346944</v>
       </c>
       <c r="Q39">
-        <v>323.2719660734694</v>
+        <v>318.9740412734694</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1060005444247054</v>
+        <v>0.1068250182848444</v>
       </c>
       <c r="T39">
-        <v>1.390312804265714</v>
+        <v>1.409353771012573</v>
       </c>
       <c r="U39">
         <v>0.09000000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.625518509653583</v>
+        <v>1.582741706767962</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09290751133660355</v>
+        <v>0.09306067968564269</v>
       </c>
       <c r="C40">
-        <v>2963.378490032731</v>
+        <v>2891.927349123583</v>
       </c>
       <c r="D40">
-        <v>4409.890490032731</v>
+        <v>4399.663349123583</v>
       </c>
       <c r="E40">
-        <v>-574.6880000000001</v>
+        <v>-513.4639999999999</v>
       </c>
       <c r="F40">
-        <v>2326.512</v>
+        <v>2387.736</v>
       </c>
       <c r="G40">
         <v>880</v>
@@ -4573,28 +4573,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M40">
-        <v>209.38608</v>
+        <v>214.89624</v>
       </c>
       <c r="N40">
-        <v>122.0180016326531</v>
+        <v>116.5078416326531</v>
       </c>
       <c r="O40">
-        <v>26.84396035918369</v>
+        <v>25.63172515918368</v>
       </c>
       <c r="P40">
-        <v>95.17404127346944</v>
+        <v>90.87611647346942</v>
       </c>
       <c r="Q40">
-        <v>318.9740412734694</v>
+        <v>314.6761164734694</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1068250182848444</v>
+        <v>0.1076765240748241</v>
       </c>
       <c r="T40">
-        <v>1.409353771012573</v>
+        <v>1.429019031751134</v>
       </c>
       <c r="U40">
         <v>0.09000000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.582741706767962</v>
+        <v>1.542158586081604</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09306067968564269</v>
+        <v>0.09321384803468184</v>
       </c>
       <c r="C41">
-        <v>2891.927349123583</v>
+        <v>2820.523534742778</v>
       </c>
       <c r="D41">
-        <v>4399.663349123583</v>
+        <v>4389.483534742778</v>
       </c>
       <c r="E41">
-        <v>-513.4639999999999</v>
+        <v>-452.2399999999998</v>
       </c>
       <c r="F41">
-        <v>2387.736</v>
+        <v>2448.96</v>
       </c>
       <c r="G41">
         <v>880</v>
@@ -4655,28 +4655,28 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M41">
-        <v>214.89624</v>
+        <v>220.4064</v>
       </c>
       <c r="N41">
-        <v>116.5078416326531</v>
+        <v>110.9976816326531</v>
       </c>
       <c r="O41">
-        <v>25.63172515918368</v>
+        <v>24.41948995918368</v>
       </c>
       <c r="P41">
-        <v>90.87611647346942</v>
+        <v>86.57819167346942</v>
       </c>
       <c r="Q41">
-        <v>314.6761164734694</v>
+        <v>310.3781916734694</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1076765240748241</v>
+        <v>0.1085564133911364</v>
       </c>
       <c r="T41">
-        <v>1.429019031751134</v>
+        <v>1.449339801180979</v>
       </c>
       <c r="U41">
         <v>0.09000000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.542158586081604</v>
+        <v>1.503604621429564</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09321384803468184</v>
+        <v>0.113239317483897</v>
       </c>
       <c r="C42">
-        <v>2820.523534742778</v>
+        <v>1739.845246610926</v>
       </c>
       <c r="D42">
-        <v>4389.483534742778</v>
+        <v>3370.029246610926</v>
       </c>
       <c r="E42">
-        <v>-452.2399999999998</v>
+        <v>-391.0159999999996</v>
       </c>
       <c r="F42">
-        <v>2448.96</v>
+        <v>2510.184</v>
       </c>
       <c r="G42">
         <v>880</v>
@@ -4737,45 +4737,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M42">
-        <v>220.4064</v>
+        <v>368.4950112000001</v>
       </c>
       <c r="N42">
-        <v>110.9976816326531</v>
+        <v>-37.09092956734696</v>
       </c>
       <c r="O42">
-        <v>24.41948995918368</v>
+        <v>-8.160004504816332</v>
       </c>
       <c r="P42">
-        <v>86.57819167346942</v>
+        <v>-28.93092506253063</v>
       </c>
       <c r="Q42">
-        <v>310.3781916734694</v>
+        <v>194.8690749374694</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1085564133911364</v>
+        <v>0.1101014679417273</v>
       </c>
       <c r="T42">
-        <v>1.449339801180979</v>
+        <v>1.485022354312409</v>
       </c>
       <c r="U42">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.22</v>
+        <v>0.197855861662161</v>
       </c>
       <c r="W42">
-        <v>0.07020000000000001</v>
+        <v>0.1177547595079948</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.503604621429564</v>
+        <v>0.8993448257370955</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.113239317483897</v>
+        <v>0.114249317483897</v>
       </c>
       <c r="C43">
-        <v>1739.845246610926</v>
+        <v>1639.602882944711</v>
       </c>
       <c r="D43">
-        <v>3370.029246610926</v>
+        <v>3331.010882944711</v>
       </c>
       <c r="E43">
-        <v>-391.0159999999996</v>
+        <v>-329.7919999999999</v>
       </c>
       <c r="F43">
-        <v>2510.184</v>
+        <v>2571.408</v>
       </c>
       <c r="G43">
         <v>880</v>
@@ -4819,37 +4819,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M43">
-        <v>368.4950112000001</v>
+        <v>377.4826944</v>
       </c>
       <c r="N43">
-        <v>-37.09092956734696</v>
+        <v>-46.0786127673469</v>
       </c>
       <c r="O43">
-        <v>-8.160004504816332</v>
+        <v>-10.13729480881632</v>
       </c>
       <c r="P43">
-        <v>-28.93092506253063</v>
+        <v>-35.94131795853058</v>
       </c>
       <c r="Q43">
-        <v>194.8690749374694</v>
+        <v>187.8586820414694</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1101014679417273</v>
+        <v>0.1112101139407226</v>
       </c>
       <c r="T43">
-        <v>1.485022354312409</v>
+        <v>1.510626188007451</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.197855861662161</v>
+        <v>0.193145007813062</v>
       </c>
       <c r="W43">
-        <v>0.1177547595079948</v>
+        <v>0.1184463128530425</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8993448257370955</v>
+        <v>0.8779318536957362</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.114249317483897</v>
+        <v>0.115259317483897</v>
       </c>
       <c r="C44">
-        <v>1639.602882944711</v>
+        <v>1540.253691141862</v>
       </c>
       <c r="D44">
-        <v>3331.01088294471</v>
+        <v>3292.885691141862</v>
       </c>
       <c r="E44">
-        <v>-329.7919999999999</v>
+        <v>-268.5680000000002</v>
       </c>
       <c r="F44">
-        <v>2571.408</v>
+        <v>2632.632</v>
       </c>
       <c r="G44">
         <v>880</v>
@@ -4901,37 +4901,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M44">
-        <v>377.4826944</v>
+        <v>386.4703776</v>
       </c>
       <c r="N44">
-        <v>-46.0786127673469</v>
+        <v>-55.06629596734689</v>
       </c>
       <c r="O44">
-        <v>-10.13729480881632</v>
+        <v>-12.11458511281632</v>
       </c>
       <c r="P44">
-        <v>-35.94131795853058</v>
+        <v>-42.95171085453057</v>
       </c>
       <c r="Q44">
-        <v>187.8586820414694</v>
+        <v>180.8482891454694</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1112101139407226</v>
+        <v>0.1123576597993318</v>
       </c>
       <c r="T44">
-        <v>1.510626188007451</v>
+        <v>1.537128401832143</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.193145007813062</v>
+        <v>0.1886532634453164</v>
       </c>
       <c r="W44">
-        <v>0.1184463128530425</v>
+        <v>0.1191057009262276</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8779318536957362</v>
+        <v>0.8575148338423471</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.115259317483897</v>
+        <v>0.116269317483897</v>
       </c>
       <c r="C45">
-        <v>1540.253691141862</v>
+        <v>1441.767349765802</v>
       </c>
       <c r="D45">
-        <v>3292.885691141862</v>
+        <v>3255.623349765801</v>
       </c>
       <c r="E45">
-        <v>-268.5680000000002</v>
+        <v>-207.3440000000001</v>
       </c>
       <c r="F45">
-        <v>2632.632</v>
+        <v>2693.856</v>
       </c>
       <c r="G45">
         <v>880</v>
@@ -4983,37 +4983,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M45">
-        <v>386.4703776</v>
+        <v>395.4580608</v>
       </c>
       <c r="N45">
-        <v>-55.06629596734689</v>
+        <v>-64.05397916734688</v>
       </c>
       <c r="O45">
-        <v>-12.11458511281632</v>
+        <v>-14.09187541681631</v>
       </c>
       <c r="P45">
-        <v>-42.95171085453057</v>
+        <v>-49.96210375053057</v>
       </c>
       <c r="Q45">
-        <v>180.8482891454694</v>
+        <v>173.8378962494695</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1123576597993318</v>
+        <v>0.1135461894386056</v>
       </c>
       <c r="T45">
-        <v>1.537128401832143</v>
+        <v>1.564577123293431</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1886532634453164</v>
+        <v>0.1843656892761046</v>
       </c>
       <c r="W45">
-        <v>0.1191057009262276</v>
+        <v>0.1197351168142679</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8575148338423471</v>
+        <v>0.8380258603459301</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.116269317483897</v>
+        <v>0.117279317483897</v>
       </c>
       <c r="C46">
-        <v>1441.767349765802</v>
+        <v>1344.114894494064</v>
       </c>
       <c r="D46">
-        <v>3255.623349765801</v>
+        <v>3219.194894494064</v>
       </c>
       <c r="E46">
-        <v>-207.3440000000001</v>
+        <v>-146.1199999999999</v>
       </c>
       <c r="F46">
-        <v>2693.856</v>
+        <v>2755.08</v>
       </c>
       <c r="G46">
         <v>880</v>
@@ -5065,37 +5065,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M46">
-        <v>395.4580608</v>
+        <v>404.445744</v>
       </c>
       <c r="N46">
-        <v>-64.05397916734688</v>
+        <v>-73.04166236734693</v>
       </c>
       <c r="O46">
-        <v>-14.09187541681631</v>
+        <v>-16.06916572081633</v>
       </c>
       <c r="P46">
-        <v>-49.96210375053057</v>
+        <v>-56.9724966465306</v>
       </c>
       <c r="Q46">
-        <v>173.8378962494695</v>
+        <v>166.8275033534694</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1135461894386056</v>
+        <v>0.1147779383374893</v>
       </c>
       <c r="T46">
-        <v>1.564577123293431</v>
+        <v>1.593023980080585</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1843656892761046</v>
+        <v>0.1802686739588578</v>
       </c>
       <c r="W46">
-        <v>0.1197351168142679</v>
+        <v>0.1203365586628397</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8380258603459301</v>
+        <v>0.8194030634493538</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.117279317483897</v>
+        <v>0.118289317483897</v>
       </c>
       <c r="C47">
-        <v>1344.114894494064</v>
+        <v>1247.268643032033</v>
       </c>
       <c r="D47">
-        <v>3219.194894494064</v>
+        <v>3183.572643032033</v>
       </c>
       <c r="E47">
-        <v>-146.1199999999999</v>
+        <v>-84.89599999999973</v>
       </c>
       <c r="F47">
-        <v>2755.08</v>
+        <v>2816.304</v>
       </c>
       <c r="G47">
         <v>880</v>
@@ -5147,37 +5147,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M47">
-        <v>404.445744</v>
+        <v>413.4334272</v>
       </c>
       <c r="N47">
-        <v>-73.04166236734693</v>
+        <v>-82.02934556734692</v>
       </c>
       <c r="O47">
-        <v>-16.06916572081633</v>
+        <v>-18.04645602481632</v>
       </c>
       <c r="P47">
-        <v>-56.9724966465306</v>
+        <v>-63.9828895425306</v>
       </c>
       <c r="Q47">
-        <v>166.8275033534694</v>
+        <v>159.8171104574694</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1147779383374893</v>
+        <v>0.1160553075659613</v>
       </c>
       <c r="T47">
-        <v>1.593023980080585</v>
+        <v>1.622524424156151</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1802686739588578</v>
+        <v>0.1763497897423609</v>
       </c>
       <c r="W47">
-        <v>0.1203365586628397</v>
+        <v>0.1209118508658214</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8194030634493538</v>
+        <v>0.8015899533743678</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.118289317483897</v>
+        <v>0.1455800116638015</v>
       </c>
       <c r="C48">
-        <v>1247.268643032033</v>
+        <v>453.2642998099022</v>
       </c>
       <c r="D48">
-        <v>3183.572643032033</v>
+        <v>2450.792299809902</v>
       </c>
       <c r="E48">
-        <v>-84.89599999999973</v>
+        <v>-23.67200000000003</v>
       </c>
       <c r="F48">
-        <v>2816.304</v>
+        <v>2877.528</v>
       </c>
       <c r="G48">
         <v>880</v>
@@ -5229,45 +5229,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M48">
-        <v>413.4334272</v>
+        <v>577.8076224</v>
       </c>
       <c r="N48">
-        <v>-82.02934556734692</v>
+        <v>-246.4035407673469</v>
       </c>
       <c r="O48">
-        <v>-18.04645602481632</v>
+        <v>-54.20877896881632</v>
       </c>
       <c r="P48">
-        <v>-63.9828895425306</v>
+        <v>-192.1947617985306</v>
       </c>
       <c r="Q48">
-        <v>159.8171104574694</v>
+        <v>31.60523820146943</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1160553075659613</v>
+        <v>0.1190803023877805</v>
       </c>
       <c r="T48">
-        <v>1.622524424156151</v>
+        <v>1.692385736438349</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1763497897423609</v>
+        <v>0.1261819594147045</v>
       </c>
       <c r="W48">
-        <v>0.1209118508658214</v>
+        <v>0.1754626625495274</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8015899533743678</v>
+        <v>0.5735543609759294</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1455800116638015</v>
+        <v>0.1471300116638015</v>
       </c>
       <c r="C49">
-        <v>453.2642998099022</v>
+        <v>360.4144709191419</v>
       </c>
       <c r="D49">
-        <v>2450.792299809902</v>
+        <v>2419.166470919142</v>
       </c>
       <c r="E49">
-        <v>-23.67200000000003</v>
+        <v>37.55200000000013</v>
       </c>
       <c r="F49">
-        <v>2877.528</v>
+        <v>2938.752</v>
       </c>
       <c r="G49">
         <v>880</v>
@@ -5311,37 +5311,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M49">
-        <v>577.8076224</v>
+        <v>590.1014016</v>
       </c>
       <c r="N49">
-        <v>-246.4035407673469</v>
+        <v>-258.6973199673469</v>
       </c>
       <c r="O49">
-        <v>-54.20877896881632</v>
+        <v>-56.91341039281632</v>
       </c>
       <c r="P49">
-        <v>-192.1947617985306</v>
+        <v>-201.7839095745306</v>
       </c>
       <c r="Q49">
-        <v>31.60523820146943</v>
+        <v>22.01609042546943</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1190803023877805</v>
+        <v>0.1204895389721609</v>
       </c>
       <c r="T49">
-        <v>1.692385736438349</v>
+        <v>1.72493161598524</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1261819594147045</v>
+        <v>0.1235531685935648</v>
       </c>
       <c r="W49">
-        <v>0.1754626625495274</v>
+        <v>0.1759905237464122</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5735543609759294</v>
+        <v>0.5616053117889308</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1471300116638015</v>
+        <v>0.1486800116638015</v>
       </c>
       <c r="C50">
-        <v>360.4144709191428</v>
+        <v>268.3704636113503</v>
       </c>
       <c r="D50">
-        <v>2419.166470919142</v>
+        <v>2388.34646361135</v>
       </c>
       <c r="E50">
-        <v>37.55199999999968</v>
+        <v>98.77599999999984</v>
       </c>
       <c r="F50">
-        <v>2938.751999999999</v>
+        <v>2999.976</v>
       </c>
       <c r="G50">
         <v>880</v>
@@ -5393,37 +5393,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M50">
-        <v>590.1014015999999</v>
+        <v>602.3951807999999</v>
       </c>
       <c r="N50">
-        <v>-258.6973199673468</v>
+        <v>-270.9910991673468</v>
       </c>
       <c r="O50">
-        <v>-56.9134103928163</v>
+        <v>-59.6180418168163</v>
       </c>
       <c r="P50">
-        <v>-201.7839095745305</v>
+        <v>-211.3730573505305</v>
       </c>
       <c r="Q50">
-        <v>22.01609042546951</v>
+        <v>12.42694264946948</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1204895389721609</v>
+        <v>0.1219540397363209</v>
       </c>
       <c r="T50">
-        <v>1.72493161598524</v>
+        <v>1.75875380453397</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1235531685935648</v>
+        <v>0.1210316753569615</v>
       </c>
       <c r="W50">
-        <v>0.1759905237464122</v>
+        <v>0.1764968395883221</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.561605311788931</v>
+        <v>0.5501439788952793</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1486800116638015</v>
+        <v>0.1502300116638015</v>
       </c>
       <c r="C51">
-        <v>268.3704636113503</v>
+        <v>177.1018669916516</v>
       </c>
       <c r="D51">
-        <v>2388.34646361135</v>
+        <v>2358.301866991651</v>
       </c>
       <c r="E51">
-        <v>98.77599999999984</v>
+        <v>160</v>
       </c>
       <c r="F51">
-        <v>2999.976</v>
+        <v>3061.2</v>
       </c>
       <c r="G51">
         <v>880</v>
@@ -5475,37 +5475,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M51">
-        <v>602.3951807999999</v>
+        <v>614.68896</v>
       </c>
       <c r="N51">
-        <v>-270.9910991673468</v>
+        <v>-283.2848783673468</v>
       </c>
       <c r="O51">
-        <v>-59.6180418168163</v>
+        <v>-62.32267324081631</v>
       </c>
       <c r="P51">
-        <v>-211.3730573505305</v>
+        <v>-220.9622051265305</v>
       </c>
       <c r="Q51">
-        <v>12.42694264946948</v>
+        <v>2.837794873469477</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1219540397363209</v>
+        <v>0.1234771205310473</v>
       </c>
       <c r="T51">
-        <v>1.75875380453397</v>
+        <v>1.79392888062465</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1210316753569615</v>
+        <v>0.1186110418498222</v>
       </c>
       <c r="W51">
-        <v>0.1764968395883221</v>
+        <v>0.1769829027965557</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5501439788952793</v>
+        <v>0.5391410993173738</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1502300116638015</v>
+        <v>0.1517800116638015</v>
       </c>
       <c r="C52">
-        <v>177.1018669916516</v>
+        <v>86.57978138986437</v>
       </c>
       <c r="D52">
-        <v>2358.301866991651</v>
+        <v>2329.003781389864</v>
       </c>
       <c r="E52">
-        <v>160</v>
+        <v>221.2240000000002</v>
       </c>
       <c r="F52">
-        <v>3061.2</v>
+        <v>3122.424</v>
       </c>
       <c r="G52">
         <v>880</v>
@@ -5557,37 +5557,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M52">
-        <v>614.68896</v>
+        <v>626.9827392</v>
       </c>
       <c r="N52">
-        <v>-283.2848783673468</v>
+        <v>-295.5786575673469</v>
       </c>
       <c r="O52">
-        <v>-62.32267324081631</v>
+        <v>-65.02730466481631</v>
       </c>
       <c r="P52">
-        <v>-220.9622051265305</v>
+        <v>-230.5513529025305</v>
       </c>
       <c r="Q52">
-        <v>2.837794873469477</v>
+        <v>-6.751352902530527</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1234771205310473</v>
+        <v>0.1250623678888238</v>
       </c>
       <c r="T52">
-        <v>1.79392888062465</v>
+        <v>1.830539674106786</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1186110418498222</v>
+        <v>0.1162853351468845</v>
       </c>
       <c r="W52">
-        <v>0.1769829027965557</v>
+        <v>0.1774499047025056</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5391410993173738</v>
+        <v>0.5285697052131114</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1517800116638015</v>
+        <v>0.1533300116638015</v>
       </c>
       <c r="C53">
-        <v>86.57978138986437</v>
+        <v>-3.223274360211235</v>
       </c>
       <c r="D53">
-        <v>2329.003781389864</v>
+        <v>2300.424725639789</v>
       </c>
       <c r="E53">
-        <v>221.2240000000002</v>
+        <v>282.4480000000003</v>
       </c>
       <c r="F53">
-        <v>3122.424</v>
+        <v>3183.648</v>
       </c>
       <c r="G53">
         <v>880</v>
@@ -5639,37 +5639,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M53">
-        <v>626.9827392</v>
+        <v>639.2765184000001</v>
       </c>
       <c r="N53">
-        <v>-295.5786575673469</v>
+        <v>-307.872436767347</v>
       </c>
       <c r="O53">
-        <v>-65.02730466481631</v>
+        <v>-67.73193608881634</v>
       </c>
       <c r="P53">
-        <v>-230.5513529025305</v>
+        <v>-240.1405006785307</v>
       </c>
       <c r="Q53">
-        <v>-6.751352902530527</v>
+        <v>-16.34050067853065</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1250623678888238</v>
+        <v>0.126713667219841</v>
       </c>
       <c r="T53">
-        <v>1.830539674106786</v>
+        <v>1.868675917317344</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1162853351468845</v>
+        <v>0.1140490787017521</v>
       </c>
       <c r="W53">
-        <v>0.1774499047025056</v>
+        <v>0.1778989449966882</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5285697052131114</v>
+        <v>0.5184049031897823</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1533300116638015</v>
+        <v>0.1548800116638015</v>
       </c>
       <c r="C54">
-        <v>-3.223274360211235</v>
+        <v>-92.33344889763111</v>
       </c>
       <c r="D54">
-        <v>2300.424725639789</v>
+        <v>2272.538551102369</v>
       </c>
       <c r="E54">
-        <v>282.4480000000003</v>
+        <v>343.672</v>
       </c>
       <c r="F54">
-        <v>3183.648</v>
+        <v>3244.872</v>
       </c>
       <c r="G54">
         <v>880</v>
@@ -5721,37 +5721,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M54">
-        <v>639.2765184000001</v>
+        <v>651.5702976</v>
       </c>
       <c r="N54">
-        <v>-307.872436767347</v>
+        <v>-320.1662159673469</v>
       </c>
       <c r="O54">
-        <v>-67.73193608881634</v>
+        <v>-70.43656751281631</v>
       </c>
       <c r="P54">
-        <v>-240.1405006785307</v>
+        <v>-249.7296484545306</v>
       </c>
       <c r="Q54">
-        <v>-16.34050067853065</v>
+        <v>-25.92964845453056</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.126713667219841</v>
+        <v>0.1284352346074972</v>
       </c>
       <c r="T54">
-        <v>1.868675917317344</v>
+        <v>1.908434979387926</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1140490787017521</v>
+        <v>0.1118972092922851</v>
       </c>
       <c r="W54">
-        <v>0.1778989449966882</v>
+        <v>0.1783310403741092</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5184049031897823</v>
+        <v>0.5086236786012959</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1548800116638015</v>
+        <v>0.1756934526445722</v>
       </c>
       <c r="C55">
-        <v>-92.33344889763111</v>
+        <v>-471.6898621722935</v>
       </c>
       <c r="D55">
-        <v>2272.538551102369</v>
+        <v>1954.406137827707</v>
       </c>
       <c r="E55">
-        <v>343.672</v>
+        <v>404.8960000000002</v>
       </c>
       <c r="F55">
-        <v>3244.872</v>
+        <v>3306.096</v>
       </c>
       <c r="G55">
         <v>880</v>
@@ -5803,45 +5803,45 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M55">
-        <v>651.5702976</v>
+        <v>779.5774368</v>
       </c>
       <c r="N55">
-        <v>-320.1662159673469</v>
+        <v>-448.1733551673469</v>
       </c>
       <c r="O55">
-        <v>-70.43656751281631</v>
+        <v>-98.59813813681632</v>
       </c>
       <c r="P55">
-        <v>-249.7296484545306</v>
+        <v>-349.5752170305306</v>
       </c>
       <c r="Q55">
-        <v>-25.92964845453056</v>
+        <v>-125.7752170305305</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1284352346074972</v>
+        <v>0.1310217418397704</v>
       </c>
       <c r="T55">
-        <v>1.908434979387926</v>
+        <v>1.968169557500471</v>
       </c>
       <c r="U55">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1118972092922851</v>
+        <v>0.09352361230265879</v>
       </c>
       <c r="W55">
-        <v>0.1783310403741092</v>
+        <v>0.213747132219033</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5086236786012959</v>
+        <v>0.425107328648449</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1756934526445722</v>
+        <v>0.1775934526445722</v>
       </c>
       <c r="C56">
-        <v>-471.6898621722935</v>
+        <v>-557.5746181628988</v>
       </c>
       <c r="D56">
-        <v>1954.406137827707</v>
+        <v>1929.745381837101</v>
       </c>
       <c r="E56">
-        <v>404.8960000000002</v>
+        <v>466.1200000000003</v>
       </c>
       <c r="F56">
-        <v>3306.096</v>
+        <v>3367.32</v>
       </c>
       <c r="G56">
         <v>880</v>
@@ -5885,37 +5885,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M56">
-        <v>779.5774368</v>
+        <v>794.0140560000001</v>
       </c>
       <c r="N56">
-        <v>-448.1733551673469</v>
+        <v>-462.609974367347</v>
       </c>
       <c r="O56">
-        <v>-98.59813813681632</v>
+        <v>-101.7741943608163</v>
       </c>
       <c r="P56">
-        <v>-349.5752170305306</v>
+        <v>-360.8357800065306</v>
       </c>
       <c r="Q56">
-        <v>-125.7752170305305</v>
+        <v>-137.0357800065306</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1310217418397704</v>
+        <v>0.1329155583250986</v>
       </c>
       <c r="T56">
-        <v>1.968169557500471</v>
+        <v>2.011906658778259</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09352361230265879</v>
+        <v>0.09182318298806499</v>
       </c>
       <c r="W56">
-        <v>0.213747132219033</v>
+        <v>0.2141480934514143</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.425107328648449</v>
+        <v>0.4173781044912045</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1775934526445722</v>
+        <v>0.1794934526445722</v>
       </c>
       <c r="C57">
-        <v>-557.5746181628988</v>
+        <v>-642.8447886759463</v>
       </c>
       <c r="D57">
-        <v>1929.745381837101</v>
+        <v>1905.699211324054</v>
       </c>
       <c r="E57">
-        <v>466.1200000000003</v>
+        <v>527.3440000000005</v>
       </c>
       <c r="F57">
-        <v>3367.32</v>
+        <v>3428.544</v>
       </c>
       <c r="G57">
         <v>880</v>
@@ -5967,37 +5967,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M57">
-        <v>794.0140560000001</v>
+        <v>808.4506752000001</v>
       </c>
       <c r="N57">
-        <v>-462.609974367347</v>
+        <v>-477.046593567347</v>
       </c>
       <c r="O57">
-        <v>-101.7741943608163</v>
+        <v>-104.9502505848163</v>
       </c>
       <c r="P57">
-        <v>-360.8357800065306</v>
+        <v>-372.0963429825306</v>
       </c>
       <c r="Q57">
-        <v>-137.0357800065306</v>
+        <v>-148.2963429825306</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1329155583250986</v>
+        <v>0.1348954573779418</v>
       </c>
       <c r="T57">
-        <v>2.011906658778259</v>
+        <v>2.057631810114129</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09182318298806499</v>
+        <v>0.09018348329184954</v>
       </c>
       <c r="W57">
-        <v>0.2141480934514143</v>
+        <v>0.2145347346397819</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4173781044912045</v>
+        <v>0.4099249240538615</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1794934526445722</v>
+        <v>0.1813934526445722</v>
       </c>
       <c r="C58">
-        <v>-642.8447886759463</v>
+        <v>-727.5230656314166</v>
       </c>
       <c r="D58">
-        <v>1905.699211324054</v>
+        <v>1882.244934368583</v>
       </c>
       <c r="E58">
-        <v>527.3440000000005</v>
+        <v>588.5680000000002</v>
       </c>
       <c r="F58">
-        <v>3428.544</v>
+        <v>3489.768</v>
       </c>
       <c r="G58">
         <v>880</v>
@@ -6049,37 +6049,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M58">
-        <v>808.4506752000001</v>
+        <v>822.8872944000001</v>
       </c>
       <c r="N58">
-        <v>-477.046593567347</v>
+        <v>-491.483212767347</v>
       </c>
       <c r="O58">
-        <v>-104.9502505848163</v>
+        <v>-108.1263068088163</v>
       </c>
       <c r="P58">
-        <v>-372.0963429825306</v>
+        <v>-383.3569059585307</v>
       </c>
       <c r="Q58">
-        <v>-148.2963429825306</v>
+        <v>-159.5569059585306</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1348954573779418</v>
+        <v>0.1369674447588242</v>
       </c>
       <c r="T58">
-        <v>2.057631810114129</v>
+        <v>2.105483712674923</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09018348329184954</v>
+        <v>0.08860131691830832</v>
       </c>
       <c r="W58">
-        <v>0.2145347346397819</v>
+        <v>0.2149078094706629</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4099249240538615</v>
+        <v>0.4027332587195833</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1813934526445722</v>
+        <v>0.1832934526445723</v>
       </c>
       <c r="C59">
-        <v>-727.5230656314166</v>
+        <v>-811.6310374133009</v>
       </c>
       <c r="D59">
-        <v>1882.244934368583</v>
+        <v>1859.3609625867</v>
       </c>
       <c r="E59">
-        <v>588.5680000000002</v>
+        <v>649.7920000000004</v>
       </c>
       <c r="F59">
-        <v>3489.768</v>
+        <v>3550.992</v>
       </c>
       <c r="G59">
         <v>880</v>
@@ -6131,37 +6131,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M59">
-        <v>822.8872944000001</v>
+        <v>837.3239136000001</v>
       </c>
       <c r="N59">
-        <v>-491.483212767347</v>
+        <v>-505.919831967347</v>
       </c>
       <c r="O59">
-        <v>-108.1263068088163</v>
+        <v>-111.3023630328163</v>
       </c>
       <c r="P59">
-        <v>-383.3569059585307</v>
+        <v>-394.6174689345306</v>
       </c>
       <c r="Q59">
-        <v>-159.5569059585306</v>
+        <v>-170.8174689345306</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1369674447588242</v>
+        <v>0.1391380982054628</v>
       </c>
       <c r="T59">
-        <v>2.105483712674923</v>
+        <v>2.155614277262421</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08860131691830832</v>
+        <v>0.08707370800592369</v>
       </c>
       <c r="W59">
-        <v>0.2149078094706629</v>
+        <v>0.2152680196522032</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4027332587195833</v>
+        <v>0.3957895818451077</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1832934526445722</v>
+        <v>0.1851934526445722</v>
       </c>
       <c r="C60">
-        <v>-811.6310374132991</v>
+        <v>-895.1892551467054</v>
       </c>
       <c r="D60">
-        <v>1859.360962586701</v>
+        <v>1837.026744853294</v>
       </c>
       <c r="E60">
-        <v>649.7919999999999</v>
+        <v>711.0159999999996</v>
       </c>
       <c r="F60">
-        <v>3550.992</v>
+        <v>3612.215999999999</v>
       </c>
       <c r="G60">
         <v>880</v>
@@ -6213,37 +6213,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M60">
-        <v>837.3239136</v>
+        <v>851.7605327999999</v>
       </c>
       <c r="N60">
-        <v>-505.9198319673469</v>
+        <v>-520.3564511673467</v>
       </c>
       <c r="O60">
-        <v>-111.3023630328163</v>
+        <v>-114.4784192568163</v>
       </c>
       <c r="P60">
-        <v>-394.6174689345306</v>
+        <v>-405.8780319105304</v>
       </c>
       <c r="Q60">
-        <v>-170.8174689345306</v>
+        <v>-182.0780319105304</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1391380982054628</v>
+        <v>0.1414146371860838</v>
       </c>
       <c r="T60">
-        <v>2.15561427726242</v>
+        <v>2.20819023524443</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08707370800592371</v>
+        <v>0.08559788244650128</v>
       </c>
       <c r="W60">
-        <v>0.2152680196522032</v>
+        <v>0.215616019319115</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3957895818451077</v>
+        <v>0.3890812838477332</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1851934526445722</v>
+        <v>0.1870934526445722</v>
       </c>
       <c r="C61">
-        <v>-895.1892551467054</v>
+        <v>-978.2172942550292</v>
       </c>
       <c r="D61">
-        <v>1837.026744853294</v>
+        <v>1815.22270574497</v>
       </c>
       <c r="E61">
-        <v>711.0159999999996</v>
+        <v>772.2399999999998</v>
       </c>
       <c r="F61">
-        <v>3612.215999999999</v>
+        <v>3673.44</v>
       </c>
       <c r="G61">
         <v>880</v>
@@ -6295,37 +6295,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M61">
-        <v>851.7605327999999</v>
+        <v>866.197152</v>
       </c>
       <c r="N61">
-        <v>-520.3564511673467</v>
+        <v>-534.7930703673469</v>
       </c>
       <c r="O61">
-        <v>-114.4784192568163</v>
+        <v>-117.6544754808163</v>
       </c>
       <c r="P61">
-        <v>-405.8780319105304</v>
+        <v>-417.1385948865306</v>
       </c>
       <c r="Q61">
-        <v>-182.0780319105304</v>
+        <v>-193.3385948865306</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1414146371860838</v>
+        <v>0.1438050031157359</v>
       </c>
       <c r="T61">
-        <v>2.20819023524443</v>
+        <v>2.263394991125542</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08559788244650128</v>
+        <v>0.08417125107239291</v>
       </c>
       <c r="W61">
-        <v>0.215616019319115</v>
+        <v>0.2159524189971298</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3890812838477332</v>
+        <v>0.3825965957836041</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1870934526445722</v>
+        <v>0.1889934526445722</v>
       </c>
       <c r="C62">
-        <v>-978.2172942550292</v>
+        <v>-1060.733811684737</v>
       </c>
       <c r="D62">
-        <v>1815.22270574497</v>
+        <v>1793.930188315263</v>
       </c>
       <c r="E62">
-        <v>772.2399999999998</v>
+        <v>833.4639999999999</v>
       </c>
       <c r="F62">
-        <v>3673.44</v>
+        <v>3734.664</v>
       </c>
       <c r="G62">
         <v>880</v>
@@ -6377,37 +6377,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M62">
-        <v>866.197152</v>
+        <v>880.6337712</v>
       </c>
       <c r="N62">
-        <v>-534.7930703673469</v>
+        <v>-549.2296895673469</v>
       </c>
       <c r="O62">
-        <v>-117.6544754808163</v>
+        <v>-120.8305317048163</v>
       </c>
       <c r="P62">
-        <v>-417.1385948865306</v>
+        <v>-428.3991578625306</v>
       </c>
       <c r="Q62">
-        <v>-193.3385948865306</v>
+        <v>-204.5991578625305</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1438050031157359</v>
+        <v>0.1463179519135753</v>
       </c>
       <c r="T62">
-        <v>2.263394991125542</v>
+        <v>2.321430760128761</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08417125107239291</v>
+        <v>0.08279139449743565</v>
       </c>
       <c r="W62">
-        <v>0.2159524189971298</v>
+        <v>0.2162777891775047</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3825965957836041</v>
+        <v>0.3763245204428892</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1889934526445722</v>
+        <v>0.1908934526445722</v>
       </c>
       <c r="C63">
-        <v>-1060.733811684737</v>
+        <v>-1142.756599149375</v>
       </c>
       <c r="D63">
-        <v>1793.930188315263</v>
+        <v>1773.131400850625</v>
       </c>
       <c r="E63">
-        <v>833.4639999999999</v>
+        <v>894.6880000000001</v>
       </c>
       <c r="F63">
-        <v>3734.664</v>
+        <v>3795.888</v>
       </c>
       <c r="G63">
         <v>880</v>
@@ -6459,37 +6459,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M63">
-        <v>880.6337712</v>
+        <v>895.0703904000001</v>
       </c>
       <c r="N63">
-        <v>-549.2296895673469</v>
+        <v>-563.6663087673469</v>
       </c>
       <c r="O63">
-        <v>-120.8305317048163</v>
+        <v>-124.0065879288163</v>
       </c>
       <c r="P63">
-        <v>-428.3991578625306</v>
+        <v>-439.6597208385306</v>
       </c>
       <c r="Q63">
-        <v>-204.5991578625305</v>
+        <v>-215.8597208385306</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1463179519135753</v>
+        <v>0.1489631611744589</v>
       </c>
       <c r="T63">
-        <v>2.321430760128761</v>
+        <v>2.382521043290044</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08279139449743565</v>
+        <v>0.08145604942489636</v>
       </c>
       <c r="W63">
-        <v>0.2162777891775047</v>
+        <v>0.2165926635456094</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3763245204428892</v>
+        <v>0.3702547701131653</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1908934526445722</v>
+        <v>0.1927934526445722</v>
       </c>
       <c r="C64">
-        <v>-1142.756599149375</v>
+        <v>-1224.302632712166</v>
       </c>
       <c r="D64">
-        <v>1773.131400850625</v>
+        <v>1752.809367287834</v>
       </c>
       <c r="E64">
-        <v>894.6880000000001</v>
+        <v>955.9119999999998</v>
       </c>
       <c r="F64">
-        <v>3795.888</v>
+        <v>3857.112</v>
       </c>
       <c r="G64">
         <v>880</v>
@@ -6541,37 +6541,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M64">
-        <v>895.0703904000001</v>
+        <v>909.5070095999999</v>
       </c>
       <c r="N64">
-        <v>-563.6663087673469</v>
+        <v>-578.1029279673469</v>
       </c>
       <c r="O64">
-        <v>-124.0065879288163</v>
+        <v>-127.1826441528163</v>
       </c>
       <c r="P64">
-        <v>-439.6597208385306</v>
+        <v>-450.9202838145306</v>
       </c>
       <c r="Q64">
-        <v>-215.8597208385306</v>
+        <v>-227.1202838145306</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1489631611744589</v>
+        <v>0.1517513547197145</v>
       </c>
       <c r="T64">
-        <v>2.382521043290044</v>
+        <v>2.446913503919504</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08145604942489636</v>
+        <v>0.08016309625942182</v>
       </c>
       <c r="W64">
-        <v>0.2165926635456094</v>
+        <v>0.2168975419020283</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3702547701131653</v>
+        <v>0.3643777102700991</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1927934526445722</v>
+        <v>0.1946934526445722</v>
       </c>
       <c r="C65">
-        <v>-1224.302632712166</v>
+        <v>-1305.388118997617</v>
       </c>
       <c r="D65">
-        <v>1752.809367287834</v>
+        <v>1732.947881002383</v>
       </c>
       <c r="E65">
-        <v>955.9119999999998</v>
+        <v>1017.136</v>
       </c>
       <c r="F65">
-        <v>3857.112</v>
+        <v>3918.336</v>
       </c>
       <c r="G65">
         <v>880</v>
@@ -6623,37 +6623,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M65">
-        <v>909.5070095999999</v>
+        <v>923.9436287999999</v>
       </c>
       <c r="N65">
-        <v>-578.1029279673469</v>
+        <v>-592.5395471673469</v>
       </c>
       <c r="O65">
-        <v>-127.1826441528163</v>
+        <v>-130.3587003768163</v>
       </c>
       <c r="P65">
-        <v>-450.9202838145306</v>
+        <v>-462.1808467905306</v>
       </c>
       <c r="Q65">
-        <v>-227.1202838145306</v>
+        <v>-238.3808467905306</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1517513547197145</v>
+        <v>0.1546944479063733</v>
       </c>
       <c r="T65">
-        <v>2.446913503919504</v>
+        <v>2.514883323472824</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08016309625942182</v>
+        <v>0.07891054788036836</v>
       </c>
       <c r="W65">
-        <v>0.2168975419020283</v>
+        <v>0.2171928928098092</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3643777102700991</v>
+        <v>0.3586843085471288</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1946934526445722</v>
+        <v>0.1965934526445722</v>
       </c>
       <c r="C66">
-        <v>-1305.388118997617</v>
+        <v>-1386.028538296524</v>
       </c>
       <c r="D66">
-        <v>1732.947881002383</v>
+        <v>1713.531461703476</v>
       </c>
       <c r="E66">
-        <v>1017.136</v>
+        <v>1078.36</v>
       </c>
       <c r="F66">
-        <v>3918.336</v>
+        <v>3979.56</v>
       </c>
       <c r="G66">
         <v>880</v>
@@ -6705,37 +6705,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M66">
-        <v>923.9436287999999</v>
+        <v>938.3802480000001</v>
       </c>
       <c r="N66">
-        <v>-592.5395471673469</v>
+        <v>-606.9761663673469</v>
       </c>
       <c r="O66">
-        <v>-130.3587003768163</v>
+        <v>-133.5347566008163</v>
       </c>
       <c r="P66">
-        <v>-462.1808467905306</v>
+        <v>-473.4414097665306</v>
       </c>
       <c r="Q66">
-        <v>-238.3808467905306</v>
+        <v>-249.6414097665306</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1546944479063733</v>
+        <v>0.1578057178465554</v>
       </c>
       <c r="T66">
-        <v>2.514883323472824</v>
+        <v>2.586737132714905</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07891054788036836</v>
+        <v>0.0776965394514396</v>
       </c>
       <c r="W66">
-        <v>0.2171928928098092</v>
+        <v>0.2174791559973505</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3586843085471288</v>
+        <v>0.3531660884156347</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1965934526445722</v>
+        <v>0.1984934526445722</v>
       </c>
       <c r="C67">
-        <v>-1386.028538296524</v>
+        <v>-1466.23868480532</v>
       </c>
       <c r="D67">
-        <v>1713.531461703476</v>
+        <v>1694.54531519468</v>
       </c>
       <c r="E67">
-        <v>1078.36</v>
+        <v>1139.584</v>
       </c>
       <c r="F67">
-        <v>3979.56</v>
+        <v>4040.784</v>
       </c>
       <c r="G67">
         <v>880</v>
@@ -6787,37 +6787,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M67">
-        <v>938.3802480000001</v>
+        <v>952.8168672</v>
       </c>
       <c r="N67">
-        <v>-606.9761663673469</v>
+        <v>-621.4127855673469</v>
       </c>
       <c r="O67">
-        <v>-133.5347566008163</v>
+        <v>-136.7108128248163</v>
       </c>
       <c r="P67">
-        <v>-473.4414097665306</v>
+        <v>-484.7019727425305</v>
       </c>
       <c r="Q67">
-        <v>-249.6414097665306</v>
+        <v>-260.9019727425305</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1578057178465554</v>
+        <v>0.1611000036655717</v>
       </c>
       <c r="T67">
-        <v>2.586737132714905</v>
+        <v>2.662817636618284</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0776965394514396</v>
+        <v>0.07651931915672082</v>
       </c>
       <c r="W67">
-        <v>0.2174791559973505</v>
+        <v>0.2177567445428452</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3531660884156347</v>
+        <v>0.3478150870760038</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1984934526445722</v>
+        <v>0.2003934526445722</v>
       </c>
       <c r="C68">
-        <v>-1466.23868480532</v>
+        <v>-1546.032704219597</v>
       </c>
       <c r="D68">
-        <v>1694.54531519468</v>
+        <v>1675.975295780403</v>
       </c>
       <c r="E68">
-        <v>1139.584</v>
+        <v>1200.808</v>
       </c>
       <c r="F68">
-        <v>4040.784</v>
+        <v>4102.008</v>
       </c>
       <c r="G68">
         <v>880</v>
@@ -6869,37 +6869,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M68">
-        <v>952.8168672</v>
+        <v>967.2534864</v>
       </c>
       <c r="N68">
-        <v>-621.4127855673469</v>
+        <v>-635.8494047673469</v>
       </c>
       <c r="O68">
-        <v>-136.7108128248163</v>
+        <v>-139.8868690488163</v>
       </c>
       <c r="P68">
-        <v>-484.7019727425305</v>
+        <v>-495.9625357185305</v>
       </c>
       <c r="Q68">
-        <v>-260.9019727425305</v>
+        <v>-272.1625357185305</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1611000036655717</v>
+        <v>0.164593943170589</v>
       </c>
       <c r="T68">
-        <v>2.662817636618284</v>
+        <v>2.743509080152172</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07651931915672082</v>
+        <v>0.07537723976632202</v>
       </c>
       <c r="W68">
-        <v>0.2177567445428452</v>
+        <v>0.2180260468631013</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3478150870760038</v>
+        <v>0.3426238171196455</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2003934526445722</v>
+        <v>0.2022934526445722</v>
       </c>
       <c r="C69">
-        <v>-1546.032704219597</v>
+        <v>-1625.42412888257</v>
       </c>
       <c r="D69">
-        <v>1675.975295780403</v>
+        <v>1657.80787111743</v>
       </c>
       <c r="E69">
-        <v>1200.808</v>
+        <v>1262.032</v>
       </c>
       <c r="F69">
-        <v>4102.008</v>
+        <v>4163.232</v>
       </c>
       <c r="G69">
         <v>880</v>
@@ -6951,37 +6951,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M69">
-        <v>967.2534864</v>
+        <v>981.6901056</v>
       </c>
       <c r="N69">
-        <v>-635.8494047673469</v>
+        <v>-650.2860239673469</v>
       </c>
       <c r="O69">
-        <v>-139.8868690488163</v>
+        <v>-143.0629252728163</v>
       </c>
       <c r="P69">
-        <v>-495.9625357185305</v>
+        <v>-507.2230986945306</v>
       </c>
       <c r="Q69">
-        <v>-272.1625357185305</v>
+        <v>-283.4230986945306</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.164593943170589</v>
+        <v>0.1683062538946699</v>
       </c>
       <c r="T69">
-        <v>2.743509080152172</v>
+        <v>2.829243738906927</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07537723976632202</v>
+        <v>0.07426875094622903</v>
       </c>
       <c r="W69">
-        <v>0.2180260468631013</v>
+        <v>0.2182874285268792</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3426238171196455</v>
+        <v>0.3375852315737684</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2022934526445722</v>
+        <v>0.2041934526445723</v>
       </c>
       <c r="C70">
-        <v>-1625.42412888257</v>
+        <v>-1704.42591067201</v>
       </c>
       <c r="D70">
-        <v>1657.80787111743</v>
+        <v>1640.03008932799</v>
       </c>
       <c r="E70">
-        <v>1262.032</v>
+        <v>1323.256</v>
       </c>
       <c r="F70">
-        <v>4163.232</v>
+        <v>4224.456</v>
       </c>
       <c r="G70">
         <v>880</v>
@@ -7033,37 +7033,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M70">
-        <v>981.6901056</v>
+        <v>996.1267248</v>
       </c>
       <c r="N70">
-        <v>-650.2860239673469</v>
+        <v>-664.7226431673469</v>
       </c>
       <c r="O70">
-        <v>-143.0629252728163</v>
+        <v>-146.2389814968163</v>
       </c>
       <c r="P70">
-        <v>-507.2230986945306</v>
+        <v>-518.4836616705305</v>
       </c>
       <c r="Q70">
-        <v>-283.4230986945306</v>
+        <v>-294.6836616705305</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1683062538946699</v>
+        <v>0.1722580685364335</v>
       </c>
       <c r="T70">
-        <v>2.829243738906927</v>
+        <v>2.920509665968441</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07426875094622903</v>
+        <v>0.0731923922368634</v>
       </c>
       <c r="W70">
-        <v>0.2182874285268792</v>
+        <v>0.2185412339105476</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3375852315737684</v>
+        <v>0.3326926919857428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2041934526445723</v>
+        <v>0.2060934526445722</v>
       </c>
       <c r="C71">
-        <v>-1704.42591067201</v>
+        <v>-1783.050451793621</v>
       </c>
       <c r="D71">
-        <v>1640.03008932799</v>
+        <v>1622.62954820638</v>
       </c>
       <c r="E71">
-        <v>1323.256</v>
+        <v>1384.48</v>
       </c>
       <c r="F71">
-        <v>4224.456</v>
+        <v>4285.68</v>
       </c>
       <c r="G71">
         <v>880</v>
@@ -7115,37 +7115,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M71">
-        <v>996.1267248</v>
+        <v>1010.563344</v>
       </c>
       <c r="N71">
-        <v>-664.7226431673469</v>
+        <v>-679.1592623673471</v>
       </c>
       <c r="O71">
-        <v>-146.2389814968163</v>
+        <v>-149.4150377208164</v>
       </c>
       <c r="P71">
-        <v>-518.4836616705305</v>
+        <v>-529.7442246465307</v>
       </c>
       <c r="Q71">
-        <v>-294.6836616705305</v>
+        <v>-305.9442246465307</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1722580685364335</v>
+        <v>0.176473337487648</v>
       </c>
       <c r="T71">
-        <v>2.920509665968441</v>
+        <v>3.017859988167389</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0731923922368634</v>
+        <v>0.07214678663347963</v>
       </c>
       <c r="W71">
-        <v>0.2185412339105476</v>
+        <v>0.2187877877118255</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3326926919857428</v>
+        <v>0.3279399392430892</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2060934526445722</v>
+        <v>0.2079934526445723</v>
       </c>
       <c r="C72">
-        <v>-1783.050451793621</v>
+        <v>-1861.309633634713</v>
       </c>
       <c r="D72">
-        <v>1622.62954820638</v>
+        <v>1605.594366365287</v>
       </c>
       <c r="E72">
-        <v>1384.48</v>
+        <v>1445.704000000001</v>
       </c>
       <c r="F72">
-        <v>4285.68</v>
+        <v>4346.904</v>
       </c>
       <c r="G72">
         <v>880</v>
@@ -7197,37 +7197,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M72">
-        <v>1010.563344</v>
+        <v>1024.9999632</v>
       </c>
       <c r="N72">
-        <v>-679.1592623673471</v>
+        <v>-693.5958815673471</v>
       </c>
       <c r="O72">
-        <v>-149.4150377208164</v>
+        <v>-152.5910939448164</v>
       </c>
       <c r="P72">
-        <v>-529.7442246465307</v>
+        <v>-541.0047876225308</v>
       </c>
       <c r="Q72">
-        <v>-305.9442246465307</v>
+        <v>-317.2047876225308</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.176473337487648</v>
+        <v>0.1809793146423944</v>
       </c>
       <c r="T72">
-        <v>3.017859988167389</v>
+        <v>3.121924125690403</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07214678663347963</v>
+        <v>0.07113063470906442</v>
       </c>
       <c r="W72">
-        <v>0.2187877877118255</v>
+        <v>0.2190273963356026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3279399392430892</v>
+        <v>0.3233210668593837</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2079934526445723</v>
+        <v>0.2098934526445722</v>
       </c>
       <c r="C73">
-        <v>-1861.309633634713</v>
+        <v>-1939.214843819233</v>
       </c>
       <c r="D73">
-        <v>1605.594366365287</v>
+        <v>1588.913156180767</v>
       </c>
       <c r="E73">
-        <v>1445.704</v>
+        <v>1506.928</v>
       </c>
       <c r="F73">
-        <v>4346.904</v>
+        <v>4408.128</v>
       </c>
       <c r="G73">
         <v>880</v>
@@ -7279,37 +7279,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M73">
-        <v>1024.9999632</v>
+        <v>1039.4365824</v>
       </c>
       <c r="N73">
-        <v>-693.5958815673469</v>
+        <v>-708.0325007673468</v>
       </c>
       <c r="O73">
-        <v>-152.5910939448163</v>
+        <v>-155.7671501688163</v>
       </c>
       <c r="P73">
-        <v>-541.0047876225306</v>
+        <v>-552.2653505985305</v>
       </c>
       <c r="Q73">
-        <v>-317.2047876225305</v>
+        <v>-328.4653505985305</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1809793146423944</v>
+        <v>0.1858071473081942</v>
       </c>
       <c r="T73">
-        <v>3.121924125690402</v>
+        <v>3.233421415893631</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07113063470906444</v>
+        <v>0.0701427092269941</v>
       </c>
       <c r="W73">
-        <v>0.2190273963356026</v>
+        <v>0.2192603491642748</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3233210668593838</v>
+        <v>0.3188304964863368</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2098934526445722</v>
+        <v>0.2117934526445722</v>
       </c>
       <c r="C74">
-        <v>-1939.214843819233</v>
+        <v>-2016.777001593618</v>
       </c>
       <c r="D74">
-        <v>1588.913156180767</v>
+        <v>1572.574998406382</v>
       </c>
       <c r="E74">
-        <v>1506.928</v>
+        <v>1568.152</v>
       </c>
       <c r="F74">
-        <v>4408.128</v>
+        <v>4469.352</v>
       </c>
       <c r="G74">
         <v>880</v>
@@ -7361,37 +7361,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M74">
-        <v>1039.4365824</v>
+        <v>1053.8732016</v>
       </c>
       <c r="N74">
-        <v>-708.0325007673468</v>
+        <v>-722.4691199673468</v>
       </c>
       <c r="O74">
-        <v>-155.7671501688163</v>
+        <v>-158.9432063928163</v>
       </c>
       <c r="P74">
-        <v>-552.2653505985305</v>
+        <v>-563.5259135745305</v>
       </c>
       <c r="Q74">
-        <v>-328.4653505985305</v>
+        <v>-339.7259135745305</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1858071473081942</v>
+        <v>0.1909925972084977</v>
       </c>
       <c r="T74">
-        <v>3.233421415893631</v>
+        <v>3.353177764630431</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0701427092269941</v>
+        <v>0.06918185019648733</v>
       </c>
       <c r="W74">
-        <v>0.2192603491642748</v>
+        <v>0.2194869197236683</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3188304964863368</v>
+        <v>0.3144629554385787</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2117934526445722</v>
+        <v>0.2136934526445722</v>
       </c>
       <c r="C75">
-        <v>-2016.777001593618</v>
+        <v>-2094.006581662393</v>
       </c>
       <c r="D75">
-        <v>1572.574998406382</v>
+        <v>1556.569418337607</v>
       </c>
       <c r="E75">
-        <v>1568.152</v>
+        <v>1629.376</v>
       </c>
       <c r="F75">
-        <v>4469.352</v>
+        <v>4530.576</v>
       </c>
       <c r="G75">
         <v>880</v>
@@ -7443,37 +7443,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M75">
-        <v>1053.8732016</v>
+        <v>1068.3098208</v>
       </c>
       <c r="N75">
-        <v>-722.4691199673468</v>
+        <v>-736.9057391673471</v>
       </c>
       <c r="O75">
-        <v>-158.9432063928163</v>
+        <v>-162.1192626168163</v>
       </c>
       <c r="P75">
-        <v>-563.5259135745305</v>
+        <v>-574.7864765505308</v>
       </c>
       <c r="Q75">
-        <v>-339.7259135745305</v>
+        <v>-350.9864765505308</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1909925972084977</v>
+        <v>0.196576927870363</v>
       </c>
       <c r="T75">
-        <v>3.353177764630431</v>
+        <v>3.48214614019314</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06918185019648733</v>
+        <v>0.06824696032896721</v>
       </c>
       <c r="W75">
-        <v>0.2194869197236683</v>
+        <v>0.2197073667544295</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3144629554385787</v>
+        <v>0.31021345604076</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2136934526445722</v>
+        <v>0.2155934526445722</v>
       </c>
       <c r="C76">
-        <v>-2094.006581662393</v>
+        <v>-2170.913636582857</v>
       </c>
       <c r="D76">
-        <v>1556.569418337607</v>
+        <v>1540.886363417142</v>
       </c>
       <c r="E76">
-        <v>1629.376</v>
+        <v>1690.599999999999</v>
       </c>
       <c r="F76">
-        <v>4530.576</v>
+        <v>4591.799999999999</v>
       </c>
       <c r="G76">
         <v>880</v>
@@ -7525,37 +7525,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M76">
-        <v>1068.3098208</v>
+        <v>1082.74644</v>
       </c>
       <c r="N76">
-        <v>-736.9057391673471</v>
+        <v>-751.3423583673468</v>
       </c>
       <c r="O76">
-        <v>-162.1192626168163</v>
+        <v>-165.2953188408163</v>
       </c>
       <c r="P76">
-        <v>-574.7864765505308</v>
+        <v>-586.0470395265305</v>
       </c>
       <c r="Q76">
-        <v>-350.9864765505308</v>
+        <v>-362.2470395265305</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.196576927870363</v>
+        <v>0.2026080049851775</v>
       </c>
       <c r="T76">
-        <v>3.48214614019314</v>
+        <v>3.621431985800866</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06824696032896721</v>
+        <v>0.06733700085791433</v>
       </c>
       <c r="W76">
-        <v>0.2197073667544295</v>
+        <v>0.2199219351977038</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.31021345604076</v>
+        <v>0.3060772766268833</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2155934526445722</v>
+        <v>0.2174934526445723</v>
       </c>
       <c r="C77">
-        <v>-2170.913636582857</v>
+        <v>-2247.507817819455</v>
       </c>
       <c r="D77">
-        <v>1540.886363417142</v>
+        <v>1525.516182180544</v>
       </c>
       <c r="E77">
-        <v>1690.599999999999</v>
+        <v>1751.824</v>
       </c>
       <c r="F77">
-        <v>4591.799999999999</v>
+        <v>4653.023999999999</v>
       </c>
       <c r="G77">
         <v>880</v>
@@ -7607,37 +7607,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M77">
-        <v>1082.74644</v>
+        <v>1097.1830592</v>
       </c>
       <c r="N77">
-        <v>-751.3423583673468</v>
+        <v>-765.7789775673468</v>
       </c>
       <c r="O77">
-        <v>-165.2953188408163</v>
+        <v>-168.4713750648163</v>
       </c>
       <c r="P77">
-        <v>-586.0470395265305</v>
+        <v>-597.3076025025305</v>
       </c>
       <c r="Q77">
-        <v>-362.2470395265305</v>
+        <v>-373.5076025025305</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2026080049851775</v>
+        <v>0.2091416718595599</v>
       </c>
       <c r="T77">
-        <v>3.621431985800866</v>
+        <v>3.772324985209236</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06733700085791433</v>
+        <v>0.06645098768873124</v>
       </c>
       <c r="W77">
-        <v>0.2199219351977038</v>
+        <v>0.2201308571029972</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3060772766268833</v>
+        <v>0.3020499440396874</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2174934526445723</v>
+        <v>0.2193934526445722</v>
       </c>
       <c r="C78">
-        <v>-2247.507817819455</v>
+        <v>-2323.798395550504</v>
       </c>
       <c r="D78">
-        <v>1525.516182180544</v>
+        <v>1510.449604449496</v>
       </c>
       <c r="E78">
-        <v>1751.824</v>
+        <v>1813.048</v>
       </c>
       <c r="F78">
-        <v>4653.023999999999</v>
+        <v>4714.248</v>
       </c>
       <c r="G78">
         <v>880</v>
@@ -7689,37 +7689,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M78">
-        <v>1097.1830592</v>
+        <v>1111.6196784</v>
       </c>
       <c r="N78">
-        <v>-765.7789775673468</v>
+        <v>-780.2155967673468</v>
       </c>
       <c r="O78">
-        <v>-168.4713750648163</v>
+        <v>-171.6474312888163</v>
       </c>
       <c r="P78">
-        <v>-597.3076025025305</v>
+        <v>-608.5681654785305</v>
       </c>
       <c r="Q78">
-        <v>-373.5076025025305</v>
+        <v>-384.7681654785305</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2091416718595599</v>
+        <v>0.2162434836795408</v>
       </c>
       <c r="T78">
-        <v>3.772324985209236</v>
+        <v>3.936339115000941</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06645098768873124</v>
+        <v>0.06558798784861787</v>
       </c>
       <c r="W78">
-        <v>0.2201308571029972</v>
+        <v>0.2203343524652959</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3020499440396874</v>
+        <v>0.2981272174937175</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2193934526445722</v>
+        <v>0.2212934526445722</v>
       </c>
       <c r="C79">
-        <v>-2323.798395550504</v>
+        <v>-2399.794277312686</v>
       </c>
       <c r="D79">
-        <v>1510.449604449496</v>
+        <v>1495.677722687314</v>
       </c>
       <c r="E79">
-        <v>1813.048</v>
+        <v>1874.272</v>
       </c>
       <c r="F79">
-        <v>4714.248</v>
+        <v>4775.472</v>
       </c>
       <c r="G79">
         <v>880</v>
@@ -7771,37 +7771,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M79">
-        <v>1111.6196784</v>
+        <v>1126.0562976</v>
       </c>
       <c r="N79">
-        <v>-780.2155967673468</v>
+        <v>-794.6522159673468</v>
       </c>
       <c r="O79">
-        <v>-171.6474312888163</v>
+        <v>-174.8234875128163</v>
       </c>
       <c r="P79">
-        <v>-608.5681654785305</v>
+        <v>-619.8287284545305</v>
       </c>
       <c r="Q79">
-        <v>-384.7681654785305</v>
+        <v>-396.0287284545305</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2162434836795408</v>
+        <v>0.2239909147558836</v>
       </c>
       <c r="T79">
-        <v>3.936339115000941</v>
+        <v>4.115263620228258</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06558798784861787</v>
+        <v>0.06474711620953302</v>
       </c>
       <c r="W79">
-        <v>0.2203343524652959</v>
+        <v>0.2205326299977921</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2981272174937175</v>
+        <v>0.2943050736796955</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2212934526445722</v>
+        <v>0.2231934526445722</v>
       </c>
       <c r="C80">
-        <v>-2399.794277312686</v>
+        <v>-2475.504025562105</v>
       </c>
       <c r="D80">
-        <v>1495.677722687314</v>
+        <v>1481.191974437895</v>
       </c>
       <c r="E80">
-        <v>1874.272</v>
+        <v>1935.496</v>
       </c>
       <c r="F80">
-        <v>4775.472</v>
+        <v>4836.696</v>
       </c>
       <c r="G80">
         <v>880</v>
@@ -7853,37 +7853,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M80">
-        <v>1126.0562976</v>
+        <v>1140.4929168</v>
       </c>
       <c r="N80">
-        <v>-794.6522159673468</v>
+        <v>-809.088835167347</v>
       </c>
       <c r="O80">
-        <v>-174.8234875128163</v>
+        <v>-177.9995437368163</v>
       </c>
       <c r="P80">
-        <v>-619.8287284545305</v>
+        <v>-631.0892914305307</v>
       </c>
       <c r="Q80">
-        <v>-396.0287284545305</v>
+        <v>-407.2892914305307</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2239909147558836</v>
+        <v>0.2324761964109257</v>
       </c>
       <c r="T80">
-        <v>4.115263620228258</v>
+        <v>4.311228554524842</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06474711620953302</v>
+        <v>0.06392753246004525</v>
       </c>
       <c r="W80">
-        <v>0.2205326299977921</v>
+        <v>0.2207258878459213</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2943050736796955</v>
+        <v>0.2905796930002056</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2231934526445722</v>
+        <v>0.2250934526445723</v>
       </c>
       <c r="C81">
-        <v>-2475.504025562105</v>
+        <v>-2550.935874224645</v>
       </c>
       <c r="D81">
-        <v>1481.191974437895</v>
+        <v>1466.984125775355</v>
       </c>
       <c r="E81">
-        <v>1935.496</v>
+        <v>1996.72</v>
       </c>
       <c r="F81">
-        <v>4836.696</v>
+        <v>4897.92</v>
       </c>
       <c r="G81">
         <v>880</v>
@@ -7935,37 +7935,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M81">
-        <v>1140.4929168</v>
+        <v>1154.929536</v>
       </c>
       <c r="N81">
-        <v>-809.088835167347</v>
+        <v>-823.525454367347</v>
       </c>
       <c r="O81">
-        <v>-177.9995437368163</v>
+        <v>-181.1755999608164</v>
       </c>
       <c r="P81">
-        <v>-631.0892914305307</v>
+        <v>-642.3498544065307</v>
       </c>
       <c r="Q81">
-        <v>-407.2892914305307</v>
+        <v>-418.5498544065306</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2324761964109257</v>
+        <v>0.2418100062314719</v>
       </c>
       <c r="T81">
-        <v>4.311228554524842</v>
+        <v>4.526789982251084</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06392753246004525</v>
+        <v>0.06312843830429468</v>
       </c>
       <c r="W81">
-        <v>0.2207258878459213</v>
+        <v>0.2209143142478473</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2905796930002056</v>
+        <v>0.286947446837703</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2250934526445723</v>
+        <v>0.2269934526445722</v>
       </c>
       <c r="C82">
-        <v>-2550.935874224645</v>
+        <v>-2626.097744302864</v>
       </c>
       <c r="D82">
-        <v>1466.984125775355</v>
+        <v>1453.046255697136</v>
       </c>
       <c r="E82">
-        <v>1996.72</v>
+        <v>2057.944</v>
       </c>
       <c r="F82">
-        <v>4897.92</v>
+        <v>4959.144</v>
       </c>
       <c r="G82">
         <v>880</v>
@@ -8017,37 +8017,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M82">
-        <v>1154.929536</v>
+        <v>1169.3661552</v>
       </c>
       <c r="N82">
-        <v>-823.525454367347</v>
+        <v>-837.962073567347</v>
       </c>
       <c r="O82">
-        <v>-181.1755999608164</v>
+        <v>-184.3516561848163</v>
       </c>
       <c r="P82">
-        <v>-642.3498544065307</v>
+        <v>-653.6104173825307</v>
       </c>
       <c r="Q82">
-        <v>-418.5498544065306</v>
+        <v>-429.8104173825307</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2418100062314719</v>
+        <v>0.2521263223489179</v>
       </c>
       <c r="T82">
-        <v>4.526789982251084</v>
+        <v>4.765042086580089</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06312843830429468</v>
+        <v>0.06234907486843919</v>
       </c>
       <c r="W82">
-        <v>0.2209143142478473</v>
+        <v>0.2210980881460221</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.286947446837703</v>
+        <v>0.2834048857656326</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2269934526445722</v>
+        <v>0.2288934526445722</v>
       </c>
       <c r="C83">
-        <v>-2626.097744302864</v>
+        <v>-2700.997258601561</v>
       </c>
       <c r="D83">
-        <v>1453.046255697136</v>
+        <v>1439.37074139844</v>
       </c>
       <c r="E83">
-        <v>2057.944</v>
+        <v>2119.168000000001</v>
       </c>
       <c r="F83">
-        <v>4959.144</v>
+        <v>5020.368</v>
       </c>
       <c r="G83">
         <v>880</v>
@@ -8099,37 +8099,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M83">
-        <v>1169.3661552</v>
+        <v>1183.8027744</v>
       </c>
       <c r="N83">
-        <v>-837.962073567347</v>
+        <v>-852.398692767347</v>
       </c>
       <c r="O83">
-        <v>-184.3516561848163</v>
+        <v>-187.5277124088163</v>
       </c>
       <c r="P83">
-        <v>-653.6104173825307</v>
+        <v>-664.8709803585307</v>
       </c>
       <c r="Q83">
-        <v>-429.8104173825307</v>
+        <v>-441.0709803585307</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2521263223489179</v>
+        <v>0.2635888958127466</v>
       </c>
       <c r="T83">
-        <v>4.765042086580089</v>
+        <v>5.029766646945649</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06234907486843919</v>
+        <v>0.06158872029687286</v>
       </c>
       <c r="W83">
-        <v>0.2210980881460221</v>
+        <v>0.2212773797539974</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2834048857656326</v>
+        <v>0.2799487286221493</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2288934526445722</v>
+        <v>0.2307934526445722</v>
       </c>
       <c r="C84">
-        <v>-2700.997258601561</v>
+        <v>-2775.641755629553</v>
       </c>
       <c r="D84">
-        <v>1439.37074139844</v>
+        <v>1425.950244370448</v>
       </c>
       <c r="E84">
-        <v>2119.168000000001</v>
+        <v>2180.392000000001</v>
       </c>
       <c r="F84">
-        <v>5020.368</v>
+        <v>5081.592000000001</v>
       </c>
       <c r="G84">
         <v>880</v>
@@ -8181,37 +8181,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M84">
-        <v>1183.8027744</v>
+        <v>1198.2393936</v>
       </c>
       <c r="N84">
-        <v>-852.398692767347</v>
+        <v>-866.835311967347</v>
       </c>
       <c r="O84">
-        <v>-187.5277124088163</v>
+        <v>-190.7037686328163</v>
       </c>
       <c r="P84">
-        <v>-664.8709803585307</v>
+        <v>-676.1315433345306</v>
       </c>
       <c r="Q84">
-        <v>-441.0709803585307</v>
+        <v>-452.3315433345306</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2635888958127466</v>
+        <v>0.2764000073311434</v>
       </c>
       <c r="T84">
-        <v>5.029766646945649</v>
+        <v>5.325635273236569</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06158872029687286</v>
+        <v>0.06084668752221174</v>
       </c>
       <c r="W84">
-        <v>0.2212773797539974</v>
+        <v>0.2214523510822625</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2799487286221493</v>
+        <v>0.2765758523736896</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2307934526445722</v>
+        <v>0.2326934526445723</v>
       </c>
       <c r="C85">
-        <v>-2775.641755629553</v>
+        <v>-2850.038302730928</v>
       </c>
       <c r="D85">
-        <v>1425.950244370448</v>
+        <v>1412.777697269072</v>
       </c>
       <c r="E85">
-        <v>2180.392000000001</v>
+        <v>2241.616</v>
       </c>
       <c r="F85">
-        <v>5081.592000000001</v>
+        <v>5142.816</v>
       </c>
       <c r="G85">
         <v>880</v>
@@ -8263,37 +8263,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M85">
-        <v>1198.2393936</v>
+        <v>1212.6760128</v>
       </c>
       <c r="N85">
-        <v>-866.835311967347</v>
+        <v>-881.271931167347</v>
       </c>
       <c r="O85">
-        <v>-190.7037686328163</v>
+        <v>-193.8798248568164</v>
       </c>
       <c r="P85">
-        <v>-676.1315433345306</v>
+        <v>-687.3921063105306</v>
       </c>
       <c r="Q85">
-        <v>-452.3315433345306</v>
+        <v>-463.5921063105306</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2764000073311434</v>
+        <v>0.29081250778934</v>
       </c>
       <c r="T85">
-        <v>5.325635273236569</v>
+        <v>5.658487477813857</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06084668752221174</v>
+        <v>0.06012232219456635</v>
       </c>
       <c r="W85">
-        <v>0.2214523510822625</v>
+        <v>0.2216231564265213</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2765758523736896</v>
+        <v>0.2732832827025743</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2326934526445722</v>
+        <v>0.2345934526445722</v>
       </c>
       <c r="C86">
-        <v>-2850.038302730927</v>
+        <v>-2924.193708495141</v>
       </c>
       <c r="D86">
-        <v>1412.777697269073</v>
+        <v>1399.846291504859</v>
       </c>
       <c r="E86">
-        <v>2241.616</v>
+        <v>2302.84</v>
       </c>
       <c r="F86">
-        <v>5142.816</v>
+        <v>5204.04</v>
       </c>
       <c r="G86">
         <v>880</v>
@@ -8345,37 +8345,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M86">
-        <v>1212.6760128</v>
+        <v>1227.112632</v>
       </c>
       <c r="N86">
-        <v>-881.271931167347</v>
+        <v>-895.708550367347</v>
       </c>
       <c r="O86">
-        <v>-193.8798248568164</v>
+        <v>-197.0558810808163</v>
       </c>
       <c r="P86">
-        <v>-687.3921063105306</v>
+        <v>-698.6526692865307</v>
       </c>
       <c r="Q86">
-        <v>-463.5921063105306</v>
+        <v>-474.8526692865307</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2908125077893398</v>
+        <v>0.3071466749752959</v>
       </c>
       <c r="T86">
-        <v>5.658487477813853</v>
+        <v>6.035719976334777</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06012232219456635</v>
+        <v>0.05941500075698323</v>
       </c>
       <c r="W86">
-        <v>0.2216231564265213</v>
+        <v>0.2217899428215034</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2732832827025743</v>
+        <v>0.2700681852590147</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2345934526445722</v>
+        <v>0.2364934526445722</v>
       </c>
       <c r="C87">
-        <v>-2924.193708495141</v>
+        <v>-2998.114534491737</v>
       </c>
       <c r="D87">
-        <v>1399.846291504859</v>
+        <v>1387.149465508262</v>
       </c>
       <c r="E87">
-        <v>2302.84</v>
+        <v>2364.063999999999</v>
       </c>
       <c r="F87">
-        <v>5204.04</v>
+        <v>5265.263999999999</v>
       </c>
       <c r="G87">
         <v>880</v>
@@ -8427,37 +8427,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M87">
-        <v>1227.112632</v>
+        <v>1241.5492512</v>
       </c>
       <c r="N87">
-        <v>-895.708550367347</v>
+        <v>-910.1451695673468</v>
       </c>
       <c r="O87">
-        <v>-197.0558810808163</v>
+        <v>-200.2319373048163</v>
       </c>
       <c r="P87">
-        <v>-698.6526692865307</v>
+        <v>-709.9132322625305</v>
       </c>
       <c r="Q87">
-        <v>-474.8526692865307</v>
+        <v>-486.1132322625305</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3071466749752959</v>
+        <v>0.3258142946163884</v>
       </c>
       <c r="T87">
-        <v>6.035719976334777</v>
+        <v>6.466842831787261</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05941500075698323</v>
+        <v>0.05872412865515785</v>
       </c>
       <c r="W87">
-        <v>0.2217899428215034</v>
+        <v>0.2219528504631138</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2700681852590147</v>
+        <v>0.2669278575234447</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2364934526445722</v>
+        <v>0.2383934526445722</v>
       </c>
       <c r="C88">
-        <v>-2998.114534491737</v>
+        <v>-3071.807106372208</v>
       </c>
       <c r="D88">
-        <v>1387.149465508262</v>
+        <v>1374.680893627791</v>
       </c>
       <c r="E88">
-        <v>2364.063999999999</v>
+        <v>2425.288</v>
       </c>
       <c r="F88">
-        <v>5265.263999999999</v>
+        <v>5326.487999999999</v>
       </c>
       <c r="G88">
         <v>880</v>
@@ -8509,37 +8509,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M88">
-        <v>1241.5492512</v>
+        <v>1255.9858704</v>
       </c>
       <c r="N88">
-        <v>-910.1451695673468</v>
+        <v>-924.5817887673468</v>
       </c>
       <c r="O88">
-        <v>-200.2319373048163</v>
+        <v>-203.4079935288163</v>
       </c>
       <c r="P88">
-        <v>-709.9132322625305</v>
+        <v>-721.1737952385305</v>
       </c>
       <c r="Q88">
-        <v>-486.1132322625305</v>
+        <v>-497.3737952385305</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3258142946163884</v>
+        <v>0.347353855740726</v>
       </c>
       <c r="T88">
-        <v>6.466842831787261</v>
+        <v>6.964292280386282</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05872412865515785</v>
+        <v>0.05804913867061581</v>
       </c>
       <c r="W88">
-        <v>0.2219528504631138</v>
+        <v>0.2221120131014688</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2669278575234447</v>
+        <v>0.2638597212300718</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2383934526445722</v>
+        <v>0.2402934526445722</v>
       </c>
       <c r="C89">
-        <v>-3071.807106372208</v>
+        <v>-3145.277524378429</v>
       </c>
       <c r="D89">
-        <v>1374.680893627791</v>
+        <v>1362.434475621571</v>
       </c>
       <c r="E89">
-        <v>2425.288</v>
+        <v>2486.512</v>
       </c>
       <c r="F89">
-        <v>5326.487999999999</v>
+        <v>5387.712</v>
       </c>
       <c r="G89">
         <v>880</v>
@@ -8591,37 +8591,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M89">
-        <v>1255.9858704</v>
+        <v>1270.4224896</v>
       </c>
       <c r="N89">
-        <v>-924.5817887673468</v>
+        <v>-939.0184079673468</v>
       </c>
       <c r="O89">
-        <v>-203.4079935288163</v>
+        <v>-206.5840497528163</v>
       </c>
       <c r="P89">
-        <v>-721.1737952385305</v>
+        <v>-732.4343582145304</v>
       </c>
       <c r="Q89">
-        <v>-497.3737952385305</v>
+        <v>-508.6343582145304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.347353855740726</v>
+        <v>0.3724833437191198</v>
       </c>
       <c r="T89">
-        <v>6.964292280386282</v>
+        <v>7.544649970418472</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05804913867061581</v>
+        <v>0.05738948936754062</v>
       </c>
       <c r="W89">
-        <v>0.2221120131014688</v>
+        <v>0.2222675584071339</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2638597212300718</v>
+        <v>0.2608613153070029</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2402934526445722</v>
+        <v>0.2421934526445722</v>
       </c>
       <c r="C90">
-        <v>-3145.277524378429</v>
+        <v>-3218.531673294373</v>
       </c>
       <c r="D90">
-        <v>1362.434475621571</v>
+        <v>1350.404326705627</v>
       </c>
       <c r="E90">
-        <v>2486.512</v>
+        <v>2547.736</v>
       </c>
       <c r="F90">
-        <v>5387.712</v>
+        <v>5448.936</v>
       </c>
       <c r="G90">
         <v>880</v>
@@ -8673,37 +8673,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M90">
-        <v>1270.4224896</v>
+        <v>1284.8591088</v>
       </c>
       <c r="N90">
-        <v>-939.0184079673468</v>
+        <v>-953.455027167347</v>
       </c>
       <c r="O90">
-        <v>-206.5840497528163</v>
+        <v>-209.7601059768163</v>
       </c>
       <c r="P90">
-        <v>-732.4343582145304</v>
+        <v>-743.6949211905306</v>
       </c>
       <c r="Q90">
-        <v>-508.6343582145304</v>
+        <v>-519.8949211905306</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3724833437191198</v>
+        <v>0.4021818295117671</v>
       </c>
       <c r="T90">
-        <v>7.544649970418472</v>
+        <v>8.230527240456516</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05738948936754062</v>
+        <v>0.05674466364430982</v>
       </c>
       <c r="W90">
-        <v>0.2222675584071339</v>
+        <v>0.2224196083126717</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2608613153070029</v>
+        <v>0.2579302892923173</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2421934526445722</v>
+        <v>0.2440934526445722</v>
       </c>
       <c r="C91">
-        <v>-3218.531673294373</v>
+        <v>-3291.575231875206</v>
       </c>
       <c r="D91">
-        <v>1350.404326705627</v>
+        <v>1338.584768124794</v>
       </c>
       <c r="E91">
-        <v>2547.736</v>
+        <v>2608.96</v>
       </c>
       <c r="F91">
-        <v>5448.936</v>
+        <v>5510.16</v>
       </c>
       <c r="G91">
         <v>880</v>
@@ -8755,37 +8755,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M91">
-        <v>1284.8591088</v>
+        <v>1299.295728</v>
       </c>
       <c r="N91">
-        <v>-953.455027167347</v>
+        <v>-967.891646367347</v>
       </c>
       <c r="O91">
-        <v>-209.7601059768163</v>
+        <v>-212.9361622008163</v>
       </c>
       <c r="P91">
-        <v>-743.6949211905306</v>
+        <v>-754.9554841665306</v>
       </c>
       <c r="Q91">
-        <v>-519.8949211905306</v>
+        <v>-531.1554841665306</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4021818295117671</v>
+        <v>0.4378200124629439</v>
       </c>
       <c r="T91">
-        <v>8.230527240456516</v>
+        <v>9.053579964502168</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05674466364430982</v>
+        <v>0.05611416738159528</v>
       </c>
       <c r="W91">
-        <v>0.2224196083126717</v>
+        <v>0.2225682793314198</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2579302892923173</v>
+        <v>0.2550643971890694</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2440934526445722</v>
+        <v>0.2459934526445722</v>
       </c>
       <c r="C92">
-        <v>-3291.575231875206</v>
+        <v>-3364.413681785497</v>
       </c>
       <c r="D92">
-        <v>1338.584768124794</v>
+        <v>1326.970318214503</v>
       </c>
       <c r="E92">
-        <v>2608.96</v>
+        <v>2670.184</v>
       </c>
       <c r="F92">
-        <v>5510.16</v>
+        <v>5571.384</v>
       </c>
       <c r="G92">
         <v>880</v>
@@ -8837,37 +8837,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M92">
-        <v>1299.295728</v>
+        <v>1313.7323472</v>
       </c>
       <c r="N92">
-        <v>-967.891646367347</v>
+        <v>-982.328265567347</v>
       </c>
       <c r="O92">
-        <v>-212.9361622008163</v>
+        <v>-216.1122184248163</v>
       </c>
       <c r="P92">
-        <v>-754.9554841665306</v>
+        <v>-766.2160471425307</v>
       </c>
       <c r="Q92">
-        <v>-531.1554841665306</v>
+        <v>-542.4160471425307</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4378200124629439</v>
+        <v>0.4813777916254932</v>
       </c>
       <c r="T92">
-        <v>9.053579964502168</v>
+        <v>10.0595332938913</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05611416738159528</v>
+        <v>0.05549752817959971</v>
       </c>
       <c r="W92">
-        <v>0.2225682793314198</v>
+        <v>0.2227136828552504</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2550643971890694</v>
+        <v>0.2522614917254532</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2459934526445722</v>
+        <v>0.2478934526445723</v>
       </c>
       <c r="C93">
-        <v>-3364.413681785497</v>
+        <v>-3437.052316076114</v>
       </c>
       <c r="D93">
-        <v>1326.970318214503</v>
+        <v>1315.555683923887</v>
       </c>
       <c r="E93">
-        <v>2670.184</v>
+        <v>2731.408</v>
       </c>
       <c r="F93">
-        <v>5571.384</v>
+        <v>5632.608</v>
       </c>
       <c r="G93">
         <v>880</v>
@@ -8919,37 +8919,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M93">
-        <v>1313.7323472</v>
+        <v>1328.1689664</v>
       </c>
       <c r="N93">
-        <v>-982.328265567347</v>
+        <v>-996.764884767347</v>
       </c>
       <c r="O93">
-        <v>-216.1122184248163</v>
+        <v>-219.2882746488163</v>
       </c>
       <c r="P93">
-        <v>-766.2160471425307</v>
+        <v>-777.4766101185306</v>
       </c>
       <c r="Q93">
-        <v>-542.4160471425307</v>
+        <v>-553.6766101185306</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4813777916254932</v>
+        <v>0.53582501557868</v>
       </c>
       <c r="T93">
-        <v>10.0595332938913</v>
+        <v>11.31697495562771</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05549752817959971</v>
+        <v>0.05489429417764755</v>
       </c>
       <c r="W93">
-        <v>0.2227136828552504</v>
+        <v>0.2228559254329107</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2522614917254532</v>
+        <v>0.249519518989307</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2478934526445723</v>
+        <v>0.2497934526445723</v>
       </c>
       <c r="C94">
-        <v>-3437.052316076114</v>
+        <v>-3509.496247227331</v>
       </c>
       <c r="D94">
-        <v>1315.555683923887</v>
+        <v>1304.33575277267</v>
       </c>
       <c r="E94">
-        <v>2731.408</v>
+        <v>2792.632000000001</v>
       </c>
       <c r="F94">
-        <v>5632.608</v>
+        <v>5693.832</v>
       </c>
       <c r="G94">
         <v>880</v>
@@ -9001,37 +9001,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M94">
-        <v>1328.1689664</v>
+        <v>1342.6055856</v>
       </c>
       <c r="N94">
-        <v>-996.764884767347</v>
+        <v>-1011.201503967347</v>
       </c>
       <c r="O94">
-        <v>-219.2882746488163</v>
+        <v>-222.4643308728163</v>
       </c>
       <c r="P94">
-        <v>-777.4766101185306</v>
+        <v>-788.7371730945306</v>
       </c>
       <c r="Q94">
-        <v>-553.6766101185306</v>
+        <v>-564.9371730945306</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.53582501557868</v>
+        <v>0.6058285892327772</v>
       </c>
       <c r="T94">
-        <v>11.31697495562771</v>
+        <v>12.93368566357453</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05489429417764755</v>
+        <v>0.05430403294993091</v>
       </c>
       <c r="W94">
-        <v>0.2228559254329107</v>
+        <v>0.2229951090304063</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.249519518989307</v>
+        <v>0.2468365134087768</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2497934526445723</v>
+        <v>0.2516934526445722</v>
       </c>
       <c r="C95">
-        <v>-3509.496247227331</v>
+        <v>-3581.750414783846</v>
       </c>
       <c r="D95">
-        <v>1304.33575277267</v>
+        <v>1293.305585216153</v>
       </c>
       <c r="E95">
-        <v>2792.632000000001</v>
+        <v>2853.856</v>
       </c>
       <c r="F95">
-        <v>5693.832</v>
+        <v>5755.056</v>
       </c>
       <c r="G95">
         <v>880</v>
@@ -9083,37 +9083,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M95">
-        <v>1342.6055856</v>
+        <v>1357.0422048</v>
       </c>
       <c r="N95">
-        <v>-1011.201503967347</v>
+        <v>-1025.638123167347</v>
       </c>
       <c r="O95">
-        <v>-222.4643308728163</v>
+        <v>-225.6403870968163</v>
       </c>
       <c r="P95">
-        <v>-788.7371730945306</v>
+        <v>-799.9977360705307</v>
       </c>
       <c r="Q95">
-        <v>-564.9371730945306</v>
+        <v>-576.1977360705307</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6058285892327772</v>
+        <v>0.6991666874382402</v>
       </c>
       <c r="T95">
-        <v>12.93368566357453</v>
+        <v>15.08929994083696</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05430403294993091</v>
+        <v>0.05372633047174016</v>
       </c>
       <c r="W95">
-        <v>0.2229951090304063</v>
+        <v>0.2231313312747637</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2468365134087768</v>
+        <v>0.2442105930533643</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2516934526445722</v>
+        <v>0.2535934526445723</v>
       </c>
       <c r="C96">
-        <v>-3581.750414783846</v>
+        <v>-3653.819592605653</v>
       </c>
       <c r="D96">
-        <v>1293.305585216153</v>
+        <v>1282.460407394346</v>
       </c>
       <c r="E96">
-        <v>2853.856</v>
+        <v>2915.08</v>
       </c>
       <c r="F96">
-        <v>5755.056</v>
+        <v>5816.28</v>
       </c>
       <c r="G96">
         <v>880</v>
@@ -9165,37 +9165,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M96">
-        <v>1357.0422048</v>
+        <v>1371.478824</v>
       </c>
       <c r="N96">
-        <v>-1025.638123167347</v>
+        <v>-1040.074742367347</v>
       </c>
       <c r="O96">
-        <v>-225.6403870968163</v>
+        <v>-228.8164433208163</v>
       </c>
       <c r="P96">
-        <v>-799.9977360705307</v>
+        <v>-811.2582990465306</v>
       </c>
       <c r="Q96">
-        <v>-576.1977360705307</v>
+        <v>-587.4582990465306</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6991666874382402</v>
+        <v>0.8298400249258886</v>
       </c>
       <c r="T96">
-        <v>15.08929994083696</v>
+        <v>18.10715992900436</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05372633047174016</v>
+        <v>0.05316079015098499</v>
       </c>
       <c r="W96">
-        <v>0.2231313312747637</v>
+        <v>0.2232646856823978</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2442105930533643</v>
+        <v>0.24163995523175</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2535934526445723</v>
+        <v>0.2554934526445722</v>
       </c>
       <c r="C97">
-        <v>-3653.819592605653</v>
+        <v>-3725.708395757107</v>
       </c>
       <c r="D97">
-        <v>1282.460407394346</v>
+        <v>1271.795604242893</v>
       </c>
       <c r="E97">
-        <v>2915.08</v>
+        <v>2976.304</v>
       </c>
       <c r="F97">
-        <v>5816.28</v>
+        <v>5877.504</v>
       </c>
       <c r="G97">
         <v>880</v>
@@ -9247,37 +9247,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M97">
-        <v>1371.478824</v>
+        <v>1385.9154432</v>
       </c>
       <c r="N97">
-        <v>-1040.074742367347</v>
+        <v>-1054.511361567347</v>
       </c>
       <c r="O97">
-        <v>-228.8164433208163</v>
+        <v>-231.9924995448163</v>
       </c>
       <c r="P97">
-        <v>-811.2582990465306</v>
+        <v>-822.5188620225306</v>
       </c>
       <c r="Q97">
-        <v>-587.4582990465306</v>
+        <v>-598.7188620225306</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8298400249258886</v>
+        <v>1.025850031157361</v>
       </c>
       <c r="T97">
-        <v>18.10715992900436</v>
+        <v>22.63394991125546</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05316079015098499</v>
+        <v>0.05260703192024557</v>
       </c>
       <c r="W97">
-        <v>0.2232646856823978</v>
+        <v>0.2233952618732061</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.24163995523175</v>
+        <v>0.2391228723647525</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2554934526445722</v>
+        <v>0.2573934526445723</v>
       </c>
       <c r="C98">
-        <v>-3725.708395757106</v>
+        <v>-3797.421287055118</v>
       </c>
       <c r="D98">
-        <v>1271.795604242893</v>
+        <v>1261.306712944881</v>
       </c>
       <c r="E98">
-        <v>2976.303999999999</v>
+        <v>3037.527999999999</v>
       </c>
       <c r="F98">
-        <v>5877.503999999999</v>
+        <v>5938.727999999999</v>
       </c>
       <c r="G98">
         <v>880</v>
@@ -9329,37 +9329,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M98">
-        <v>1385.9154432</v>
+        <v>1400.3520624</v>
       </c>
       <c r="N98">
-        <v>-1054.511361567347</v>
+        <v>-1068.947980767347</v>
       </c>
       <c r="O98">
-        <v>-231.9924995448163</v>
+        <v>-235.1685557688163</v>
       </c>
       <c r="P98">
-        <v>-822.5188620225305</v>
+        <v>-833.7794249985304</v>
       </c>
       <c r="Q98">
-        <v>-598.7188620225304</v>
+        <v>-609.9794249985305</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.025850031157358</v>
+        <v>1.352533374876478</v>
       </c>
       <c r="T98">
-        <v>22.63394991125539</v>
+        <v>30.17859988167386</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05260703192024558</v>
+        <v>0.05206469138498531</v>
       </c>
       <c r="W98">
-        <v>0.2233952618732061</v>
+        <v>0.2235231457714205</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2391228723647526</v>
+        <v>0.2366576881135696</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2573934526445723</v>
+        <v>0.2592934526445722</v>
       </c>
       <c r="C99">
-        <v>-3797.421287055118</v>
+        <v>-3868.962583295959</v>
       </c>
       <c r="D99">
-        <v>1261.306712944881</v>
+        <v>1250.98941670404</v>
       </c>
       <c r="E99">
-        <v>3037.527999999999</v>
+        <v>3098.751999999999</v>
       </c>
       <c r="F99">
-        <v>5938.727999999999</v>
+        <v>5999.951999999999</v>
       </c>
       <c r="G99">
         <v>880</v>
@@ -9411,37 +9411,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M99">
-        <v>1400.3520624</v>
+        <v>1414.7886816</v>
       </c>
       <c r="N99">
-        <v>-1068.947980767347</v>
+        <v>-1083.384599967347</v>
       </c>
       <c r="O99">
-        <v>-235.1685557688163</v>
+        <v>-238.3446119928163</v>
       </c>
       <c r="P99">
-        <v>-833.7794249985304</v>
+        <v>-845.0399879745305</v>
       </c>
       <c r="Q99">
-        <v>-609.9794249985305</v>
+        <v>-621.2399879745305</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.352533374876478</v>
+        <v>2.005900062314717</v>
       </c>
       <c r="T99">
-        <v>30.17859988167386</v>
+        <v>45.26789982251078</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05206469138498531</v>
+        <v>0.05153341902391403</v>
       </c>
       <c r="W99">
-        <v>0.2235231457714205</v>
+        <v>0.2236484197941611</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2366576881135696</v>
+        <v>0.2342428137450637</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2592934526445722</v>
+        <v>0.2611934526445723</v>
       </c>
       <c r="C100">
-        <v>-3868.962583295959</v>
+        <v>-3940.336461178933</v>
       </c>
       <c r="D100">
-        <v>1250.98941670404</v>
+        <v>1240.839538821067</v>
       </c>
       <c r="E100">
-        <v>3098.751999999999</v>
+        <v>3159.976</v>
       </c>
       <c r="F100">
-        <v>5999.951999999999</v>
+        <v>6061.175999999999</v>
       </c>
       <c r="G100">
         <v>880</v>
@@ -9493,37 +9493,37 @@
         <v>331.4040816326531</v>
       </c>
       <c r="M100">
-        <v>1414.7886816</v>
+        <v>1429.2253008</v>
       </c>
       <c r="N100">
-        <v>-1083.384599967347</v>
+        <v>-1097.821219167347</v>
       </c>
       <c r="O100">
-        <v>-238.3446119928163</v>
+        <v>-241.5206682168163</v>
       </c>
       <c r="P100">
-        <v>-845.0399879745305</v>
+        <v>-856.3005509505306</v>
       </c>
       <c r="Q100">
-        <v>-621.2399879745305</v>
+        <v>-632.5005509505306</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.005900062314717</v>
+        <v>3.966000124629434</v>
       </c>
       <c r="T100">
-        <v>45.26789982251078</v>
+        <v>90.53579964502158</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05153341902391403</v>
+        <v>0.05101287943781389</v>
       </c>
       <c r="W100">
-        <v>0.2236484197941611</v>
+        <v>0.2237711630285635</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2342428137450637</v>
+        <v>0.2318767247173358</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2611934526445723</v>
-      </c>
-      <c r="C101">
-        <v>-3940.336461178933</v>
-      </c>
-      <c r="D101">
-        <v>1240.839538821067</v>
-      </c>
-      <c r="E101">
-        <v>3159.976</v>
-      </c>
-      <c r="F101">
-        <v>6061.175999999999</v>
-      </c>
-      <c r="G101">
-        <v>880</v>
-      </c>
-      <c r="H101">
-        <v>3221.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>555.2040816326531</v>
-      </c>
-      <c r="K101">
-        <v>223.8</v>
-      </c>
-      <c r="L101">
-        <v>331.4040816326531</v>
-      </c>
-      <c r="M101">
-        <v>1429.2253008</v>
-      </c>
-      <c r="N101">
-        <v>-1097.821219167347</v>
-      </c>
-      <c r="O101">
-        <v>-241.5206682168163</v>
-      </c>
-      <c r="P101">
-        <v>-856.3005509505306</v>
-      </c>
-      <c r="Q101">
-        <v>-632.5005509505306</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.966000124629434</v>
-      </c>
-      <c r="T101">
-        <v>90.53579964502158</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05101287943781389</v>
-      </c>
-      <c r="W101">
-        <v>0.2237711630285635</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2318767247173358</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
